--- a/research/traditional_assets/database/data/netherlands/netherlands_aerospace_defense.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_aerospace_defense.xlsx
@@ -650,10 +650,10 @@
         <v>0.2254142757216166</v>
       </c>
       <c r="X2">
-        <v>0.0877015882097974</v>
+        <v>0.08767464921407095</v>
       </c>
       <c r="Y2">
-        <v>0.1377126875118192</v>
+        <v>0.1377396265075456</v>
       </c>
       <c r="Z2">
         <v>63.35684787189192</v>
@@ -662,10 +662,10 @@
         <v>2.662110245675048</v>
       </c>
       <c r="AB2">
-        <v>0.08279189059205444</v>
+        <v>0.08276774129399381</v>
       </c>
       <c r="AC2">
-        <v>2.579318355082993</v>
+        <v>2.579342504381054</v>
       </c>
       <c r="AD2">
         <v>14633.1</v>
@@ -787,10 +787,10 @@
         <v>0.2254142757216166</v>
       </c>
       <c r="X3">
-        <v>0.0877015882097974</v>
+        <v>0.08767464921407095</v>
       </c>
       <c r="Y3">
-        <v>0.1377126875118192</v>
+        <v>0.1377396265075456</v>
       </c>
       <c r="Z3">
         <v>63.35684787189192</v>
@@ -799,10 +799,10 @@
         <v>2.662110245675048</v>
       </c>
       <c r="AB3">
-        <v>0.08279189059205444</v>
+        <v>0.08276774129399381</v>
       </c>
       <c r="AC3">
-        <v>2.579318355082993</v>
+        <v>2.579342504381054</v>
       </c>
       <c r="AD3">
         <v>14633.1</v>
@@ -1139,49 +1139,49 @@
         <v>4.73434574578739</v>
       </c>
       <c r="F2">
-        <v>3.09066843759605</v>
+        <v>2.53310368485578</v>
       </c>
       <c r="G2">
         <v>2.11748618065002</v>
       </c>
       <c r="H2">
-        <v>3.68058923971869</v>
+        <v>4.49849795965618</v>
       </c>
       <c r="I2">
         <v>0.103556112266995</v>
       </c>
       <c r="J2">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="K2">
         <v>126672.9</v>
       </c>
       <c r="L2">
-        <v>118404.476226392</v>
+        <v>114725.456802314</v>
       </c>
       <c r="M2">
         <v>131066.2</v>
       </c>
       <c r="N2">
-        <v>133599.756226392</v>
+        <v>135572.976802314</v>
       </c>
       <c r="O2">
         <v>14633.1</v>
       </c>
       <c r="P2">
-        <v>25435.08</v>
+        <v>31087.32</v>
       </c>
       <c r="Q2">
-        <v>0.0827918905920544</v>
+        <v>0.08276774129399379</v>
       </c>
       <c r="R2">
-        <v>0.0820903845610351</v>
+        <v>0.0815388433024667</v>
       </c>
       <c r="S2">
         <v>0.0402906</v>
       </c>
       <c r="T2">
-        <v>0.0429618</v>
+        <v>0.0428876</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1190,20 +1190,20 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="W2">
-        <v>0.0877015882097974</v>
+        <v>0.08767464921407089</v>
       </c>
       <c r="X2">
-        <v>0.0906795860500428</v>
+        <v>0.0924404760288034</v>
       </c>
       <c r="Y2">
         <v>0.967081967992401</v>
       </c>
       <c r="Z2">
-        <v>1.03581368282865</v>
+        <v>1.07714725239731</v>
       </c>
       <c r="AA2">
         <v>14633.1</v>
@@ -1236,7 +1236,7 @@
         <v>126672.9</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.04329999999999999</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08439354478064845</v>
+        <v>0.08436873256272703</v>
       </c>
       <c r="C2">
-        <v>135866.6777142078</v>
+        <v>135865.4312313797</v>
       </c>
       <c r="D2">
-        <v>125626.8777142078</v>
+        <v>125625.6312313797</v>
       </c>
       <c r="E2">
         <v>-14633.1</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08439354478064845</v>
+        <v>0.08436873256272703</v>
       </c>
       <c r="T2">
         <v>0.890732853642657</v>
       </c>
       <c r="U2">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.258</v>
       </c>
       <c r="W2">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08421958743511436</v>
+        <v>0.08418445123271522</v>
       </c>
       <c r="C3">
-        <v>135022.4348107424</v>
+        <v>135055.4919655159</v>
       </c>
       <c r="D3">
-        <v>126195.6948107424</v>
+        <v>126228.7519655159</v>
       </c>
       <c r="E3">
         <v>-13220.04</v>
@@ -1539,37 +1539,37 @@
         <v>4551.6</v>
       </c>
       <c r="M3">
-        <v>73.05520199999999</v>
+        <v>71.07691799999999</v>
       </c>
       <c r="N3">
-        <v>4478.544798000001</v>
+        <v>4480.523082000001</v>
       </c>
       <c r="O3">
-        <v>1155.464557884</v>
+        <v>1155.974955156</v>
       </c>
       <c r="P3">
-        <v>3323.080240116001</v>
+        <v>3324.548126844001</v>
       </c>
       <c r="Q3">
-        <v>5682.080240116001</v>
+        <v>5683.548126844001</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08468280144961046</v>
+        <v>0.0846578032653689</v>
       </c>
       <c r="T3">
         <v>0.8974088513942009</v>
       </c>
       <c r="U3">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.258</v>
       </c>
       <c r="W3">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>62.30357148283569</v>
+        <v>64.03766691178143</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08404563008958028</v>
+        <v>0.08400016990270337</v>
       </c>
       <c r="C4">
-        <v>134183.3663500552</v>
+        <v>134251.371725658</v>
       </c>
       <c r="D4">
-        <v>126769.6863500552</v>
+        <v>126837.691725658</v>
       </c>
       <c r="E4">
         <v>-11806.98</v>
@@ -1621,37 +1621,37 @@
         <v>4551.6</v>
       </c>
       <c r="M4">
-        <v>146.110404</v>
+        <v>142.153836</v>
       </c>
       <c r="N4">
-        <v>4405.489596</v>
+        <v>4409.446164</v>
       </c>
       <c r="O4">
-        <v>1136.616315768</v>
+        <v>1137.637110312</v>
       </c>
       <c r="P4">
-        <v>3268.873280232</v>
+        <v>3271.809053688</v>
       </c>
       <c r="Q4">
-        <v>5627.873280232</v>
+        <v>5630.809053688</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08497796131589826</v>
+        <v>0.08495277337010548</v>
       </c>
       <c r="T4">
         <v>0.9042210939978171</v>
       </c>
       <c r="U4">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.258</v>
       </c>
       <c r="W4">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>31.15178574141784</v>
+        <v>32.0188334558907</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08387167274404622</v>
+        <v>0.08381588857269152</v>
       </c>
       <c r="C5">
-        <v>133349.5432614433</v>
+        <v>133453.1551346749</v>
       </c>
       <c r="D5">
-        <v>127348.9232614433</v>
+        <v>127452.5351346749</v>
       </c>
       <c r="E5">
         <v>-10393.92</v>
@@ -1703,37 +1703,37 @@
         <v>4551.6</v>
       </c>
       <c r="M5">
-        <v>219.165606</v>
+        <v>213.230754</v>
       </c>
       <c r="N5">
-        <v>4332.434394</v>
+        <v>4338.369246</v>
       </c>
       <c r="O5">
-        <v>1117.768073652</v>
+        <v>1119.299265468</v>
       </c>
       <c r="P5">
-        <v>3214.666320348</v>
+        <v>3219.069980532</v>
       </c>
       <c r="Q5">
-        <v>5573.666320348</v>
+        <v>5578.069980532</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08527920695262498</v>
+        <v>0.08525382533267167</v>
       </c>
       <c r="T5">
         <v>0.9111737952118173</v>
       </c>
       <c r="U5">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.258</v>
       </c>
       <c r="W5">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>20.76785716094522</v>
+        <v>21.3458889705938</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08369771539851215</v>
+        <v>0.08363160724267969</v>
       </c>
       <c r="C6">
-        <v>132521.0377765172</v>
+        <v>132660.9284642591</v>
       </c>
       <c r="D6">
-        <v>127933.4777765172</v>
+        <v>128073.3684642591</v>
       </c>
       <c r="E6">
         <v>-8980.860000000001</v>
@@ -1785,37 +1785,37 @@
         <v>4551.6</v>
       </c>
       <c r="M6">
-        <v>292.220808</v>
+        <v>284.307672</v>
       </c>
       <c r="N6">
-        <v>4259.379192</v>
+        <v>4267.292328</v>
       </c>
       <c r="O6">
-        <v>1098.919831536</v>
+        <v>1100.961420624</v>
       </c>
       <c r="P6">
-        <v>3160.459360464</v>
+        <v>3166.330907376</v>
       </c>
       <c r="Q6">
-        <v>5519.459360464</v>
+        <v>5525.330907376</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08558672854011681</v>
+        <v>0.08556114921112468</v>
       </c>
       <c r="T6">
         <v>0.9182713443677758</v>
       </c>
       <c r="U6">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.258</v>
       </c>
       <c r="W6">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>15.57589287070892</v>
+        <v>16.00941672794535</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08352375805297807</v>
+        <v>0.08344732591266785</v>
       </c>
       <c r="C7">
-        <v>131697.923459227</v>
+        <v>131874.7796752822</v>
       </c>
       <c r="D7">
-        <v>128523.423459227</v>
+        <v>128700.2796752822</v>
       </c>
       <c r="E7">
         <v>-7567.8</v>
@@ -1867,37 +1867,37 @@
         <v>4551.6</v>
       </c>
       <c r="M7">
-        <v>365.27601</v>
+        <v>355.38459</v>
       </c>
       <c r="N7">
-        <v>4186.323990000001</v>
+        <v>4196.215410000001</v>
       </c>
       <c r="O7">
-        <v>1080.07158942</v>
+        <v>1082.62357578</v>
       </c>
       <c r="P7">
-        <v>3106.252400580001</v>
+        <v>3113.59183422</v>
       </c>
       <c r="Q7">
-        <v>5465.252400580001</v>
+        <v>5472.59183422</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.08590072426629272</v>
+        <v>0.08587494306596617</v>
       </c>
       <c r="T7">
         <v>0.9255183156112282</v>
       </c>
       <c r="U7">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.258</v>
       </c>
       <c r="W7">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>12.46071429656714</v>
+        <v>12.80753338235628</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08334980070744399</v>
+        <v>0.08326304458265602</v>
       </c>
       <c r="C8">
-        <v>130880.2752367251</v>
+        <v>131094.7984593391</v>
       </c>
       <c r="D8">
-        <v>129118.8352367251</v>
+        <v>129333.3584593391</v>
       </c>
       <c r="E8">
         <v>-6154.74</v>
@@ -1949,37 +1949,37 @@
         <v>4551.6</v>
       </c>
       <c r="M8">
-        <v>438.3312120000001</v>
+        <v>426.461508</v>
       </c>
       <c r="N8">
-        <v>4113.268788</v>
+        <v>4125.138492</v>
       </c>
       <c r="O8">
-        <v>1061.223347304</v>
+        <v>1064.285730936</v>
       </c>
       <c r="P8">
-        <v>3052.045440696</v>
+        <v>3060.852761064</v>
       </c>
       <c r="Q8">
-        <v>5411.045440696</v>
+        <v>5419.852761064</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.0862214007526</v>
+        <v>0.08619541338580428</v>
       </c>
       <c r="T8">
         <v>0.9329194777322006</v>
       </c>
       <c r="U8">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.258</v>
       </c>
       <c r="W8">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>10.38392858047261</v>
+        <v>10.6729444852969</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08317584336190993</v>
+        <v>0.0830787632526442</v>
       </c>
       <c r="C9">
-        <v>130068.1694310891</v>
+        <v>130321.0762815264</v>
       </c>
       <c r="D9">
-        <v>129719.7894310891</v>
+        <v>129972.6962815264</v>
       </c>
       <c r="E9">
         <v>-4741.68</v>
@@ -2031,37 +2031,37 @@
         <v>4551.6</v>
       </c>
       <c r="M9">
-        <v>511.3864140000001</v>
+        <v>497.538426</v>
       </c>
       <c r="N9">
-        <v>4040.213586</v>
+        <v>4054.061574</v>
       </c>
       <c r="O9">
-        <v>1042.375105188</v>
+        <v>1045.947886092</v>
       </c>
       <c r="P9">
-        <v>2997.838480812</v>
+        <v>3008.113687908</v>
       </c>
       <c r="Q9">
-        <v>5356.838480812</v>
+        <v>5367.113687908</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.08654897350743003</v>
+        <v>0.08652277554047763</v>
       </c>
       <c r="T9">
         <v>0.9404798046299684</v>
       </c>
       <c r="U9">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.258</v>
       </c>
       <c r="W9">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>8.900510211833668</v>
+        <v>9.148238130254487</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08306718201637586</v>
+        <v>0.08298352192263235</v>
       </c>
       <c r="C10">
-        <v>129033.3383740713</v>
+        <v>129240.9264476165</v>
       </c>
       <c r="D10">
-        <v>130098.0183740713</v>
+        <v>130305.6064476165</v>
       </c>
       <c r="E10">
         <v>-3328.620000000001</v>
@@ -2113,37 +2113,37 @@
         <v>4551.6</v>
       </c>
       <c r="M10">
-        <v>596.876544</v>
+        <v>585.572064</v>
       </c>
       <c r="N10">
-        <v>3954.723456000001</v>
+        <v>3966.027936</v>
       </c>
       <c r="O10">
-        <v>1020.318651648</v>
+        <v>1023.235207488</v>
       </c>
       <c r="P10">
-        <v>2934.404804352001</v>
+        <v>2942.792728512</v>
       </c>
       <c r="Q10">
-        <v>5293.404804352001</v>
+        <v>5301.792728512</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.08688366740910419</v>
+        <v>0.08685725426373081</v>
       </c>
       <c r="T10">
         <v>0.9482044864602961</v>
       </c>
       <c r="U10">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.258</v>
       </c>
       <c r="W10">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>7.625697551284577</v>
+        <v>7.772911789726364</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08290138667084178</v>
+        <v>0.08281037059262052</v>
       </c>
       <c r="C11">
-        <v>128201.6487174763</v>
+        <v>128437.4952814575</v>
       </c>
       <c r="D11">
-        <v>130679.3887174763</v>
+        <v>130915.2352814575</v>
       </c>
       <c r="E11">
         <v>-1915.560000000001</v>
@@ -2195,37 +2195,37 @@
         <v>4551.6</v>
       </c>
       <c r="M11">
-        <v>671.4861119999999</v>
+        <v>658.7685719999999</v>
       </c>
       <c r="N11">
-        <v>3880.113888</v>
+        <v>3892.831428</v>
       </c>
       <c r="O11">
-        <v>1001.069383104</v>
+        <v>1004.350508424</v>
       </c>
       <c r="P11">
-        <v>2879.044504896</v>
+        <v>2888.480919576</v>
       </c>
       <c r="Q11">
-        <v>5238.044504896</v>
+        <v>5247.480919576001</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.08722571722070525</v>
+        <v>0.08719908416771485</v>
       </c>
       <c r="T11">
         <v>0.9560989415176643</v>
       </c>
       <c r="U11">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.258</v>
       </c>
       <c r="W11">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>6.778397823364068</v>
+        <v>6.909254924201212</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08289883132530772</v>
+        <v>0.08276335926260869</v>
       </c>
       <c r="C12">
-        <v>126797.5898363909</v>
+        <v>127190.9379871685</v>
       </c>
       <c r="D12">
-        <v>130688.3898363909</v>
+        <v>131081.7379871685</v>
       </c>
       <c r="E12">
         <v>-502.5</v>
@@ -2277,37 +2277,37 @@
         <v>4551.6</v>
       </c>
       <c r="M12">
-        <v>777.183</v>
+        <v>755.9871000000001</v>
       </c>
       <c r="N12">
-        <v>3774.417</v>
+        <v>3795.6129</v>
       </c>
       <c r="O12">
-        <v>973.7995860000001</v>
+        <v>979.2681282000001</v>
       </c>
       <c r="P12">
-        <v>2800.617414</v>
+        <v>2816.3447718</v>
       </c>
       <c r="Q12">
-        <v>5159.617414</v>
+        <v>5175.3447718</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.08757536813923079</v>
+        <v>0.08754851029178742</v>
       </c>
       <c r="T12">
         <v>0.9641688289096405</v>
       </c>
       <c r="U12">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.258</v>
       </c>
       <c r="W12">
-        <v>0.04081</v>
+        <v>0.039697</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>5.856535719386554</v>
+        <v>6.020737655444121</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08287178997977365</v>
+        <v>0.08266811793259685</v>
       </c>
       <c r="C13">
-        <v>125479.8581145448</v>
+        <v>126116.501159878</v>
       </c>
       <c r="D13">
-        <v>130783.7181145448</v>
+        <v>131420.361159878</v>
       </c>
       <c r="E13">
         <v>910.5599999999995</v>
@@ -2359,37 +2359,37 @@
         <v>4551.6</v>
       </c>
       <c r="M13">
-        <v>878.2167900000001</v>
+        <v>844.0207380000001</v>
       </c>
       <c r="N13">
-        <v>3673.38321</v>
+        <v>3707.579262</v>
       </c>
       <c r="O13">
-        <v>947.7328681800001</v>
+        <v>956.5554495960001</v>
       </c>
       <c r="P13">
-        <v>2725.65034182</v>
+        <v>2751.023812404</v>
       </c>
       <c r="Q13">
-        <v>5084.650341820001</v>
+        <v>5110.023812404001</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.08793287638176814</v>
+        <v>0.08790578868831106</v>
       </c>
       <c r="T13">
         <v>0.972420062085706</v>
       </c>
       <c r="U13">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V13">
         <v>0.258</v>
       </c>
       <c r="W13">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.182774972908454</v>
+        <v>5.392758489306219</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08273344863423956</v>
+        <v>0.08251351660258502</v>
       </c>
       <c r="C14">
-        <v>124556.6737207221</v>
+        <v>125256.8548479724</v>
       </c>
       <c r="D14">
-        <v>131273.5937207222</v>
+        <v>131973.7748479724</v>
       </c>
       <c r="E14">
         <v>2323.620000000001</v>
@@ -2441,37 +2441,37 @@
         <v>4551.6</v>
       </c>
       <c r="M14">
-        <v>958.0546800000001</v>
+        <v>920.749896</v>
       </c>
       <c r="N14">
-        <v>3593.54532</v>
+        <v>3630.850104</v>
       </c>
       <c r="O14">
-        <v>927.1346925600001</v>
+        <v>936.7593268320001</v>
       </c>
       <c r="P14">
-        <v>2666.41062744</v>
+        <v>2694.090777168</v>
       </c>
       <c r="Q14">
-        <v>5025.41062744</v>
+        <v>5053.090777167999</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.08829850981163587</v>
+        <v>0.08827118704839206</v>
       </c>
       <c r="T14">
         <v>0.9808588232885004</v>
       </c>
       <c r="U14">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0.258</v>
       </c>
       <c r="W14">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>4.750877058499416</v>
+        <v>4.943361948530701</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08259510728870549</v>
+        <v>0.08235891527257316</v>
       </c>
       <c r="C15">
-        <v>123637.1729715738</v>
+        <v>124401.8891176207</v>
       </c>
       <c r="D15">
-        <v>131767.1529715738</v>
+        <v>132531.8691176207</v>
       </c>
       <c r="E15">
         <v>3736.679999999998</v>
@@ -2523,37 +2523,37 @@
         <v>4551.6</v>
       </c>
       <c r="M15">
-        <v>1037.89257</v>
+        <v>997.4790539999999</v>
       </c>
       <c r="N15">
-        <v>3513.70743</v>
+        <v>3554.120946</v>
       </c>
       <c r="O15">
-        <v>906.5365169400001</v>
+        <v>916.9632040680001</v>
       </c>
       <c r="P15">
-        <v>2607.17091306</v>
+        <v>2637.157741932</v>
       </c>
       <c r="Q15">
-        <v>4966.17091306</v>
+        <v>4996.157741932</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.08867254860770746</v>
+        <v>0.08864498537077375</v>
       </c>
       <c r="T15">
         <v>0.9894915790017037</v>
       </c>
       <c r="U15">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.258</v>
       </c>
       <c r="W15">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>4.385424977076385</v>
+        <v>4.563103337105263</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08260219794317142</v>
+        <v>0.08230819394256134</v>
       </c>
       <c r="C16">
-        <v>122198.7254837633</v>
+        <v>123172.9574445704</v>
       </c>
       <c r="D16">
-        <v>131741.7654837633</v>
+        <v>132715.9974445704</v>
       </c>
       <c r="E16">
         <v>5149.74</v>
@@ -2605,37 +2605,37 @@
         <v>4551.6</v>
       </c>
       <c r="M16">
-        <v>1145.426436</v>
+        <v>1093.991052</v>
       </c>
       <c r="N16">
-        <v>3406.173564000001</v>
+        <v>3457.608948</v>
       </c>
       <c r="O16">
-        <v>878.7927795120002</v>
+        <v>892.063108584</v>
       </c>
       <c r="P16">
-        <v>2527.380784488</v>
+        <v>2565.545839416</v>
       </c>
       <c r="Q16">
-        <v>4886.380784488</v>
+        <v>4924.545839416</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.08905528598043189</v>
+        <v>0.08902747667739691</v>
       </c>
       <c r="T16">
         <v>0.9983250964756794</v>
       </c>
       <c r="U16">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V16">
         <v>0.258</v>
       </c>
       <c r="W16">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>3.973716562623495</v>
+        <v>4.160545912764924</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08247424459763736</v>
+        <v>0.0821610126125495</v>
       </c>
       <c r="C17">
-        <v>121245.3013897009</v>
+        <v>122297.1024235923</v>
       </c>
       <c r="D17">
-        <v>132201.4013897009</v>
+        <v>133253.2024235923</v>
       </c>
       <c r="E17">
         <v>6562.799999999997</v>
@@ -2687,37 +2687,37 @@
         <v>4551.6</v>
       </c>
       <c r="M17">
-        <v>1227.24261</v>
+        <v>1172.13327</v>
       </c>
       <c r="N17">
-        <v>3324.357390000001</v>
+        <v>3379.466730000001</v>
       </c>
       <c r="O17">
-        <v>857.6842066200002</v>
+        <v>871.9024163400002</v>
       </c>
       <c r="P17">
-        <v>2466.67318338</v>
+        <v>2507.56431366</v>
       </c>
       <c r="Q17">
-        <v>4825.67318338</v>
+        <v>4866.56431366</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.08944702893839689</v>
+        <v>0.08941896777947</v>
       </c>
       <c r="T17">
         <v>1.007366461419631</v>
       </c>
       <c r="U17">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V17">
         <v>0.258</v>
       </c>
       <c r="W17">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>3.708802125115263</v>
+        <v>3.883176185247264</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08234629125210326</v>
+        <v>0.08201383128253767</v>
       </c>
       <c r="C18">
-        <v>120295.0957864828</v>
+        <v>121425.6140515161</v>
       </c>
       <c r="D18">
-        <v>132664.2557864828</v>
+        <v>133794.7740515161</v>
       </c>
       <c r="E18">
         <v>7975.859999999999</v>
@@ -2769,37 +2769,37 @@
         <v>4551.6</v>
       </c>
       <c r="M18">
-        <v>1309.058784</v>
+        <v>1250.275488</v>
       </c>
       <c r="N18">
-        <v>3242.541216000001</v>
+        <v>3301.324512</v>
       </c>
       <c r="O18">
-        <v>836.5756337280002</v>
+        <v>851.7417240960001</v>
       </c>
       <c r="P18">
-        <v>2405.965582272001</v>
+        <v>2449.582787904</v>
       </c>
       <c r="Q18">
-        <v>4764.965582272001</v>
+        <v>4808.582787904</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.08984809910964675</v>
+        <v>0.08981978009825914</v>
       </c>
       <c r="T18">
         <v>1.016623096957486</v>
       </c>
       <c r="U18">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V18">
         <v>0.258</v>
       </c>
       <c r="W18">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.477001992295558</v>
+        <v>3.640477673669309</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.0822183379065692</v>
+        <v>0.08186664995252584</v>
       </c>
       <c r="C19">
-        <v>119348.1425979528</v>
+        <v>120558.5457868021</v>
       </c>
       <c r="D19">
-        <v>133130.3625979528</v>
+        <v>134340.7657868021</v>
       </c>
       <c r="E19">
         <v>9388.92</v>
@@ -2851,37 +2851,37 @@
         <v>4551.6</v>
       </c>
       <c r="M19">
-        <v>1390.874958</v>
+        <v>1328.417706</v>
       </c>
       <c r="N19">
-        <v>3160.725042</v>
+        <v>3223.182294</v>
       </c>
       <c r="O19">
-        <v>815.4670608360001</v>
+        <v>831.581031852</v>
       </c>
       <c r="P19">
-        <v>2345.257981164</v>
+        <v>2391.601262148</v>
       </c>
       <c r="Q19">
-        <v>4704.257981164</v>
+        <v>4750.601262148</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09025883362237253</v>
+        <v>0.09023025054521185</v>
       </c>
       <c r="T19">
         <v>1.026102783954084</v>
       </c>
       <c r="U19">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V19">
         <v>0.258</v>
       </c>
       <c r="W19">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.272472463336995</v>
+        <v>3.42633192815935</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08209038456103512</v>
+        <v>0.081719468622514</v>
       </c>
       <c r="C20">
-        <v>118404.4762263924</v>
+        <v>119695.9519641029</v>
       </c>
       <c r="D20">
-        <v>133599.7562263924</v>
+        <v>134891.2319641029</v>
       </c>
       <c r="E20">
         <v>10801.98</v>
@@ -2933,37 +2933,37 @@
         <v>4551.6</v>
       </c>
       <c r="M20">
-        <v>1472.691132</v>
+        <v>1406.559924</v>
       </c>
       <c r="N20">
-        <v>3078.908868</v>
+        <v>3145.040076</v>
       </c>
       <c r="O20">
-        <v>794.3584879440001</v>
+        <v>811.4203396080001</v>
       </c>
       <c r="P20">
-        <v>2284.550380056</v>
+        <v>2333.619736392</v>
       </c>
       <c r="Q20">
-        <v>4643.550380056</v>
+        <v>4692.619736392</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09067958605004284</v>
+        <v>0.09065073246648048</v>
       </c>
       <c r="T20">
         <v>1.035813682828649</v>
       </c>
       <c r="U20">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V20">
         <v>0.258</v>
       </c>
       <c r="W20">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.090668437596052</v>
+        <v>3.23598015437272</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08232897921550106</v>
+        <v>0.08157228729250218</v>
       </c>
       <c r="C21">
-        <v>116118.7888396396</v>
+        <v>118837.8878122876</v>
       </c>
       <c r="D21">
-        <v>132727.1288396396</v>
+        <v>135446.2278122876</v>
       </c>
       <c r="E21">
         <v>12215.04</v>
@@ -3015,45 +3015,45 @@
         <v>4551.6</v>
       </c>
       <c r="M21">
-        <v>1624.31247</v>
+        <v>1484.702142</v>
       </c>
       <c r="N21">
-        <v>2927.287530000001</v>
+        <v>3066.897858</v>
       </c>
       <c r="O21">
-        <v>755.2401827400001</v>
+        <v>791.2596473640001</v>
       </c>
       <c r="P21">
-        <v>2172.047347260001</v>
+        <v>2275.638210636</v>
       </c>
       <c r="Q21">
-        <v>4531.047347260001</v>
+        <v>4634.638210636</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09111072742654452</v>
+        <v>0.09108159665741009</v>
       </c>
       <c r="T21">
         <v>1.045764356984067</v>
       </c>
       <c r="U21">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V21">
         <v>0.258</v>
       </c>
       <c r="W21">
-        <v>0.044891</v>
+        <v>0.0410326</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>2.802170200663423</v>
+        <v>3.065665409405734</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08222031786996697</v>
+        <v>0.08179610596249033</v>
       </c>
       <c r="C22">
-        <v>115101.7250651553</v>
+        <v>116582.6424215831</v>
       </c>
       <c r="D22">
-        <v>133123.1250651554</v>
+        <v>134604.0424215831</v>
       </c>
       <c r="E22">
         <v>13628.1</v>
@@ -3097,37 +3097,37 @@
         <v>4551.6</v>
       </c>
       <c r="M22">
-        <v>1709.8026</v>
+        <v>1633.49736</v>
       </c>
       <c r="N22">
-        <v>2841.7974</v>
+        <v>2918.10264</v>
       </c>
       <c r="O22">
-        <v>733.1837292000001</v>
+        <v>752.87048112</v>
       </c>
       <c r="P22">
-        <v>2108.6136708</v>
+        <v>2165.23215888</v>
       </c>
       <c r="Q22">
-        <v>4467.6136708</v>
+        <v>4524.23215888</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09155264733745871</v>
+        <v>0.0915232324531129</v>
       </c>
       <c r="T22">
         <v>1.05596379799337</v>
       </c>
       <c r="U22">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V22">
         <v>0.258</v>
       </c>
       <c r="W22">
-        <v>0.044891</v>
+        <v>0.0428876</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>2.662061690630252</v>
+        <v>2.786414053341353</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08211165652443292</v>
+        <v>0.08166747463247849</v>
       </c>
       <c r="C23">
-        <v>114087.0313000184</v>
+        <v>115652.3121698878</v>
       </c>
       <c r="D23">
-        <v>133521.4913000184</v>
+        <v>135086.7721698878</v>
       </c>
       <c r="E23">
         <v>15041.16</v>
@@ -3179,37 +3179,37 @@
         <v>4551.6</v>
       </c>
       <c r="M23">
-        <v>1795.29273</v>
+        <v>1715.172228</v>
       </c>
       <c r="N23">
-        <v>2756.30727</v>
+        <v>2836.427772</v>
       </c>
       <c r="O23">
-        <v>711.1272756600001</v>
+        <v>731.7983651760001</v>
       </c>
       <c r="P23">
-        <v>2045.17999434</v>
+        <v>2104.629406824</v>
       </c>
       <c r="Q23">
-        <v>4404.17999434</v>
+        <v>4463.629406824</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09200575509421888</v>
+        <v>0.0919760489018715</v>
       </c>
       <c r="T23">
         <v>1.066421452699111</v>
       </c>
       <c r="U23">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V23">
         <v>0.258</v>
       </c>
       <c r="W23">
-        <v>0.044891</v>
+        <v>0.0428876</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.535296848219287</v>
+        <v>2.653727669848908</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08244374317889884</v>
+        <v>0.08153884330246666</v>
       </c>
       <c r="C24">
-        <v>111463.9228306618</v>
+        <v>114725.4568023141</v>
       </c>
       <c r="D24">
-        <v>132311.4428306618</v>
+        <v>135572.9768023141</v>
       </c>
       <c r="E24">
         <v>16454.22</v>
@@ -3261,45 +3261,45 @@
         <v>4551.6</v>
       </c>
       <c r="M24">
-        <v>1964.718624</v>
+        <v>1796.847096</v>
       </c>
       <c r="N24">
-        <v>2586.881376</v>
+        <v>2754.752904</v>
       </c>
       <c r="O24">
-        <v>667.4153950080001</v>
+        <v>710.726249232</v>
       </c>
       <c r="P24">
-        <v>1919.465980992</v>
+        <v>2044.026654768</v>
       </c>
       <c r="Q24">
-        <v>4278.465980992</v>
+        <v>4403.026654768</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09247048099858825</v>
+        <v>0.0924404760288034</v>
       </c>
       <c r="T24">
         <v>1.077147252397307</v>
       </c>
       <c r="U24">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V24">
         <v>0.258</v>
       </c>
       <c r="W24">
-        <v>0.0468944</v>
+        <v>0.0428876</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.316667610516833</v>
+        <v>2.533103684855776</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08315721783336476</v>
+        <v>0.08200752197245484</v>
       </c>
       <c r="C25">
-        <v>107523.8850086897</v>
+        <v>111557.5083428833</v>
       </c>
       <c r="D25">
-        <v>129784.4650086897</v>
+        <v>133818.0883428833</v>
       </c>
       <c r="E25">
         <v>17867.28</v>
@@ -3343,45 +3343,45 @@
         <v>4551.6</v>
       </c>
       <c r="M25">
-        <v>2206.775802</v>
+        <v>1992.273294</v>
       </c>
       <c r="N25">
-        <v>2344.824198</v>
+        <v>2559.326706</v>
       </c>
       <c r="O25">
-        <v>604.964643084</v>
+        <v>660.3062901480001</v>
       </c>
       <c r="P25">
-        <v>1739.859554916</v>
+        <v>1899.020415852</v>
       </c>
       <c r="Q25">
-        <v>4098.859554916</v>
+        <v>4258.020415852</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09294727770566852</v>
+        <v>0.09291696619799328</v>
       </c>
       <c r="T25">
         <v>1.088151644295457</v>
       </c>
       <c r="U25">
-        <v>0.0679</v>
+        <v>0.0613</v>
       </c>
       <c r="V25">
         <v>0.258</v>
       </c>
       <c r="W25">
-        <v>0.0503818</v>
+        <v>0.0454846</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.062556602204396</v>
+        <v>2.28462631793929</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.0855965844878307</v>
+        <v>0.08240348464244299</v>
       </c>
       <c r="C26">
-        <v>98155.5720571026</v>
+        <v>108696.8548126346</v>
       </c>
       <c r="D26">
-        <v>121829.2120571026</v>
+        <v>132370.4948126346</v>
       </c>
       <c r="E26">
         <v>19280.34</v>
@@ -3425,45 +3425,45 @@
         <v>4551.6</v>
       </c>
       <c r="M26">
-        <v>2777.510736</v>
+        <v>2173.851504</v>
       </c>
       <c r="N26">
-        <v>1774.089264</v>
+        <v>2377.748496</v>
       </c>
       <c r="O26">
-        <v>457.7150301120001</v>
+        <v>613.459111968</v>
       </c>
       <c r="P26">
-        <v>1316.374233888</v>
+        <v>1764.289384032</v>
       </c>
       <c r="Q26">
-        <v>3675.374233888</v>
+        <v>4123.289384032</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09343662169451407</v>
+        <v>0.09340599558216182</v>
       </c>
       <c r="T26">
         <v>1.099445625454084</v>
       </c>
       <c r="U26">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V26">
         <v>0.258</v>
       </c>
       <c r="W26">
-        <v>0.0607698</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>1.63873353971439</v>
+        <v>2.093795271491553</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08564671114229662</v>
+        <v>0.08232159931243116</v>
       </c>
       <c r="C27">
-        <v>96589.25246197984</v>
+        <v>107580.583613115</v>
       </c>
       <c r="D27">
-        <v>121675.9524619798</v>
+        <v>132667.283613115</v>
       </c>
       <c r="E27">
         <v>20693.4</v>
@@ -3507,45 +3507,45 @@
         <v>4551.6</v>
       </c>
       <c r="M27">
-        <v>2893.24035</v>
+        <v>2264.42865</v>
       </c>
       <c r="N27">
-        <v>1658.35965</v>
+        <v>2287.17135</v>
       </c>
       <c r="O27">
-        <v>427.8567897000001</v>
+        <v>590.0902083000001</v>
       </c>
       <c r="P27">
-        <v>1230.5028603</v>
+        <v>1697.0811417</v>
       </c>
       <c r="Q27">
-        <v>3589.5028603</v>
+        <v>4056.0811417</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.0939390148563955</v>
+        <v>0.0939080657499082</v>
       </c>
       <c r="T27">
         <v>1.111040779443607</v>
       </c>
       <c r="U27">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V27">
         <v>0.258</v>
       </c>
       <c r="W27">
-        <v>0.0607698</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>1.573184198125814</v>
+        <v>2.01004346063189</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08569683779676254</v>
+        <v>0.08449687798241931</v>
       </c>
       <c r="C28">
-        <v>95023.31797962252</v>
+        <v>98709.85965428123</v>
       </c>
       <c r="D28">
-        <v>121523.0779796225</v>
+        <v>125209.6196542812</v>
       </c>
       <c r="E28">
         <v>22106.46</v>
@@ -3589,37 +3589,37 @@
         <v>4551.6</v>
       </c>
       <c r="M28">
-        <v>3008.969964</v>
+        <v>2784.858648</v>
       </c>
       <c r="N28">
-        <v>1542.630036</v>
+        <v>1766.741352</v>
       </c>
       <c r="O28">
-        <v>397.9985492880001</v>
+        <v>455.8192688160001</v>
       </c>
       <c r="P28">
-        <v>1144.631486712</v>
+        <v>1310.922083184</v>
       </c>
       <c r="Q28">
-        <v>3503.631486712</v>
+        <v>3669.922083184</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.09445498621184127</v>
+        <v>0.09442370538164771</v>
       </c>
       <c r="T28">
         <v>1.122949315973389</v>
       </c>
       <c r="U28">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V28">
         <v>0.258</v>
       </c>
       <c r="W28">
-        <v>0.0607698</v>
+        <v>0.0562436</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>1.512677113582514</v>
+        <v>1.634409704517255</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.09660993932699152</v>
+        <v>0.08450180665240747</v>
       </c>
       <c r="C29">
-        <v>67509.18984563547</v>
+        <v>97280.85422568244</v>
       </c>
       <c r="D29">
-        <v>95422.00984563546</v>
+        <v>125193.6742256824</v>
       </c>
       <c r="E29">
         <v>23519.52</v>
@@ -3671,45 +3671,45 @@
         <v>4551.6</v>
       </c>
       <c r="M29">
-        <v>4994.177958</v>
+        <v>2891.968596000001</v>
       </c>
       <c r="N29">
-        <v>-442.5779579999999</v>
+        <v>1659.631404</v>
       </c>
       <c r="O29">
-        <v>-114.185113164</v>
+        <v>428.184902232</v>
       </c>
       <c r="P29">
-        <v>-328.3928448359999</v>
+        <v>1231.446501768</v>
       </c>
       <c r="Q29">
-        <v>2030.607155164</v>
+        <v>3590.446501768</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.09531145686685075</v>
+        <v>0.09495347212658559</v>
       </c>
       <c r="T29">
-        <v>1.142716521990192</v>
+        <v>1.135184113777958</v>
       </c>
       <c r="U29">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V29">
-        <v>0.2351363547466123</v>
+        <v>0.258</v>
       </c>
       <c r="W29">
-        <v>0.1001206511636684</v>
+        <v>0.0562436</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y29">
-        <v>0.9113812199481098</v>
+        <v>1.573876011757356</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.09746093932699154</v>
+        <v>0.08450673532239564</v>
       </c>
       <c r="C30">
-        <v>64524.26275540215</v>
+        <v>95851.85285786301</v>
       </c>
       <c r="D30">
-        <v>93850.14275540215</v>
+        <v>125177.732857863</v>
       </c>
       <c r="E30">
         <v>24932.58</v>
@@ -3753,45 +3753,45 @@
         <v>4551.6</v>
       </c>
       <c r="M30">
-        <v>5179.147512</v>
+        <v>2999.078544</v>
       </c>
       <c r="N30">
-        <v>-627.5475119999992</v>
+        <v>1552.521456</v>
       </c>
       <c r="O30">
-        <v>-161.9072580959998</v>
+        <v>400.550535648</v>
       </c>
       <c r="P30">
-        <v>-465.6402539039994</v>
+        <v>1151.970920352</v>
       </c>
       <c r="Q30">
-        <v>1893.359746096001</v>
+        <v>3510.970920352</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.09599911599000147</v>
+        <v>0.09549795461443839</v>
       </c>
       <c r="T30">
-        <v>1.158587584795611</v>
+        <v>1.147758767077099</v>
       </c>
       <c r="U30">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V30">
-        <v>0.2267386277913762</v>
+        <v>0.258</v>
       </c>
       <c r="W30">
-        <v>0.1012199136221088</v>
+        <v>0.0562436</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y30">
-        <v>0.8788318906642489</v>
+        <v>1.517666154194593</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.09831193932699152</v>
+        <v>0.09446775755140904</v>
       </c>
       <c r="C31">
-        <v>61590.28251310228</v>
+        <v>68818.17168464491</v>
       </c>
       <c r="D31">
-        <v>92329.22251310227</v>
+        <v>99557.11168464491</v>
       </c>
       <c r="E31">
         <v>26345.64</v>
@@ -3835,37 +3835,37 @@
         <v>4551.6</v>
       </c>
       <c r="M31">
-        <v>5364.117065999999</v>
+        <v>4860.078564</v>
       </c>
       <c r="N31">
-        <v>-812.5170659999985</v>
+        <v>-308.478564</v>
       </c>
       <c r="O31">
-        <v>-209.6294030279996</v>
+        <v>-79.587469512</v>
       </c>
       <c r="P31">
-        <v>-602.8876629719989</v>
+        <v>-228.891094488</v>
       </c>
       <c r="Q31">
-        <v>1756.112337028001</v>
+        <v>2130.108905512</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.09670614579267753</v>
+        <v>0.09631574892565994</v>
       </c>
       <c r="T31">
-        <v>1.174905719792732</v>
+        <v>1.166645471724248</v>
       </c>
       <c r="U31">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V31">
-        <v>0.2189200544192598</v>
+        <v>0.2416242421878677</v>
       </c>
       <c r="W31">
-        <v>0.1022433648765189</v>
+        <v>0.08994336487651891</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.8485273427103094</v>
+        <v>0.936528070495611</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.09916293932699151</v>
+        <v>0.09519575755140904</v>
       </c>
       <c r="C32">
-        <v>58704.81170984453</v>
+        <v>65937.82823968533</v>
       </c>
       <c r="D32">
-        <v>90856.81170984452</v>
+        <v>98089.82823968532</v>
       </c>
       <c r="E32">
         <v>27758.7</v>
@@ -3917,37 +3917,37 @@
         <v>4551.6</v>
       </c>
       <c r="M32">
-        <v>5549.086619999999</v>
+        <v>5027.66748</v>
       </c>
       <c r="N32">
-        <v>-997.4866199999988</v>
+        <v>-476.0674799999997</v>
       </c>
       <c r="O32">
-        <v>-257.3515479599997</v>
+        <v>-122.8254098399999</v>
       </c>
       <c r="P32">
-        <v>-740.1350720399992</v>
+        <v>-353.2420701599998</v>
       </c>
       <c r="Q32">
-        <v>1618.864927960001</v>
+        <v>2005.75792984</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.09743337644685864</v>
+        <v>0.09703740248174079</v>
       </c>
       <c r="T32">
-        <v>1.191690087218342</v>
+        <v>1.183311835606023</v>
       </c>
       <c r="U32">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V32">
-        <v>0.2116227192719512</v>
+        <v>0.2335701007816054</v>
       </c>
       <c r="W32">
-        <v>0.1031985860473016</v>
+        <v>0.09089858604730161</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.8202430979532991</v>
+        <v>0.9053104681457573</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.127296889232646</v>
+        <v>0.09592375755140904</v>
       </c>
       <c r="C33">
-        <v>25926.61601815846</v>
+        <v>63100.10659325446</v>
       </c>
       <c r="D33">
-        <v>59491.67601815846</v>
+        <v>96665.16659325446</v>
       </c>
       <c r="E33">
         <v>29171.76</v>
@@ -3999,45 +3999,45 @@
         <v>4551.6</v>
       </c>
       <c r="M33">
-        <v>9453.088788000001</v>
+        <v>5195.256396000001</v>
       </c>
       <c r="N33">
-        <v>-4901.488788000001</v>
+        <v>-643.6563960000003</v>
       </c>
       <c r="O33">
-        <v>-1264.584107304</v>
+        <v>-166.0633501680001</v>
       </c>
       <c r="P33">
-        <v>-3636.904680696</v>
+        <v>-477.5930458320003</v>
       </c>
       <c r="Q33">
-        <v>-1277.904680696</v>
+        <v>1881.406954168</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.09957871509921096</v>
+        <v>0.0977799735322008</v>
       </c>
       <c r="T33">
-        <v>1.241204160898298</v>
+        <v>1.200461282498864</v>
       </c>
       <c r="U33">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V33">
-        <v>0.1242253009926981</v>
+        <v>0.2260355814015536</v>
       </c>
       <c r="W33">
-        <v>0.1889921800457758</v>
+        <v>0.09179218004577576</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y33">
-        <v>0.4814934147003803</v>
+        <v>0.8761069046571844</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.128996889232646</v>
+        <v>0.09665175755140903</v>
       </c>
       <c r="C34">
-        <v>23297.93545633601</v>
+        <v>60303.17620866165</v>
       </c>
       <c r="D34">
-        <v>58276.05545633601</v>
+        <v>95281.29620866165</v>
       </c>
       <c r="E34">
         <v>30584.82</v>
@@ -4081,45 +4081,45 @@
         <v>4551.6</v>
       </c>
       <c r="M34">
-        <v>9758.027136000001</v>
+        <v>5362.845312</v>
       </c>
       <c r="N34">
-        <v>-5206.427136</v>
+        <v>-811.245312</v>
       </c>
       <c r="O34">
-        <v>-1343.258201088</v>
+        <v>-209.301290496</v>
       </c>
       <c r="P34">
-        <v>-3863.168934912</v>
+        <v>-601.944021504</v>
       </c>
       <c r="Q34">
-        <v>-1504.168934912</v>
+        <v>1757.055978496</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1003695785565523</v>
+        <v>0.09854438490767435</v>
       </c>
       <c r="T34">
-        <v>1.259457163264449</v>
+        <v>1.218115124888553</v>
       </c>
       <c r="U34">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V34">
-        <v>0.1203432603366763</v>
+        <v>0.2189719694827551</v>
       </c>
       <c r="W34">
-        <v>0.1898299244193453</v>
+        <v>0.09262992441934526</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y34">
-        <v>0.4664467454909935</v>
+        <v>0.8487285638866475</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1306968892326461</v>
+        <v>0.09737975755140904</v>
       </c>
       <c r="C35">
-        <v>20717.93877383532</v>
+        <v>57545.30989446423</v>
       </c>
       <c r="D35">
-        <v>57109.11877383533</v>
+        <v>93936.48989446423</v>
       </c>
       <c r="E35">
         <v>31997.88</v>
@@ -4163,45 +4163,45 @@
         <v>4551.6</v>
       </c>
       <c r="M35">
-        <v>10062.965484</v>
+        <v>5530.434228000001</v>
       </c>
       <c r="N35">
-        <v>-5511.365484000002</v>
+        <v>-978.8342280000006</v>
       </c>
       <c r="O35">
-        <v>-1421.932294872001</v>
+        <v>-252.5392308240002</v>
       </c>
       <c r="P35">
-        <v>-4089.433189128001</v>
+        <v>-726.2949971760005</v>
       </c>
       <c r="Q35">
-        <v>-1730.433189128001</v>
+        <v>1632.705002824</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1011840498782919</v>
+        <v>0.09933161453316203</v>
       </c>
       <c r="T35">
-        <v>1.278255031372874</v>
+        <v>1.236295947648084</v>
       </c>
       <c r="U35">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V35">
-        <v>0.1166964948719285</v>
+        <v>0.2123364552560049</v>
       </c>
       <c r="W35">
-        <v>0.1906168964066378</v>
+        <v>0.09341689640663783</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.45231199562763</v>
+        <v>0.823009516496143</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.132396889232646</v>
+        <v>0.1271620806483054</v>
       </c>
       <c r="C36">
-        <v>18183.75880317801</v>
+        <v>21747.10548403124</v>
       </c>
       <c r="D36">
-        <v>55987.99880317802</v>
+        <v>59551.34548403124</v>
       </c>
       <c r="E36">
         <v>33410.94</v>
@@ -4245,37 +4245,37 @@
         <v>4551.6</v>
       </c>
       <c r="M36">
-        <v>10367.903832</v>
+        <v>9647.243232000001</v>
       </c>
       <c r="N36">
-        <v>-5816.303832000001</v>
+        <v>-5095.643232</v>
       </c>
       <c r="O36">
-        <v>-1500.606388656</v>
+        <v>-1314.675953856</v>
       </c>
       <c r="P36">
-        <v>-4315.697443344001</v>
+        <v>-3780.967278144</v>
       </c>
       <c r="Q36">
-        <v>-1956.697443344001</v>
+        <v>-1421.967278144</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1020232021491751</v>
+        <v>0.101818946718356</v>
       </c>
       <c r="T36">
-        <v>1.29762253184822</v>
+        <v>1.293740108968961</v>
       </c>
       <c r="U36">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.1132642450227542</v>
+        <v>0.1217252195015456</v>
       </c>
       <c r="W36">
-        <v>0.1913575759240897</v>
+        <v>0.1763575759240897</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.4390087016385821</v>
+        <v>0.4718031763625797</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1340968892326461</v>
+        <v>0.1287120806483054</v>
       </c>
       <c r="C37">
-        <v>15692.74918578408</v>
+        <v>19220.76277807934</v>
       </c>
       <c r="D37">
-        <v>54910.04918578408</v>
+        <v>58438.06277807934</v>
       </c>
       <c r="E37">
         <v>34824.00000000001</v>
@@ -4327,37 +4327,37 @@
         <v>4551.6</v>
       </c>
       <c r="M37">
-        <v>10672.84218</v>
+        <v>9930.985680000002</v>
       </c>
       <c r="N37">
-        <v>-6121.242180000001</v>
+        <v>-5379.385680000001</v>
       </c>
       <c r="O37">
-        <v>-1579.28048244</v>
+        <v>-1387.88150544</v>
       </c>
       <c r="P37">
-        <v>-4541.961697560001</v>
+        <v>-3991.504174560001</v>
       </c>
       <c r="Q37">
-        <v>-2182.961697560001</v>
+        <v>-1632.504174560001</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1028881744899316</v>
+        <v>0.1026807766678692</v>
       </c>
       <c r="T37">
-        <v>1.317585955415116</v>
+        <v>1.313643802953099</v>
       </c>
       <c r="U37">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.1100281237363898</v>
+        <v>0.1182473560872157</v>
       </c>
       <c r="W37">
-        <v>0.1920559308976871</v>
+        <v>0.1770559308976871</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.4264655958774797</v>
+        <v>0.4583230856093632</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.135796889232646</v>
+        <v>0.1302620806483054</v>
       </c>
       <c r="C38">
-        <v>13242.46351707764</v>
+        <v>16735.28073246119</v>
       </c>
       <c r="D38">
-        <v>53872.82351707764</v>
+        <v>57365.64073246119</v>
       </c>
       <c r="E38">
         <v>36237.06</v>
@@ -4409,37 +4409,37 @@
         <v>4551.6</v>
       </c>
       <c r="M38">
-        <v>10977.780528</v>
+        <v>10214.728128</v>
       </c>
       <c r="N38">
-        <v>-6426.180527999999</v>
+        <v>-5663.128127999998</v>
       </c>
       <c r="O38">
-        <v>-1657.954576224</v>
+        <v>-1461.087057024</v>
       </c>
       <c r="P38">
-        <v>-4768.225951775999</v>
+        <v>-4202.041070975999</v>
       </c>
       <c r="Q38">
-        <v>-2409.225951775999</v>
+        <v>-1843.041070975999</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1037801772163368</v>
+        <v>0.1035695388033046</v>
       </c>
       <c r="T38">
-        <v>1.338173235968477</v>
+        <v>1.334169487374241</v>
       </c>
       <c r="U38">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.1069717869659345</v>
+        <v>0.1149627073070153</v>
       </c>
       <c r="W38">
-        <v>0.1927154883727513</v>
+        <v>0.1777154883727513</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.4146193293253276</v>
+        <v>0.4455918887868809</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1374968892326461</v>
+        <v>0.1318120806483055</v>
       </c>
       <c r="C39">
-        <v>10830.63681140811</v>
+        <v>14288.45033108129</v>
       </c>
       <c r="D39">
-        <v>52874.05681140812</v>
+        <v>56331.87033108129</v>
       </c>
       <c r="E39">
         <v>37650.12</v>
@@ -4491,37 +4491,37 @@
         <v>4551.6</v>
       </c>
       <c r="M39">
-        <v>11282.718876</v>
+        <v>10498.470576</v>
       </c>
       <c r="N39">
-        <v>-6731.118876</v>
+        <v>-5946.870575999999</v>
       </c>
       <c r="O39">
-        <v>-1736.628670008</v>
+        <v>-1534.292608608</v>
       </c>
       <c r="P39">
-        <v>-4994.490205992</v>
+        <v>-4412.577967392</v>
       </c>
       <c r="Q39">
-        <v>-2635.490205992</v>
+        <v>-2053.577967392</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.104700497489612</v>
+        <v>0.1044865156097063</v>
       </c>
       <c r="T39">
-        <v>1.35941408098385</v>
+        <v>1.355346780824626</v>
       </c>
       <c r="U39">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.1040806575884768</v>
+        <v>0.1118556071095284</v>
       </c>
       <c r="W39">
-        <v>0.1933393940924067</v>
+        <v>0.1783393940924067</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.4034134015057241</v>
+        <v>0.4335488647656138</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1391968892326461</v>
+        <v>0.1333620806483055</v>
       </c>
       <c r="C40">
-        <v>8455.16899121301</v>
+        <v>11878.21897143904</v>
       </c>
       <c r="D40">
-        <v>51911.64899121301</v>
+        <v>55334.69897143904</v>
       </c>
       <c r="E40">
         <v>39063.18</v>
@@ -4573,37 +4573,37 @@
         <v>4551.6</v>
       </c>
       <c r="M40">
-        <v>11587.657224</v>
+        <v>10782.213024</v>
       </c>
       <c r="N40">
-        <v>-7036.057224</v>
+        <v>-6230.613024</v>
       </c>
       <c r="O40">
-        <v>-1815.302763792</v>
+        <v>-1607.498160192</v>
       </c>
       <c r="P40">
-        <v>-5220.754460208</v>
+        <v>-4623.114863808</v>
       </c>
       <c r="Q40">
-        <v>-2861.754460208</v>
+        <v>-2264.114863808</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.105650505513638</v>
+        <v>0.1054330723130887</v>
       </c>
       <c r="T40">
-        <v>1.381340114548105</v>
+        <v>1.37720721277341</v>
       </c>
       <c r="U40">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.1013416929150959</v>
+        <v>0.1089120385013829</v>
       </c>
       <c r="W40">
-        <v>0.1939304626689223</v>
+        <v>0.1789304626689223</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3927972593608366</v>
+        <v>0.4221396841138871</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.140896889232646</v>
+        <v>0.1349120806483055</v>
       </c>
       <c r="C41">
-        <v>6114.110147116597</v>
+        <v>9502.676861474283</v>
       </c>
       <c r="D41">
-        <v>50983.6501471166</v>
+        <v>54372.21686147428</v>
       </c>
       <c r="E41">
         <v>40476.24000000001</v>
@@ -4655,37 +4655,37 @@
         <v>4551.6</v>
       </c>
       <c r="M41">
-        <v>11892.595572</v>
+        <v>11065.955472</v>
       </c>
       <c r="N41">
-        <v>-7340.995572000002</v>
+        <v>-6514.355472000001</v>
       </c>
       <c r="O41">
-        <v>-1893.976857576</v>
+        <v>-1680.703711776</v>
       </c>
       <c r="P41">
-        <v>-5447.018714424001</v>
+        <v>-4833.651760224001</v>
       </c>
       <c r="Q41">
-        <v>-3088.018714424001</v>
+        <v>-2474.651760224001</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1066316613417304</v>
+        <v>0.1064106636624835</v>
       </c>
       <c r="T41">
-        <v>1.40398503445873</v>
+        <v>1.399784380195925</v>
       </c>
       <c r="U41">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.09874318796855493</v>
+        <v>0.1061194221295526</v>
       </c>
       <c r="W41">
-        <v>0.1944912200363859</v>
+        <v>0.1794912200363859</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3827255347618408</v>
+        <v>0.4113155896494285</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1425968892326461</v>
+        <v>0.1364620806483055</v>
       </c>
       <c r="C42">
-        <v>3805.647351250016</v>
+        <v>7160.044811807667</v>
       </c>
       <c r="D42">
-        <v>50088.24735125001</v>
+        <v>53442.64481180767</v>
       </c>
       <c r="E42">
         <v>41889.3</v>
@@ -4737,37 +4737,37 @@
         <v>4551.6</v>
       </c>
       <c r="M42">
-        <v>12197.53392</v>
+        <v>11349.69792</v>
       </c>
       <c r="N42">
-        <v>-7645.933920000001</v>
+        <v>-6798.09792</v>
       </c>
       <c r="O42">
-        <v>-1972.65095136</v>
+        <v>-1753.90926336</v>
       </c>
       <c r="P42">
-        <v>-5673.282968640001</v>
+        <v>-5044.18865664</v>
       </c>
       <c r="Q42">
-        <v>-3314.282968640001</v>
+        <v>-2685.18865664</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1076455223640926</v>
+        <v>0.1074208413901916</v>
       </c>
       <c r="T42">
-        <v>1.427384785033042</v>
+        <v>1.423114119865857</v>
       </c>
       <c r="U42">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.09627460826934105</v>
+        <v>0.1034664365763137</v>
       </c>
       <c r="W42">
-        <v>0.1950239395354762</v>
+        <v>0.1800239395354762</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3731573963927948</v>
+        <v>0.4010326999081928</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1442968892326461</v>
+        <v>0.1380120806483054</v>
       </c>
       <c r="C43">
-        <v>1528.092836138938</v>
+        <v>4848.663259187728</v>
       </c>
       <c r="D43">
-        <v>49223.75283613895</v>
+        <v>52544.32325918773</v>
       </c>
       <c r="E43">
         <v>43302.36000000001</v>
@@ -4819,37 +4819,37 @@
         <v>4551.6</v>
       </c>
       <c r="M43">
-        <v>12502.472268</v>
+        <v>11633.440368</v>
       </c>
       <c r="N43">
-        <v>-7950.872268000003</v>
+        <v>-7081.840368000001</v>
       </c>
       <c r="O43">
-        <v>-2051.325045144001</v>
+        <v>-1827.114814944</v>
       </c>
       <c r="P43">
-        <v>-5899.547222856002</v>
+        <v>-5254.725553056001</v>
       </c>
       <c r="Q43">
-        <v>-3540.547222856002</v>
+        <v>-2895.725553056001</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1086937515567044</v>
+        <v>0.1084652624307033</v>
       </c>
       <c r="T43">
-        <v>1.451577747491229</v>
+        <v>1.447234698168668</v>
       </c>
       <c r="U43">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.09392644709204004</v>
+        <v>0.1009428649525012</v>
       </c>
       <c r="W43">
-        <v>0.1955306727175378</v>
+        <v>0.1805306727175378</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3640559964807754</v>
+        <v>0.3912514145445783</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1459968892326461</v>
+        <v>0.1395620806483054</v>
       </c>
       <c r="C44">
-        <v>-720.1266230248948</v>
+        <v>2566.982378671753</v>
       </c>
       <c r="D44">
-        <v>48388.5933769751</v>
+        <v>51675.70237867175</v>
       </c>
       <c r="E44">
         <v>44715.42</v>
@@ -4901,37 +4901,37 @@
         <v>4551.6</v>
       </c>
       <c r="M44">
-        <v>12807.410616</v>
+        <v>11917.182816</v>
       </c>
       <c r="N44">
-        <v>-8255.810616000001</v>
+        <v>-7365.582816</v>
       </c>
       <c r="O44">
-        <v>-2129.999138928</v>
+        <v>-1900.320366528</v>
       </c>
       <c r="P44">
-        <v>-6125.811477072</v>
+        <v>-5465.262449472</v>
       </c>
       <c r="Q44">
-        <v>-3766.811477072</v>
+        <v>-3106.262449472</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1097781265835441</v>
+        <v>0.1095456979898534</v>
       </c>
       <c r="T44">
-        <v>1.476604950034182</v>
+        <v>1.472187020550886</v>
       </c>
       <c r="U44">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.09169010311365815</v>
+        <v>0.09853946340601309</v>
       </c>
       <c r="W44">
-        <v>0.1960132757480726</v>
+        <v>0.1810132757480726</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3553879965645664</v>
+        <v>0.3819359046744694</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1476968892326461</v>
+        <v>0.1411120806483054</v>
       </c>
       <c r="C45">
-        <v>-2940.479263264817</v>
+        <v>313.5531606027944</v>
       </c>
       <c r="D45">
-        <v>47581.30073673518</v>
+        <v>50835.3331606028</v>
       </c>
       <c r="E45">
         <v>46128.48</v>
@@ -4983,37 +4983,37 @@
         <v>4551.6</v>
       </c>
       <c r="M45">
-        <v>13112.348964</v>
+        <v>12200.925264</v>
       </c>
       <c r="N45">
-        <v>-8560.748964</v>
+        <v>-7649.325264000001</v>
       </c>
       <c r="O45">
-        <v>-2208.673232712</v>
+        <v>-1973.525918112</v>
       </c>
       <c r="P45">
-        <v>-6352.075731288</v>
+        <v>-5675.799345888001</v>
       </c>
       <c r="Q45">
-        <v>-3993.075731288</v>
+        <v>-3316.799345888001</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1109005498569396</v>
+        <v>0.1106640435686227</v>
       </c>
       <c r="T45">
-        <v>1.502510300034781</v>
+        <v>1.498014863016692</v>
       </c>
       <c r="U45">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.08955777513427075</v>
+        <v>0.09624784797796626</v>
       </c>
       <c r="W45">
-        <v>0.1964734321260244</v>
+        <v>0.1814734321260244</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3471231594351579</v>
+        <v>0.3730536743332026</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.149396889232646</v>
+        <v>0.1426620806483054</v>
       </c>
       <c r="C46">
-        <v>-5134.336947940465</v>
+        <v>-1912.980655688923</v>
       </c>
       <c r="D46">
-        <v>46800.50305205954</v>
+        <v>50021.85934431108</v>
       </c>
       <c r="E46">
         <v>47541.54</v>
@@ -5065,37 +5065,37 @@
         <v>4551.6</v>
       </c>
       <c r="M46">
-        <v>13417.287312</v>
+        <v>12484.667712</v>
       </c>
       <c r="N46">
-        <v>-8865.687312</v>
+        <v>-7933.067712</v>
       </c>
       <c r="O46">
-        <v>-2287.347326496</v>
+        <v>-2046.731469696</v>
       </c>
       <c r="P46">
-        <v>-6578.339985504</v>
+        <v>-5886.336242304</v>
       </c>
       <c r="Q46">
-        <v>-4219.339985504</v>
+        <v>-3527.336242304</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1120630596758135</v>
+        <v>0.1118223300609196</v>
       </c>
       <c r="T46">
-        <v>1.529340841106831</v>
+        <v>1.524765128427704</v>
       </c>
       <c r="U46">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.08752237115394641</v>
+        <v>0.09406039688755796</v>
       </c>
       <c r="W46">
-        <v>0.1969126723049784</v>
+        <v>0.1819126723049784</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3392339967207225</v>
+        <v>0.3645751817347207</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1510968892326461</v>
+        <v>0.1442120806483054</v>
       </c>
       <c r="C47">
-        <v>-7302.982946428201</v>
+        <v>-4113.889885914679</v>
       </c>
       <c r="D47">
-        <v>46044.9170535718</v>
+        <v>49234.01011408532</v>
       </c>
       <c r="E47">
         <v>48954.60000000001</v>
@@ -5147,37 +5147,37 @@
         <v>4551.6</v>
       </c>
       <c r="M47">
-        <v>13722.22566</v>
+        <v>12768.41016</v>
       </c>
       <c r="N47">
-        <v>-9170.625660000002</v>
+        <v>-8216.810160000001</v>
       </c>
       <c r="O47">
-        <v>-2366.02142028</v>
+        <v>-2119.93702128</v>
       </c>
       <c r="P47">
-        <v>-6804.604239720002</v>
+        <v>-6096.87313872</v>
       </c>
       <c r="Q47">
-        <v>-4445.604239720002</v>
+        <v>-3737.87313872</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1132678425790101</v>
+        <v>0.1130227360620272</v>
       </c>
       <c r="T47">
-        <v>1.557147038217864</v>
+        <v>1.552488130762753</v>
       </c>
       <c r="U47">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.08557742957274761</v>
+        <v>0.09197016584561221</v>
       </c>
       <c r="W47">
-        <v>0.1973323906982011</v>
+        <v>0.1823323906982011</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.331695463460262</v>
+        <v>0.3564735110295048</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1527968892326461</v>
+        <v>0.1457620806483055</v>
       </c>
       <c r="C48">
-        <v>-9447.618972165503</v>
+        <v>-6290.366525323414</v>
       </c>
       <c r="D48">
-        <v>45313.3410278345</v>
+        <v>48470.59347467659</v>
       </c>
       <c r="E48">
         <v>50367.66</v>
@@ -5229,37 +5229,37 @@
         <v>4551.6</v>
       </c>
       <c r="M48">
-        <v>14027.164008</v>
+        <v>13052.152608</v>
       </c>
       <c r="N48">
-        <v>-9475.564008000001</v>
+        <v>-8500.552608</v>
       </c>
       <c r="O48">
-        <v>-2444.695514064</v>
+        <v>-2193.142572864</v>
       </c>
       <c r="P48">
-        <v>-7030.868493936001</v>
+        <v>-6307.410035135999</v>
       </c>
       <c r="Q48">
-        <v>-4671.868493936001</v>
+        <v>-3948.410035135999</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.114517247071214</v>
+        <v>0.1142676015446573</v>
       </c>
       <c r="T48">
-        <v>1.585983094481158</v>
+        <v>1.581237910962063</v>
       </c>
       <c r="U48">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.08371705066899222</v>
+        <v>0.08997081441418588</v>
       </c>
       <c r="W48">
-        <v>0.1977338604656315</v>
+        <v>0.1827338604656315</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3244846925154737</v>
+        <v>0.3487240868766894</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1544968892326461</v>
+        <v>0.1473120806483054</v>
       </c>
       <c r="C49">
-        <v>-11569.37156025277</v>
+        <v>-8443.529766296648</v>
       </c>
       <c r="D49">
-        <v>44604.64843974724</v>
+        <v>47730.49023370336</v>
       </c>
       <c r="E49">
         <v>51780.72000000001</v>
@@ -5311,37 +5311,37 @@
         <v>4551.6</v>
       </c>
       <c r="M49">
-        <v>14332.102356</v>
+        <v>13335.895056</v>
       </c>
       <c r="N49">
-        <v>-9780.502356000003</v>
+        <v>-8784.295056000001</v>
       </c>
       <c r="O49">
-        <v>-2523.369607848001</v>
+        <v>-2266.348124448</v>
       </c>
       <c r="P49">
-        <v>-7257.132748152002</v>
+        <v>-6517.946931552</v>
       </c>
       <c r="Q49">
-        <v>-4898.132748152002</v>
+        <v>-4158.946931552</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1158137989027463</v>
+        <v>0.1155594430832358</v>
       </c>
       <c r="T49">
-        <v>1.615907303810991</v>
+        <v>1.611072588527385</v>
       </c>
       <c r="U49">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.0819358368249711</v>
+        <v>0.08805654176707553</v>
       </c>
       <c r="W49">
-        <v>0.1981182464131713</v>
+        <v>0.1831182464131712</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3175807628874848</v>
+        <v>0.3413044254537811</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.156196889232646</v>
+        <v>0.1488620806483054</v>
       </c>
       <c r="C50">
-        <v>-13669.29785580366</v>
+        <v>-10574.43147293461</v>
       </c>
       <c r="D50">
-        <v>43917.78214419635</v>
+        <v>47012.6485270654</v>
       </c>
       <c r="E50">
         <v>53193.78000000001</v>
@@ -5393,37 +5393,37 @@
         <v>4551.6</v>
       </c>
       <c r="M50">
-        <v>14637.040704</v>
+        <v>13619.637504</v>
       </c>
       <c r="N50">
-        <v>-10085.440704</v>
+        <v>-9068.037504000002</v>
       </c>
       <c r="O50">
-        <v>-2602.043701632001</v>
+        <v>-2339.553676032001</v>
       </c>
       <c r="P50">
-        <v>-7483.397002368001</v>
+        <v>-6728.483827968001</v>
       </c>
       <c r="Q50">
-        <v>-5124.397002368001</v>
+        <v>-4369.483827968001</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1171602181124145</v>
+        <v>0.1169009708348364</v>
       </c>
       <c r="T50">
-        <v>1.646982444268895</v>
+        <v>1.642054753691373</v>
       </c>
       <c r="U50">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.08022884022445088</v>
+        <v>0.08622203048026145</v>
       </c>
       <c r="W50">
-        <v>0.1984866162795635</v>
+        <v>0.1834866162795635</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3109644969939956</v>
+        <v>0.3341939165901606</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1578968892326461</v>
+        <v>0.1504120806483054</v>
       </c>
       <c r="C51">
-        <v>-15748.39087559767</v>
+        <v>-12684.06116895213</v>
       </c>
       <c r="D51">
-        <v>43251.74912440233</v>
+        <v>46316.07883104787</v>
       </c>
       <c r="E51">
         <v>54606.84</v>
@@ -5475,37 +5475,37 @@
         <v>4551.6</v>
       </c>
       <c r="M51">
-        <v>14941.979052</v>
+        <v>13903.379952</v>
       </c>
       <c r="N51">
-        <v>-10390.379052</v>
+        <v>-9351.779952000001</v>
       </c>
       <c r="O51">
-        <v>-2680.717795416001</v>
+        <v>-2412.759227616</v>
       </c>
       <c r="P51">
-        <v>-7709.661256584001</v>
+        <v>-6939.020724384</v>
       </c>
       <c r="Q51">
-        <v>-5350.661256584001</v>
+        <v>-4580.020724384</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1185594380754031</v>
+        <v>0.1182951075178724</v>
       </c>
       <c r="T51">
-        <v>1.679276217685932</v>
+        <v>1.674251905724538</v>
       </c>
       <c r="U51">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.07859151695456412</v>
+        <v>0.08446239720515408</v>
       </c>
       <c r="W51">
-        <v>0.1988399506412051</v>
+        <v>0.1838399506412051</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3046182827696283</v>
+        <v>0.3273736325781166</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.159596889232646</v>
+        <v>0.1519620806483054</v>
       </c>
       <c r="C52">
-        <v>-17807.58429811295</v>
+        <v>-14773.35058862554</v>
       </c>
       <c r="D52">
-        <v>42605.61570188704</v>
+        <v>45639.84941137446</v>
       </c>
       <c r="E52">
         <v>56019.9</v>
@@ -5557,37 +5557,37 @@
         <v>4551.6</v>
       </c>
       <c r="M52">
-        <v>15246.9174</v>
+        <v>14187.1224</v>
       </c>
       <c r="N52">
-        <v>-10695.3174</v>
+        <v>-9635.5224</v>
       </c>
       <c r="O52">
-        <v>-2759.391889200001</v>
+        <v>-2485.9647792</v>
       </c>
       <c r="P52">
-        <v>-7935.925510800002</v>
+        <v>-7149.5576208</v>
       </c>
       <c r="Q52">
-        <v>-5576.925510800002</v>
+        <v>-4790.5576208</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1200146268369111</v>
+        <v>0.1197450096682299</v>
       </c>
       <c r="T52">
-        <v>1.712861742039651</v>
+        <v>1.707736943839028</v>
       </c>
       <c r="U52">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.07701968661547284</v>
+        <v>0.082773149261051</v>
       </c>
       <c r="W52">
-        <v>0.199179151628381</v>
+        <v>0.1841791516283809</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2985259171142358</v>
+        <v>0.3208261599265543</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.161296889232646</v>
+        <v>0.1535120806483055</v>
       </c>
       <c r="C53">
-        <v>-19847.75683053202</v>
+        <v>-16843.17783480485</v>
       </c>
       <c r="D53">
-        <v>41978.50316946798</v>
+        <v>44983.08216519515</v>
       </c>
       <c r="E53">
         <v>57432.96</v>
@@ -5639,37 +5639,37 @@
         <v>4551.6</v>
       </c>
       <c r="M53">
-        <v>15551.855748</v>
+        <v>14470.864848</v>
       </c>
       <c r="N53">
-        <v>-11000.255748</v>
+        <v>-9919.264847999999</v>
       </c>
       <c r="O53">
-        <v>-2838.065982984001</v>
+        <v>-2559.170330784</v>
       </c>
       <c r="P53">
-        <v>-8162.189765016001</v>
+        <v>-7360.094517215999</v>
       </c>
       <c r="Q53">
-        <v>-5803.189765016001</v>
+        <v>-5001.094517215999</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1215292110580726</v>
+        <v>0.1212540914981938</v>
       </c>
       <c r="T53">
-        <v>1.747818104122093</v>
+        <v>1.74258871820309</v>
       </c>
       <c r="U53">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.07550949668183611</v>
+        <v>0.08115014633436372</v>
       </c>
       <c r="W53">
-        <v>0.1995050506160598</v>
+        <v>0.1845050506160598</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2926724677590548</v>
+        <v>0.3145354509083865</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1629968892326461</v>
+        <v>0.1550620806483054</v>
       </c>
       <c r="C54">
-        <v>-21869.73619567347</v>
+        <v>-18894.37118301079</v>
       </c>
       <c r="D54">
-        <v>41369.58380432653</v>
+        <v>44344.94881698921</v>
       </c>
       <c r="E54">
         <v>58846.02</v>
@@ -5721,37 +5721,37 @@
         <v>4551.6</v>
       </c>
       <c r="M54">
-        <v>15856.794096</v>
+        <v>14754.607296</v>
       </c>
       <c r="N54">
-        <v>-11305.194096</v>
+        <v>-10203.007296</v>
       </c>
       <c r="O54">
-        <v>-2916.740076768</v>
+        <v>-2632.375882368</v>
       </c>
       <c r="P54">
-        <v>-8388.454019231998</v>
+        <v>-7570.631413632</v>
       </c>
       <c r="Q54">
-        <v>-6029.454019231998</v>
+        <v>-5211.631413632</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1231069029551158</v>
+        <v>0.1228260517377395</v>
       </c>
       <c r="T54">
-        <v>1.784230981291303</v>
+        <v>1.778892649832321</v>
       </c>
       <c r="U54">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.07405739097641621</v>
+        <v>0.07958956659716443</v>
       </c>
       <c r="W54">
-        <v>0.1998184150272894</v>
+        <v>0.1848184150272894</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2870441510713806</v>
+        <v>0.3084866922370714</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1646968892326461</v>
+        <v>0.1566120806483055</v>
       </c>
       <c r="C55">
-        <v>-23874.30277689062</v>
+        <v>-20927.71256626977</v>
       </c>
       <c r="D55">
-        <v>40778.07722310939</v>
+        <v>43724.66743373024</v>
       </c>
       <c r="E55">
         <v>60259.08000000001</v>
@@ -5803,37 +5803,37 @@
         <v>4551.6</v>
       </c>
       <c r="M55">
-        <v>16161.732444</v>
+        <v>15038.349744</v>
       </c>
       <c r="N55">
-        <v>-11610.132444</v>
+        <v>-10486.749744</v>
       </c>
       <c r="O55">
-        <v>-2995.414170552001</v>
+        <v>-2705.581433952001</v>
       </c>
       <c r="P55">
-        <v>-8614.718273448001</v>
+        <v>-7781.168310048002</v>
       </c>
       <c r="Q55">
-        <v>-6255.718273448001</v>
+        <v>-5422.168310048002</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.124751730677565</v>
+        <v>0.1244649039023722</v>
       </c>
       <c r="T55">
-        <v>1.822193342595373</v>
+        <v>1.816741429615988</v>
       </c>
       <c r="U55">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.07266008171271023</v>
+        <v>0.07808787666136886</v>
       </c>
       <c r="W55">
-        <v>0.2001199543663972</v>
+        <v>0.1851199543663971</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2816282236926753</v>
+        <v>0.3026661886099568</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.166396889232646</v>
+        <v>0.1581620806483054</v>
       </c>
       <c r="C56">
-        <v>-25862.19295468694</v>
+        <v>-22943.9407715152</v>
       </c>
       <c r="D56">
-        <v>40203.24704531307</v>
+        <v>43121.4992284848</v>
       </c>
       <c r="E56">
         <v>61672.14000000001</v>
@@ -5885,37 +5885,37 @@
         <v>4551.6</v>
       </c>
       <c r="M56">
-        <v>16466.670792</v>
+        <v>15322.092192</v>
       </c>
       <c r="N56">
-        <v>-11915.070792</v>
+        <v>-10770.492192</v>
       </c>
       <c r="O56">
-        <v>-3074.088264336001</v>
+        <v>-2778.786985536</v>
       </c>
       <c r="P56">
-        <v>-8840.982527664004</v>
+        <v>-7991.705206464001</v>
       </c>
       <c r="Q56">
-        <v>-6481.982527664004</v>
+        <v>-5632.705206464001</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1264680726488164</v>
+        <v>0.1261750105089456</v>
       </c>
       <c r="T56">
-        <v>1.861806241347446</v>
+        <v>1.856235808520683</v>
       </c>
       <c r="U56">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.07131452464395632</v>
+        <v>0.07664180487134352</v>
       </c>
       <c r="W56">
-        <v>0.2004103255818342</v>
+        <v>0.1854103255818342</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.276412886216885</v>
+        <v>0.2970612591912539</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1680968892326461</v>
+        <v>0.1597120806483054</v>
       </c>
       <c r="C57">
-        <v>-27834.10216504599</v>
+        <v>-24943.75437502902</v>
       </c>
       <c r="D57">
-        <v>39644.39783495402</v>
+        <v>42534.74562497098</v>
       </c>
       <c r="E57">
         <v>63085.2</v>
@@ -5967,37 +5967,37 @@
         <v>4551.6</v>
       </c>
       <c r="M57">
-        <v>16771.60914</v>
+        <v>15605.83464</v>
       </c>
       <c r="N57">
-        <v>-12220.00914</v>
+        <v>-11054.23464</v>
       </c>
       <c r="O57">
-        <v>-3152.76235812</v>
+        <v>-2851.99253712</v>
       </c>
       <c r="P57">
-        <v>-9067.24678188</v>
+        <v>-8202.24210288</v>
       </c>
       <c r="Q57">
-        <v>-6708.24678188</v>
+        <v>-5843.24210288</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1282606964854568</v>
+        <v>0.1279611218535888</v>
       </c>
       <c r="T57">
-        <v>1.90317971337739</v>
+        <v>1.897485493154476</v>
       </c>
       <c r="U57">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.07001789692315713</v>
+        <v>0.07524831751004636</v>
       </c>
       <c r="W57">
-        <v>0.2006901378439827</v>
+        <v>0.1856901378439827</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.271387197376578</v>
+        <v>0.2916601453877766</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.169796889232646</v>
+        <v>0.1612620806483054</v>
       </c>
       <c r="C58">
-        <v>-29790.68770618252</v>
+        <v>-26927.81444144496</v>
       </c>
       <c r="D58">
-        <v>39100.87229381748</v>
+        <v>41963.74555855504</v>
       </c>
       <c r="E58">
         <v>64498.26</v>
@@ -6049,37 +6049,37 @@
         <v>4551.6</v>
       </c>
       <c r="M58">
-        <v>17076.547488</v>
+        <v>15889.577088</v>
       </c>
       <c r="N58">
-        <v>-12524.947488</v>
+        <v>-11337.977088</v>
       </c>
       <c r="O58">
-        <v>-3231.436451904</v>
+        <v>-2925.198088704</v>
       </c>
       <c r="P58">
-        <v>-9293.511036095999</v>
+        <v>-8412.778999295999</v>
       </c>
       <c r="Q58">
-        <v>-6934.511036095999</v>
+        <v>-6053.778999295999</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1301348032237626</v>
+        <v>0.129828420077534</v>
       </c>
       <c r="T58">
-        <v>1.94643379777233</v>
+        <v>1.940610163453442</v>
       </c>
       <c r="U58">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.06876757733524361</v>
+        <v>0.07390459755450983</v>
       </c>
       <c r="W58">
-        <v>0.2009599568110544</v>
+        <v>0.1859599568110544</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2665409974234249</v>
+        <v>0.286451928505852</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1714968892326461</v>
+        <v>0.1628120806483055</v>
       </c>
       <c r="C59">
-        <v>-31732.57131753271</v>
+        <v>-28896.74700823797</v>
       </c>
       <c r="D59">
-        <v>38572.04868246731</v>
+        <v>41407.87299176204</v>
       </c>
       <c r="E59">
         <v>65911.32000000001</v>
@@ -6131,37 +6131,37 @@
         <v>4551.6</v>
       </c>
       <c r="M59">
-        <v>17381.485836</v>
+        <v>16173.319536</v>
       </c>
       <c r="N59">
-        <v>-12829.885836</v>
+        <v>-11621.719536</v>
       </c>
       <c r="O59">
-        <v>-3310.110545688001</v>
+        <v>-2998.403640288001</v>
       </c>
       <c r="P59">
-        <v>-9519.775290312002</v>
+        <v>-8623.315895712001</v>
       </c>
       <c r="Q59">
-        <v>-7160.775290312002</v>
+        <v>-6264.315895712001</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1320960777173385</v>
+        <v>0.1317825693816627</v>
       </c>
       <c r="T59">
-        <v>1.991699700046106</v>
+        <v>1.985740632370964</v>
       </c>
       <c r="U59">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.0675611286100639</v>
+        <v>0.07260802566758859</v>
       </c>
       <c r="W59">
-        <v>0.2012203084459482</v>
+        <v>0.1862203084459482</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2618648395738911</v>
+        <v>0.2814264560759248</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.173196889232646</v>
+        <v>0.1643620806483054</v>
       </c>
       <c r="C60">
-        <v>-33660.34155225787</v>
+        <v>-30851.14537533034</v>
       </c>
       <c r="D60">
-        <v>38057.33844774213</v>
+        <v>40866.53462466966</v>
       </c>
       <c r="E60">
         <v>67324.37999999999</v>
@@ -6213,37 +6213,37 @@
         <v>4551.6</v>
       </c>
       <c r="M60">
-        <v>17686.424184</v>
+        <v>16457.061984</v>
       </c>
       <c r="N60">
-        <v>-13134.824184</v>
+        <v>-11905.461984</v>
       </c>
       <c r="O60">
-        <v>-3388.784639472</v>
+        <v>-3071.609191872</v>
       </c>
       <c r="P60">
-        <v>-9746.039544527999</v>
+        <v>-8833.852792128</v>
       </c>
       <c r="Q60">
-        <v>-7387.039544527999</v>
+        <v>-6474.852792128</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.134150746234418</v>
+        <v>0.1338297734145594</v>
       </c>
       <c r="T60">
-        <v>2.039121121475775</v>
+        <v>2.033020171236938</v>
       </c>
       <c r="U60">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.0663962815650628</v>
+        <v>0.07135616315607844</v>
       </c>
       <c r="W60">
-        <v>0.2014716824382595</v>
+        <v>0.1864716824382595</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2573499285467551</v>
+        <v>0.2765742757987537</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1748968892326461</v>
+        <v>0.1659120806483054</v>
       </c>
       <c r="C61">
-        <v>-35574.55596229613</v>
+        <v>-32791.57221741935</v>
       </c>
       <c r="D61">
-        <v>37556.18403770386</v>
+        <v>40339.16778258065</v>
       </c>
       <c r="E61">
         <v>68737.43999999999</v>
@@ -6295,37 +6295,37 @@
         <v>4551.6</v>
       </c>
       <c r="M61">
-        <v>17991.362532</v>
+        <v>16740.804432</v>
       </c>
       <c r="N61">
-        <v>-13439.762532</v>
+        <v>-12189.204432</v>
       </c>
       <c r="O61">
-        <v>-3467.458733256</v>
+        <v>-3144.814743456</v>
       </c>
       <c r="P61">
-        <v>-9972.303798743998</v>
+        <v>-9044.389688544001</v>
       </c>
       <c r="Q61">
-        <v>-7613.303798743998</v>
+        <v>-6685.389688544001</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.136305642484038</v>
+        <v>0.1359768410588169</v>
       </c>
       <c r="T61">
-        <v>2.088855782975184</v>
+        <v>2.082606029071985</v>
       </c>
       <c r="U61">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.06527092086057022</v>
+        <v>0.07014673666190763</v>
       </c>
       <c r="W61">
-        <v>0.201714535278289</v>
+        <v>0.186714535278289</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2529880653510473</v>
+        <v>0.2718865762089443</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.176596889232646</v>
+        <v>0.1674620806483054</v>
       </c>
       <c r="C62">
-        <v>-37475.74311301556</v>
+        <v>-34718.56153483539</v>
       </c>
       <c r="D62">
-        <v>37068.05688698444</v>
+        <v>39825.2384651646</v>
       </c>
       <c r="E62">
         <v>70150.49999999999</v>
@@ -6377,37 +6377,37 @@
         <v>4551.6</v>
       </c>
       <c r="M62">
-        <v>18296.30088</v>
+        <v>17024.54688</v>
       </c>
       <c r="N62">
-        <v>-13744.70088</v>
+        <v>-12472.94688</v>
       </c>
       <c r="O62">
-        <v>-3546.13282704</v>
+        <v>-3218.020295039999</v>
       </c>
       <c r="P62">
-        <v>-10198.56805296</v>
+        <v>-9254.926584959998</v>
       </c>
       <c r="Q62">
-        <v>-7839.568052959999</v>
+        <v>-6895.926584959998</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1385682835461389</v>
+        <v>0.1382312620852874</v>
       </c>
       <c r="T62">
-        <v>2.141077177549563</v>
+        <v>2.134671179798786</v>
       </c>
       <c r="U62">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.06418307217956072</v>
+        <v>0.06897762438420917</v>
       </c>
       <c r="W62">
-        <v>0.2019492930236508</v>
+        <v>0.1869492930236508</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2487715975951965</v>
+        <v>0.2673551332721286</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1782968892326461</v>
+        <v>0.1690120806483054</v>
       </c>
       <c r="C63">
-        <v>-39364.40444277378</v>
+        <v>-36632.62045715055</v>
       </c>
       <c r="D63">
-        <v>36592.45555722622</v>
+        <v>39324.23954284946</v>
       </c>
       <c r="E63">
         <v>71563.56</v>
@@ -6459,37 +6459,37 @@
         <v>4551.6</v>
       </c>
       <c r="M63">
-        <v>18601.239228</v>
+        <v>17308.289328</v>
       </c>
       <c r="N63">
-        <v>-14049.639228</v>
+        <v>-12756.689328</v>
       </c>
       <c r="O63">
-        <v>-3624.806920824</v>
+        <v>-3291.225846624</v>
       </c>
       <c r="P63">
-        <v>-10424.832307176</v>
+        <v>-9465.463481376002</v>
       </c>
       <c r="Q63">
-        <v>-8065.832307176002</v>
+        <v>-7106.463481376002</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1409469574832194</v>
+        <v>0.1406012944464486</v>
       </c>
       <c r="T63">
-        <v>2.195976592358527</v>
+        <v>2.189406338255165</v>
       </c>
       <c r="U63">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.06313089066842036</v>
+        <v>0.06784684365659918</v>
       </c>
       <c r="W63">
-        <v>0.2021763537937549</v>
+        <v>0.1871763537937549</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2446933746837998</v>
+        <v>0.2629722622348805</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1799968892326461</v>
+        <v>0.1705620806483054</v>
       </c>
       <c r="C64">
-        <v>-41241.01598113652</v>
+        <v>-38534.23091234242</v>
       </c>
       <c r="D64">
-        <v>36128.90401886348</v>
+        <v>38835.68908765758</v>
       </c>
       <c r="E64">
         <v>72976.62</v>
@@ -6541,37 +6541,37 @@
         <v>4551.6</v>
       </c>
       <c r="M64">
-        <v>18906.177576</v>
+        <v>17592.031776</v>
       </c>
       <c r="N64">
-        <v>-14354.577576</v>
+        <v>-13040.431776</v>
       </c>
       <c r="O64">
-        <v>-3703.481014608</v>
+        <v>-3364.431398208</v>
       </c>
       <c r="P64">
-        <v>-10651.096561392</v>
+        <v>-9676.000377791999</v>
       </c>
       <c r="Q64">
-        <v>-8292.096561392002</v>
+        <v>-7317.000377791999</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1434508247854094</v>
+        <v>0.1430960653529341</v>
       </c>
       <c r="T64">
-        <v>2.253765450052172</v>
+        <v>2.247022294525038</v>
       </c>
       <c r="U64">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.06211265049634907</v>
+        <v>0.06675253972665403</v>
       </c>
       <c r="W64">
-        <v>0.2023960900228879</v>
+        <v>0.1873960900228879</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2407467073501902</v>
+        <v>0.258730774134318</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.181696889232646</v>
+        <v>0.1721120806483054</v>
       </c>
       <c r="C65">
-        <v>-43106.02993813196</v>
+        <v>-40423.85117306263</v>
       </c>
       <c r="D65">
-        <v>35676.95006186804</v>
+        <v>38359.12882693737</v>
       </c>
       <c r="E65">
         <v>74389.67999999999</v>
@@ -6623,37 +6623,37 @@
         <v>4551.6</v>
       </c>
       <c r="M65">
-        <v>19211.115924</v>
+        <v>17875.774224</v>
       </c>
       <c r="N65">
-        <v>-14659.515924</v>
+        <v>-13324.174224</v>
       </c>
       <c r="O65">
-        <v>-3782.155108392</v>
+        <v>-3437.636949792</v>
       </c>
       <c r="P65">
-        <v>-10877.360815608</v>
+        <v>-9886.537274208</v>
       </c>
       <c r="Q65">
-        <v>-8518.360815608001</v>
+        <v>-7527.537274208</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1460900362660961</v>
+        <v>0.1457256887408512</v>
       </c>
       <c r="T65">
-        <v>2.314678029783312</v>
+        <v>2.307752626809498</v>
       </c>
       <c r="U65">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.06112673540910543</v>
+        <v>0.06569297560400872</v>
       </c>
       <c r="W65">
-        <v>0.2026088504987151</v>
+        <v>0.187608850498715</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2369253310430443</v>
+        <v>0.2546239364496462</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.183396889232646</v>
+        <v>0.1736620806483054</v>
       </c>
       <c r="C66">
-        <v>-44959.87617569456</v>
+        <v>-42301.9172904376</v>
       </c>
       <c r="D66">
-        <v>35236.16382430543</v>
+        <v>37894.1227095624</v>
       </c>
       <c r="E66">
         <v>75802.73999999999</v>
@@ -6705,37 +6705,37 @@
         <v>4551.6</v>
       </c>
       <c r="M66">
-        <v>19516.054272</v>
+        <v>18159.516672</v>
       </c>
       <c r="N66">
-        <v>-14964.454272</v>
+        <v>-13607.916672</v>
       </c>
       <c r="O66">
-        <v>-3860.829202176</v>
+        <v>-3510.842501376</v>
       </c>
       <c r="P66">
-        <v>-11103.625069824</v>
+        <v>-10097.074170624</v>
       </c>
       <c r="Q66">
-        <v>-8744.625069824</v>
+        <v>-7738.074170624001</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.148875870606821</v>
+        <v>0.148501402316986</v>
       </c>
       <c r="T66">
-        <v>2.378974641721737</v>
+        <v>2.371856866443095</v>
       </c>
       <c r="U66">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.06017163016833816</v>
+        <v>0.0646665228601961</v>
       </c>
       <c r="W66">
-        <v>0.2028149622096727</v>
+        <v>0.1878149622096726</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2332233727454968</v>
+        <v>0.2506454374426205</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1850968892326461</v>
+        <v>0.1752120806483055</v>
       </c>
       <c r="C67">
-        <v>-46802.96357136223</v>
+        <v>-44168.8444248317</v>
       </c>
       <c r="D67">
-        <v>34806.13642863778</v>
+        <v>37440.25557516831</v>
       </c>
       <c r="E67">
         <v>77215.8</v>
@@ -6787,37 +6787,37 @@
         <v>4551.6</v>
       </c>
       <c r="M67">
-        <v>19820.99262</v>
+        <v>18443.25912</v>
       </c>
       <c r="N67">
-        <v>-15269.39262</v>
+        <v>-13891.65912</v>
       </c>
       <c r="O67">
-        <v>-3939.503295960001</v>
+        <v>-3584.048052960001</v>
       </c>
       <c r="P67">
-        <v>-11329.88932404</v>
+        <v>-10307.61106704</v>
       </c>
       <c r="Q67">
-        <v>-8970.889324040003</v>
+        <v>-7948.611067040001</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1518208954813016</v>
+        <v>0.1514357280974713</v>
       </c>
       <c r="T67">
-        <v>2.44694534577093</v>
+        <v>2.439624205484327</v>
       </c>
       <c r="U67">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.05924591278113295</v>
+        <v>0.06367165327773154</v>
       </c>
       <c r="W67">
-        <v>0.2030147320218315</v>
+        <v>0.1880147320218315</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2296353208571045</v>
+        <v>0.2467893537896571</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1867968892326461</v>
+        <v>0.1767620806483055</v>
       </c>
       <c r="C68">
-        <v>-48635.68128332104</v>
+        <v>-46025.02808210891</v>
       </c>
       <c r="D68">
-        <v>34386.47871667896</v>
+        <v>36997.1319178911</v>
       </c>
       <c r="E68">
         <v>78628.86</v>
@@ -6869,37 +6869,37 @@
         <v>4551.6</v>
       </c>
       <c r="M68">
-        <v>20125.930968</v>
+        <v>18727.001568</v>
       </c>
       <c r="N68">
-        <v>-15574.330968</v>
+        <v>-14175.401568</v>
       </c>
       <c r="O68">
-        <v>-4018.177389744001</v>
+        <v>-3657.253604544001</v>
       </c>
       <c r="P68">
-        <v>-11556.153578256</v>
+        <v>-10518.147963456</v>
       </c>
       <c r="Q68">
-        <v>-9197.153578256002</v>
+        <v>-8159.147963456002</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1549391571131046</v>
+        <v>0.1545426612768087</v>
       </c>
       <c r="T68">
-        <v>2.518914326528898</v>
+        <v>2.511377858586807</v>
       </c>
       <c r="U68">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.05834824743596427</v>
+        <v>0.06270693125837196</v>
       </c>
       <c r="W68">
-        <v>0.2032084482033189</v>
+        <v>0.1882084482033189</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.226155997813815</v>
+        <v>0.2430501211564805</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1884968892326461</v>
+        <v>0.1783120806483054</v>
       </c>
       <c r="C69">
-        <v>-50458.39992502451</v>
+        <v>-47870.84526313098</v>
       </c>
       <c r="D69">
-        <v>33976.8200749755</v>
+        <v>36564.37473686902</v>
       </c>
       <c r="E69">
         <v>80041.92</v>
@@ -6951,37 +6951,37 @@
         <v>4551.6</v>
       </c>
       <c r="M69">
-        <v>20430.869316</v>
+        <v>19010.744016</v>
       </c>
       <c r="N69">
-        <v>-15879.269316</v>
+        <v>-14459.144016</v>
       </c>
       <c r="O69">
-        <v>-4096.851483528001</v>
+        <v>-3730.459156128</v>
       </c>
       <c r="P69">
-        <v>-11782.417832472</v>
+        <v>-10728.684859872</v>
       </c>
       <c r="Q69">
-        <v>-9423.417832472001</v>
+        <v>-8369.684859871999</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1582464042983502</v>
+        <v>0.157837893436712</v>
       </c>
       <c r="T69">
-        <v>2.59524506369644</v>
+        <v>2.587480217937922</v>
       </c>
       <c r="U69">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.05747737807124838</v>
+        <v>0.06177100691123209</v>
       </c>
       <c r="W69">
-        <v>0.2033963818122246</v>
+        <v>0.1883963818122246</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2227805351598775</v>
+        <v>0.2394225074078763</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.190196889232646</v>
+        <v>0.1798620806483054</v>
       </c>
       <c r="C70">
-        <v>-52271.47265683895</v>
+        <v>-49706.65553351375</v>
       </c>
       <c r="D70">
-        <v>33576.80734316106</v>
+        <v>36141.62446648625</v>
       </c>
       <c r="E70">
         <v>81454.98</v>
@@ -7033,37 +7033,37 @@
         <v>4551.6</v>
       </c>
       <c r="M70">
-        <v>20735.807664</v>
+        <v>19294.486464</v>
       </c>
       <c r="N70">
-        <v>-16184.207664</v>
+        <v>-14742.886464</v>
       </c>
       <c r="O70">
-        <v>-4175.525577312001</v>
+        <v>-3803.664707712001</v>
       </c>
       <c r="P70">
-        <v>-12008.682086688</v>
+        <v>-10939.221756288</v>
       </c>
       <c r="Q70">
-        <v>-9649.682086688003</v>
+        <v>-8580.221756288</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1617603544326736</v>
+        <v>0.1613390776066093</v>
       </c>
       <c r="T70">
-        <v>2.676346471936955</v>
+        <v>2.668338974748482</v>
       </c>
       <c r="U70">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.05663212251137709</v>
+        <v>0.0608626097507728</v>
       </c>
       <c r="W70">
-        <v>0.2035787879620448</v>
+        <v>0.1885787879620448</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.219504350819291</v>
+        <v>0.2359015881812899</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1918968892326461</v>
+        <v>0.1814120806483054</v>
       </c>
       <c r="C71">
-        <v>-54075.23620147417</v>
+        <v>-51532.8020200218</v>
       </c>
       <c r="D71">
-        <v>33186.10379852584</v>
+        <v>35728.53797997822</v>
       </c>
       <c r="E71">
         <v>82868.04000000001</v>
@@ -7115,37 +7115,37 @@
         <v>4551.6</v>
       </c>
       <c r="M71">
-        <v>21040.746012</v>
+        <v>19578.228912</v>
       </c>
       <c r="N71">
-        <v>-16489.146012</v>
+        <v>-15026.628912</v>
       </c>
       <c r="O71">
-        <v>-4254.199671096001</v>
+        <v>-3876.870259296001</v>
       </c>
       <c r="P71">
-        <v>-12234.946340904</v>
+        <v>-11149.758652704</v>
       </c>
       <c r="Q71">
-        <v>-9875.946340904004</v>
+        <v>-8790.758652704</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.165501011027276</v>
+        <v>0.1650661446261773</v>
       </c>
       <c r="T71">
-        <v>2.762680229096211</v>
+        <v>2.754414425546821</v>
       </c>
       <c r="U71">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.05581136711266148</v>
+        <v>0.05998054294279058</v>
       </c>
       <c r="W71">
-        <v>0.2037559069770877</v>
+        <v>0.1887559069770877</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2163231283436491</v>
+        <v>0.2324827245844596</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1935968892326461</v>
+        <v>0.1829620806483055</v>
       </c>
       <c r="C72">
-        <v>-55870.01178933536</v>
+        <v>-53349.61233940462</v>
       </c>
       <c r="D72">
-        <v>32804.38821066465</v>
+        <v>35324.78766059539</v>
       </c>
       <c r="E72">
         <v>84281.10000000001</v>
@@ -7197,37 +7197,37 @@
         <v>4551.6</v>
       </c>
       <c r="M72">
-        <v>21345.68436</v>
+        <v>19861.97136</v>
       </c>
       <c r="N72">
-        <v>-16794.08436</v>
+        <v>-15310.37136</v>
       </c>
       <c r="O72">
-        <v>-4332.873764880001</v>
+        <v>-3950.075810880001</v>
       </c>
       <c r="P72">
-        <v>-12461.21059512</v>
+        <v>-11360.29554912</v>
       </c>
       <c r="Q72">
-        <v>-10102.21059512</v>
+        <v>-9001.295549120001</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1694910447281852</v>
+        <v>0.1690416827803832</v>
       </c>
       <c r="T72">
-        <v>2.854769570066085</v>
+        <v>2.846228239731715</v>
       </c>
       <c r="U72">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.05501406186819489</v>
+        <v>0.05912367804360785</v>
       </c>
       <c r="W72">
-        <v>0.2039279654488436</v>
+        <v>0.1889279654488435</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2132327979387399</v>
+        <v>0.2291615428046816</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.195296889232646</v>
+        <v>0.1845120806483054</v>
       </c>
       <c r="C73">
-        <v>-57656.10603937478</v>
+        <v>-55157.39946495861</v>
       </c>
       <c r="D73">
-        <v>32431.35396062522</v>
+        <v>34930.06053504138</v>
       </c>
       <c r="E73">
         <v>85694.15999999999</v>
@@ -7279,37 +7279,37 @@
         <v>4551.6</v>
       </c>
       <c r="M73">
-        <v>21650.622708</v>
+        <v>20145.713808</v>
       </c>
       <c r="N73">
-        <v>-17099.022708</v>
+        <v>-15594.113808</v>
       </c>
       <c r="O73">
-        <v>-4411.547858664001</v>
+        <v>-4023.281362464</v>
       </c>
       <c r="P73">
-        <v>-12687.474849336</v>
+        <v>-11570.832445536</v>
       </c>
       <c r="Q73">
-        <v>-10328.474849336</v>
+        <v>-9211.832445536</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1737562531670881</v>
+        <v>0.1732913959797067</v>
       </c>
       <c r="T73">
-        <v>2.953209900068363</v>
+        <v>2.944374041101773</v>
       </c>
       <c r="U73">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.05423921592638933</v>
+        <v>0.05829095018383873</v>
       </c>
       <c r="W73">
-        <v>0.2040951772030852</v>
+        <v>0.1890951772030852</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2102295190945321</v>
+        <v>0.2259339154412354</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.196996889232646</v>
+        <v>0.1860620806483054</v>
       </c>
       <c r="C74">
-        <v>-59433.81178051982</v>
+        <v>-56956.46253563222</v>
       </c>
       <c r="D74">
-        <v>32066.70821948017</v>
+        <v>34544.05746436778</v>
       </c>
       <c r="E74">
         <v>87107.21999999999</v>
@@ -7361,37 +7361,37 @@
         <v>4551.6</v>
       </c>
       <c r="M74">
-        <v>21955.561056</v>
+        <v>20429.456256</v>
       </c>
       <c r="N74">
-        <v>-17403.961056</v>
+        <v>-15877.856256</v>
       </c>
       <c r="O74">
-        <v>-4490.221952448001</v>
+        <v>-4096.486914048</v>
       </c>
       <c r="P74">
-        <v>-12913.739103552</v>
+        <v>-11781.369341952</v>
       </c>
       <c r="Q74">
-        <v>-10554.739103552</v>
+        <v>-9422.369341951999</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.178326119351627</v>
+        <v>0.1778446601218391</v>
       </c>
       <c r="T74">
-        <v>3.058681682213662</v>
+        <v>3.049530256855407</v>
       </c>
       <c r="U74">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.05348589348296726</v>
+        <v>0.05748135365350765</v>
       </c>
       <c r="W74">
-        <v>0.2042577441863757</v>
+        <v>0.1892577441863757</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2073096646626638</v>
+        <v>0.2227959443934405</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1986968892326461</v>
+        <v>0.1876120806483054</v>
       </c>
       <c r="C75">
-        <v>-61203.40881830201</v>
+        <v>-58747.08761206994</v>
       </c>
       <c r="D75">
-        <v>31710.171181698</v>
+        <v>34166.49238793006</v>
       </c>
       <c r="E75">
         <v>88520.28</v>
@@ -7443,37 +7443,37 @@
         <v>4551.6</v>
       </c>
       <c r="M75">
-        <v>22260.499404</v>
+        <v>20713.198704</v>
       </c>
       <c r="N75">
-        <v>-17708.899404</v>
+        <v>-16161.598704</v>
       </c>
       <c r="O75">
-        <v>-4568.896046232001</v>
+        <v>-4169.692465632001</v>
       </c>
       <c r="P75">
-        <v>-13140.003357768</v>
+        <v>-11991.906238368</v>
       </c>
       <c r="Q75">
-        <v>-10781.003357768</v>
+        <v>-9632.906238368001</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.183234494142428</v>
+        <v>0.1827352030893147</v>
       </c>
       <c r="T75">
-        <v>3.171966188962315</v>
+        <v>3.162475821924126</v>
       </c>
       <c r="U75">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.05275321001059784</v>
+        <v>0.05669393785003492</v>
       </c>
       <c r="W75">
-        <v>0.204415857279713</v>
+        <v>0.189415857279713</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2044698062426272</v>
+        <v>0.2197439451551741</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.200396889232646</v>
+        <v>0.1891620806483054</v>
       </c>
       <c r="C76">
-        <v>-62965.16465090548</v>
+        <v>-60529.54838361155</v>
       </c>
       <c r="D76">
-        <v>31361.47534909453</v>
+        <v>33797.09161638846</v>
       </c>
       <c r="E76">
         <v>89933.34</v>
@@ -7525,37 +7525,37 @@
         <v>4551.6</v>
       </c>
       <c r="M76">
-        <v>22565.437752</v>
+        <v>20996.941152</v>
       </c>
       <c r="N76">
-        <v>-18013.837752</v>
+        <v>-16445.341152</v>
       </c>
       <c r="O76">
-        <v>-4647.570140016</v>
+        <v>-4242.898017216</v>
       </c>
       <c r="P76">
-        <v>-13366.267611984</v>
+        <v>-12202.443134784</v>
       </c>
       <c r="Q76">
-        <v>-11007.267611984</v>
+        <v>-9843.443134784</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1885204362248291</v>
+        <v>0.1880019416696729</v>
       </c>
       <c r="T76">
-        <v>3.293964888537789</v>
+        <v>3.284109507382746</v>
       </c>
       <c r="U76">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.05204032879423841</v>
+        <v>0.05592780355476419</v>
       </c>
       <c r="W76">
-        <v>0.2045696970462034</v>
+        <v>0.1895696970462034</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2017067007528621</v>
+        <v>0.2167744323828068</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2247782844355175</v>
+        <v>0.1907120806483055</v>
       </c>
       <c r="C77">
-        <v>-68650.45536896707</v>
+        <v>-62304.10682991803</v>
       </c>
       <c r="D77">
-        <v>27089.24463103293</v>
+        <v>33435.59317008196</v>
       </c>
       <c r="E77">
         <v>91346.39999999999</v>
@@ -7607,45 +7607,45 @@
         <v>4551.6</v>
       </c>
       <c r="M77">
-        <v>26049.7611</v>
+        <v>21280.6836</v>
       </c>
       <c r="N77">
-        <v>-21498.1611</v>
+        <v>-16729.0836</v>
       </c>
       <c r="O77">
-        <v>-5546.525563800002</v>
+        <v>-4316.103568799999</v>
       </c>
       <c r="P77">
-        <v>-15951.6355362</v>
+        <v>-12412.9800312</v>
       </c>
       <c r="Q77">
-        <v>-13592.6355362</v>
+        <v>-10053.9800312</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1949548344853078</v>
+        <v>0.1936900193364599</v>
       </c>
       <c r="T77">
-        <v>3.442469773398829</v>
+        <v>3.415473887678057</v>
       </c>
       <c r="U77">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.04507959959755638</v>
+        <v>0.05518209950736733</v>
       </c>
       <c r="W77">
-        <v>0.2347194344189207</v>
+        <v>0.1897194344189206</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.1747271302230867</v>
+        <v>0.213884106617703</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2267782844355174</v>
+        <v>0.1922620806483055</v>
       </c>
       <c r="C78">
-        <v>-70362.8799553375</v>
+        <v>-64071.01384058609</v>
       </c>
       <c r="D78">
-        <v>26789.88004466251</v>
+        <v>33081.74615941391</v>
       </c>
       <c r="E78">
         <v>92759.45999999999</v>
@@ -7689,45 +7689,45 @@
         <v>4551.6</v>
       </c>
       <c r="M78">
-        <v>26397.091248</v>
+        <v>21564.426048</v>
       </c>
       <c r="N78">
-        <v>-21845.491248</v>
+        <v>-17012.826048</v>
       </c>
       <c r="O78">
-        <v>-5636.136741984</v>
+        <v>-4389.309120384</v>
       </c>
       <c r="P78">
-        <v>-16209.354506016</v>
+        <v>-12623.516927616</v>
       </c>
       <c r="Q78">
-        <v>-13850.354506016</v>
+        <v>-10264.516927616</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2011696192555289</v>
+        <v>0.199852103475479</v>
       </c>
       <c r="T78">
-        <v>3.585906013957113</v>
+        <v>3.557785299664643</v>
       </c>
       <c r="U78">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.04448644697127276</v>
+        <v>0.05445601925069145</v>
       </c>
       <c r="W78">
-        <v>0.2348652313344612</v>
+        <v>0.1898652313344612</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.172428089035941</v>
+        <v>0.2110698420569435</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2287782844355175</v>
+        <v>0.1938120806483054</v>
       </c>
       <c r="C79">
-        <v>-72068.7602769107</v>
+        <v>-65830.50979583037</v>
       </c>
       <c r="D79">
-        <v>26497.05972308929</v>
+        <v>32735.31020416963</v>
       </c>
       <c r="E79">
         <v>94172.51999999999</v>
@@ -7771,45 +7771,45 @@
         <v>4551.6</v>
       </c>
       <c r="M79">
-        <v>26744.421396</v>
+        <v>21848.168496</v>
       </c>
       <c r="N79">
-        <v>-22192.821396</v>
+        <v>-17296.568496</v>
       </c>
       <c r="O79">
-        <v>-5725.747920168</v>
+        <v>-4462.514671968</v>
       </c>
       <c r="P79">
-        <v>-16467.073475832</v>
+        <v>-12834.053824032</v>
       </c>
       <c r="Q79">
-        <v>-14108.073475832</v>
+        <v>-10475.053824032</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2079248200927259</v>
+        <v>0.2065500210178911</v>
       </c>
       <c r="T79">
-        <v>3.741814971085684</v>
+        <v>3.712471617041366</v>
       </c>
       <c r="U79">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.04390870090671076</v>
+        <v>0.0537487982214617</v>
       </c>
       <c r="W79">
-        <v>0.2350072413171305</v>
+        <v>0.1900072413171305</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.1701887632043053</v>
+        <v>0.2083286752769832</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2307782844355174</v>
+        <v>0.1953620806483055</v>
       </c>
       <c r="C80">
-        <v>-73768.30860502932</v>
+        <v>-67582.82511105816</v>
       </c>
       <c r="D80">
-        <v>26210.57139497069</v>
+        <v>32396.05488894185</v>
       </c>
       <c r="E80">
         <v>95585.58</v>
@@ -7853,45 +7853,45 @@
         <v>4551.6</v>
       </c>
       <c r="M80">
-        <v>27091.751544</v>
+        <v>22131.910944</v>
       </c>
       <c r="N80">
-        <v>-22540.151544</v>
+        <v>-17580.310944</v>
       </c>
       <c r="O80">
-        <v>-5815.359098352</v>
+        <v>-4535.720223552002</v>
       </c>
       <c r="P80">
-        <v>-16724.792445648</v>
+        <v>-13044.590720448</v>
       </c>
       <c r="Q80">
-        <v>-14365.792445648</v>
+        <v>-10685.590720448</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2152941300969407</v>
+        <v>0.213856840155068</v>
       </c>
       <c r="T80">
-        <v>3.911897469771397</v>
+        <v>3.881220326906884</v>
       </c>
       <c r="U80">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.04334576884380421</v>
+        <v>0.05305971106477628</v>
       </c>
       <c r="W80">
-        <v>0.2351456100181929</v>
+        <v>0.1901456100181929</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.1680068559837373</v>
+        <v>0.2056577948247141</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2327782844355175</v>
+        <v>0.1969120806483055</v>
       </c>
       <c r="C81">
-        <v>-75461.72812885424</v>
+        <v>-69328.18074792869</v>
       </c>
       <c r="D81">
-        <v>25930.21187114577</v>
+        <v>32063.75925207131</v>
       </c>
       <c r="E81">
         <v>96998.64</v>
@@ -7935,45 +7935,45 @@
         <v>4551.6</v>
       </c>
       <c r="M81">
-        <v>27439.081692</v>
+        <v>22415.653392</v>
       </c>
       <c r="N81">
-        <v>-22887.481692</v>
+        <v>-17864.053392</v>
       </c>
       <c r="O81">
-        <v>-5904.970276536001</v>
+        <v>-4608.925775136001</v>
       </c>
       <c r="P81">
-        <v>-16982.511415464</v>
+        <v>-13255.127616864</v>
       </c>
       <c r="Q81">
-        <v>-14623.511415464</v>
+        <v>-10896.127616864</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.223365279149176</v>
+        <v>0.2218595468291189</v>
       </c>
       <c r="T81">
-        <v>4.098178301665273</v>
+        <v>4.066040342473879</v>
       </c>
       <c r="U81">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.04279708822552821</v>
+        <v>0.05238806915256393</v>
       </c>
       <c r="W81">
-        <v>0.2352804757141652</v>
+        <v>0.1902804757141652</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.1658801869206521</v>
+        <v>0.2030545315990849</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2347782844355175</v>
+        <v>0.1984620806483055</v>
       </c>
       <c r="C82">
-        <v>-77149.21343595869</v>
+        <v>-71066.78869427959</v>
       </c>
       <c r="D82">
-        <v>25655.78656404131</v>
+        <v>31738.21130572042</v>
       </c>
       <c r="E82">
         <v>98411.7</v>
@@ -8017,45 +8017,45 @@
         <v>4551.6</v>
       </c>
       <c r="M82">
-        <v>27786.41184</v>
+        <v>22699.39584</v>
       </c>
       <c r="N82">
-        <v>-23234.81184</v>
+        <v>-18147.79584</v>
       </c>
       <c r="O82">
-        <v>-5994.581454720001</v>
+        <v>-4682.13132672</v>
       </c>
       <c r="P82">
-        <v>-17240.23038528</v>
+        <v>-13465.66451328</v>
       </c>
       <c r="Q82">
-        <v>-14881.23038528</v>
+        <v>-11106.66451328</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2322435431066348</v>
+        <v>0.2306625241705748</v>
       </c>
       <c r="T82">
-        <v>4.303087216748537</v>
+        <v>4.269342359597571</v>
       </c>
       <c r="U82">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.0422621246227091</v>
+        <v>0.05173321828815687</v>
       </c>
       <c r="W82">
-        <v>0.2354119697677381</v>
+        <v>0.1904119697677381</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.1638066845841439</v>
+        <v>0.2005163499540965</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2367782844355175</v>
+        <v>0.2285990101245626</v>
       </c>
       <c r="C83">
-        <v>-78830.95096272435</v>
+        <v>-77712.32908447027</v>
       </c>
       <c r="D83">
-        <v>25387.10903727565</v>
+        <v>26505.73091552973</v>
       </c>
       <c r="E83">
         <v>99824.75999999999</v>
@@ -8099,37 +8099,37 @@
         <v>4551.6</v>
       </c>
       <c r="M83">
-        <v>28133.741988</v>
+        <v>26989.163388</v>
       </c>
       <c r="N83">
-        <v>-23582.141988</v>
+        <v>-22437.563388</v>
       </c>
       <c r="O83">
-        <v>-6084.192632904001</v>
+        <v>-5788.891354104001</v>
       </c>
       <c r="P83">
-        <v>-17497.949355096</v>
+        <v>-16648.672033896</v>
       </c>
       <c r="Q83">
-        <v>-15138.949355096</v>
+        <v>-14289.672033896</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2420563611648787</v>
+        <v>0.2416391279493266</v>
       </c>
       <c r="T83">
-        <v>4.529565491314249</v>
+        <v>4.522843601601077</v>
       </c>
       <c r="U83">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.0417403699977374</v>
+        <v>0.04351052987889674</v>
       </c>
       <c r="W83">
-        <v>0.2355402170545562</v>
+        <v>0.2255402170545562</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1617843798361914</v>
+        <v>0.1686454646468866</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2387782844355174</v>
+        <v>0.2304990101245626</v>
       </c>
       <c r="C84">
-        <v>-80507.11941673032</v>
+        <v>-79398.05372249699</v>
       </c>
       <c r="D84">
-        <v>25124.0005832697</v>
+        <v>26233.06627750302</v>
       </c>
       <c r="E84">
         <v>101237.82</v>
@@ -8181,37 +8181,37 @@
         <v>4551.6</v>
       </c>
       <c r="M84">
-        <v>28481.07213600001</v>
+        <v>27322.362936</v>
       </c>
       <c r="N84">
-        <v>-23929.472136</v>
+        <v>-22770.76293600001</v>
       </c>
       <c r="O84">
-        <v>-6173.803811088002</v>
+        <v>-5874.856837488001</v>
       </c>
       <c r="P84">
-        <v>-17755.668324912</v>
+        <v>-16895.906098512</v>
       </c>
       <c r="Q84">
-        <v>-15396.668324912</v>
+        <v>-14536.906098512</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2529594923407052</v>
+        <v>0.252519079502067</v>
       </c>
       <c r="T84">
-        <v>4.781208018609485</v>
+        <v>4.774112690578916</v>
       </c>
       <c r="U84">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04123134109532596</v>
+        <v>0.04297991366086142</v>
       </c>
       <c r="W84">
-        <v>0.2356653363587689</v>
+        <v>0.2256653363587689</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1598113995942867</v>
+        <v>0.1665888126389976</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2407782844355174</v>
+        <v>0.2323990101245625</v>
       </c>
       <c r="C85">
-        <v>-82177.89017314615</v>
+        <v>-81078.22567498797</v>
       </c>
       <c r="D85">
-        <v>24866.28982685385</v>
+        <v>25965.95432501204</v>
       </c>
       <c r="E85">
         <v>102650.88</v>
@@ -8263,37 +8263,37 @@
         <v>4551.6</v>
       </c>
       <c r="M85">
-        <v>28828.402284</v>
+        <v>27655.562484</v>
       </c>
       <c r="N85">
-        <v>-24276.802284</v>
+        <v>-23103.962484</v>
       </c>
       <c r="O85">
-        <v>-6263.414989272002</v>
+        <v>-5960.822320872001</v>
       </c>
       <c r="P85">
-        <v>-18013.387294728</v>
+        <v>-17143.140163128</v>
       </c>
       <c r="Q85">
-        <v>-15654.387294728</v>
+        <v>-14784.140163128</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.265145344831335</v>
+        <v>0.2646790253551298</v>
       </c>
       <c r="T85">
-        <v>5.062455549115926</v>
+        <v>5.054942848848264</v>
       </c>
       <c r="U85">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04073457794959914</v>
+        <v>0.0424620833757908</v>
       </c>
       <c r="W85">
-        <v>0.2357874407399886</v>
+        <v>0.2257874407399885</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1578859610449579</v>
+        <v>0.1645817185108169</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2427782844355174</v>
+        <v>0.2342990101245625</v>
       </c>
       <c r="C86">
-        <v>-83843.42764697644</v>
+        <v>-82753.01284896579</v>
       </c>
       <c r="D86">
-        <v>24613.81235302355</v>
+        <v>25704.22715103419</v>
       </c>
       <c r="E86">
         <v>104063.94</v>
@@ -8345,37 +8345,37 @@
         <v>4551.6</v>
       </c>
       <c r="M86">
-        <v>29175.732432</v>
+        <v>27988.762032</v>
       </c>
       <c r="N86">
-        <v>-24624.132432</v>
+        <v>-23437.162032</v>
       </c>
       <c r="O86">
-        <v>-6353.026167456</v>
+        <v>-6046.787804256001</v>
       </c>
       <c r="P86">
-        <v>-18271.106264544</v>
+        <v>-17390.374227744</v>
       </c>
       <c r="Q86">
-        <v>-15912.106264544</v>
+        <v>-15031.374227744</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2788544288832934</v>
+        <v>0.2783589644398253</v>
       </c>
       <c r="T86">
-        <v>5.378859020935669</v>
+        <v>5.370876776901278</v>
       </c>
       <c r="U86">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04024964249781821</v>
+        <v>0.04195658238322186</v>
       </c>
       <c r="W86">
-        <v>0.2359066378740363</v>
+        <v>0.2259066378740363</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1560063662706133</v>
+        <v>0.1626224123380692</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2447782844355174</v>
+        <v>0.2361990101245625</v>
       </c>
       <c r="C87">
-        <v>-85503.88964285605</v>
+        <v>-84422.57644924719</v>
       </c>
       <c r="D87">
-        <v>24366.41035714394</v>
+        <v>25447.72355075279</v>
       </c>
       <c r="E87">
         <v>105477</v>
@@ -8427,37 +8427,37 @@
         <v>4551.6</v>
       </c>
       <c r="M87">
-        <v>29523.06258</v>
+        <v>28321.96158</v>
       </c>
       <c r="N87">
-        <v>-24971.46258</v>
+        <v>-23770.36158</v>
       </c>
       <c r="O87">
-        <v>-6442.63734564</v>
+        <v>-6132.753287639999</v>
       </c>
       <c r="P87">
-        <v>-18528.82523436</v>
+        <v>-17637.60829236</v>
       </c>
       <c r="Q87">
-        <v>-16169.82523436</v>
+        <v>-15278.60829236</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2943913908088462</v>
+        <v>0.2938628954024803</v>
       </c>
       <c r="T87">
-        <v>5.73744962233138</v>
+        <v>5.728935228694697</v>
       </c>
       <c r="U87">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03977611729196152</v>
+        <v>0.04146297553165455</v>
       </c>
       <c r="W87">
-        <v>0.2360230303696359</v>
+        <v>0.2260230303696359</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1541709972556649</v>
+        <v>0.1607092074870332</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2467782844355175</v>
+        <v>0.2380990101245625</v>
       </c>
       <c r="C88">
-        <v>-87159.42768395969</v>
+        <v>-86087.07130954685</v>
       </c>
       <c r="D88">
-        <v>24123.93231604032</v>
+        <v>25196.28869045314</v>
       </c>
       <c r="E88">
         <v>106890.06</v>
@@ -8509,37 +8509,37 @@
         <v>4551.6</v>
       </c>
       <c r="M88">
-        <v>29870.392728</v>
+        <v>28655.161128</v>
       </c>
       <c r="N88">
-        <v>-25318.792728</v>
+        <v>-24103.561128</v>
       </c>
       <c r="O88">
-        <v>-6532.248523824001</v>
+        <v>-6218.718771024</v>
       </c>
       <c r="P88">
-        <v>-18786.544204176</v>
+        <v>-17884.842356976</v>
       </c>
       <c r="Q88">
-        <v>-16427.544204176</v>
+        <v>-15525.842356976</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3121479187237639</v>
+        <v>0.3115816736455146</v>
       </c>
       <c r="T88">
-        <v>6.147267452497908</v>
+        <v>6.138144887887176</v>
       </c>
       <c r="U88">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03931360430019452</v>
+        <v>0.04098084790919344</v>
       </c>
       <c r="W88">
-        <v>0.2361367160630122</v>
+        <v>0.2261367160630122</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1523783112410642</v>
+        <v>0.1588404957720677</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2487782844355174</v>
+        <v>0.2399990101245625</v>
       </c>
       <c r="C89">
-        <v>-88810.18732146651</v>
+        <v>-87746.64620414469</v>
       </c>
       <c r="D89">
-        <v>23886.2326785335</v>
+        <v>24949.77379585531</v>
       </c>
       <c r="E89">
         <v>108303.12</v>
@@ -8591,37 +8591,37 @@
         <v>4551.6</v>
       </c>
       <c r="M89">
-        <v>30217.722876</v>
+        <v>28988.360676</v>
       </c>
       <c r="N89">
-        <v>-25666.122876</v>
+        <v>-24436.760676</v>
       </c>
       <c r="O89">
-        <v>-6621.859702008001</v>
+        <v>-6304.684254408</v>
       </c>
       <c r="P89">
-        <v>-19044.263173992</v>
+        <v>-18132.076421592</v>
       </c>
       <c r="Q89">
-        <v>-16685.263173992</v>
+        <v>-15773.076421592</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3326362201640534</v>
+        <v>0.3320264177720927</v>
       </c>
       <c r="T89">
-        <v>6.620134179613132</v>
+        <v>6.610309879263111</v>
       </c>
       <c r="U89">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03886172379099689</v>
+        <v>0.04050980368035215</v>
       </c>
       <c r="W89">
-        <v>0.236247788292173</v>
+        <v>0.226247788292173</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1506268363992128</v>
+        <v>0.1570147429471014</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2507782844355174</v>
+        <v>0.2418990101245625</v>
       </c>
       <c r="C90">
-        <v>-90456.30842590801</v>
+        <v>-89401.44414143469</v>
       </c>
       <c r="D90">
-        <v>23653.171574092</v>
+        <v>24708.0358585653</v>
       </c>
       <c r="E90">
         <v>109716.18</v>
@@ -8673,37 +8673,37 @@
         <v>4551.6</v>
       </c>
       <c r="M90">
-        <v>30565.053024</v>
+        <v>29321.560224</v>
       </c>
       <c r="N90">
-        <v>-26013.453024</v>
+        <v>-24769.960224</v>
       </c>
       <c r="O90">
-        <v>-6711.470880192001</v>
+        <v>-6390.649737792</v>
       </c>
       <c r="P90">
-        <v>-19301.982143808</v>
+        <v>-18379.310486208</v>
       </c>
       <c r="Q90">
-        <v>-16942.982143808</v>
+        <v>-16020.310486208</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3565392385110578</v>
+        <v>0.3558786192531005</v>
       </c>
       <c r="T90">
-        <v>7.171812027914226</v>
+        <v>7.161169035868372</v>
       </c>
       <c r="U90">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03842011329337192</v>
+        <v>0.04004946500216632</v>
       </c>
       <c r="W90">
-        <v>0.2363563361524892</v>
+        <v>0.2263563361524892</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1489151678037671</v>
+        <v>0.1552304845045206</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2527782844355174</v>
+        <v>0.2437990101245626</v>
       </c>
       <c r="C91">
-        <v>-92097.92546162409</v>
+        <v>-91051.60264057235</v>
       </c>
       <c r="D91">
-        <v>23424.6145383759</v>
+        <v>24470.93735942765</v>
       </c>
       <c r="E91">
         <v>111129.24</v>
@@ -8755,37 +8755,37 @@
         <v>4551.6</v>
       </c>
       <c r="M91">
-        <v>30912.383172</v>
+        <v>29654.759772</v>
       </c>
       <c r="N91">
-        <v>-26360.783172</v>
+        <v>-25103.159772</v>
       </c>
       <c r="O91">
-        <v>-6801.082058376001</v>
+        <v>-6476.615221176</v>
       </c>
       <c r="P91">
-        <v>-19559.701113624</v>
+        <v>-18626.544550824</v>
       </c>
       <c r="Q91">
-        <v>-17200.701113624</v>
+        <v>-16267.544550824</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3847882601938813</v>
+        <v>0.3840675846397459</v>
       </c>
       <c r="T91">
-        <v>7.823794939542793</v>
+        <v>7.812184402765497</v>
       </c>
       <c r="U91">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03798842662715426</v>
+        <v>0.03959947101337793</v>
       </c>
       <c r="W91">
-        <v>0.2364624447350455</v>
+        <v>0.2264624447350455</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1472419636711405</v>
+        <v>0.1534863217572788</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2547782844355175</v>
+        <v>0.2456990101245626</v>
       </c>
       <c r="C92">
-        <v>-93735.16774545949</v>
+        <v>-92697.25399234514</v>
       </c>
       <c r="D92">
-        <v>23200.43225454052</v>
+        <v>24238.34600765487</v>
       </c>
       <c r="E92">
         <v>112542.3</v>
@@ -8837,37 +8837,37 @@
         <v>4551.6</v>
       </c>
       <c r="M92">
-        <v>31259.71332000001</v>
+        <v>29987.95932</v>
       </c>
       <c r="N92">
-        <v>-26708.11332</v>
+        <v>-25436.35932</v>
       </c>
       <c r="O92">
-        <v>-6890.693236560001</v>
+        <v>-6562.580704560001</v>
       </c>
       <c r="P92">
-        <v>-19817.42008344</v>
+        <v>-18873.77861544</v>
       </c>
       <c r="Q92">
-        <v>-17458.42008344</v>
+        <v>-16514.77861544</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4186870862132696</v>
+        <v>0.4178943431037206</v>
       </c>
       <c r="T92">
-        <v>8.606174433497074</v>
+        <v>8.593402843042048</v>
       </c>
       <c r="U92">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03756633299796365</v>
+        <v>0.03915947689100707</v>
       </c>
       <c r="W92">
-        <v>0.2365661953491006</v>
+        <v>0.2265661953491006</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1456059418525724</v>
+        <v>0.1517809181821979</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2567782844355175</v>
+        <v>0.2475990101245625</v>
       </c>
       <c r="C93">
-        <v>-95368.15969074583</v>
+        <v>-94338.52550530607</v>
       </c>
       <c r="D93">
-        <v>22980.50030925418</v>
+        <v>24010.13449469394</v>
       </c>
       <c r="E93">
         <v>113955.36</v>
@@ -8919,37 +8919,37 @@
         <v>4551.6</v>
       </c>
       <c r="M93">
-        <v>31607.043468</v>
+        <v>30321.158868</v>
       </c>
       <c r="N93">
-        <v>-27055.443468</v>
+        <v>-25769.558868</v>
       </c>
       <c r="O93">
-        <v>-6980.304414744001</v>
+        <v>-6648.546187944</v>
       </c>
       <c r="P93">
-        <v>-20075.139053256</v>
+        <v>-19121.012680056</v>
       </c>
       <c r="Q93">
-        <v>-17716.139053256</v>
+        <v>-16762.012680056</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4601189846814107</v>
+        <v>0.459238159004134</v>
       </c>
       <c r="T93">
-        <v>9.562416037218972</v>
+        <v>9.548225381157831</v>
       </c>
       <c r="U93">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03715351615183218</v>
+        <v>0.03872915296912787</v>
       </c>
       <c r="W93">
-        <v>0.2366676657298797</v>
+        <v>0.2266676657298797</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1440058765574891</v>
+        <v>0.1501129960043717</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2587782844355175</v>
+        <v>0.2494990101245625</v>
       </c>
       <c r="C94">
-        <v>-96997.02103753723</v>
+        <v>-95975.53973813236</v>
       </c>
       <c r="D94">
-        <v>22764.69896246277</v>
+        <v>23786.18026186765</v>
       </c>
       <c r="E94">
         <v>115368.42</v>
@@ -9001,37 +9001,37 @@
         <v>4551.6</v>
       </c>
       <c r="M94">
-        <v>31954.373616</v>
+        <v>30654.358416</v>
       </c>
       <c r="N94">
-        <v>-27402.77361600001</v>
+        <v>-26102.758416</v>
       </c>
       <c r="O94">
-        <v>-7069.915592928001</v>
+        <v>-6734.511671328001</v>
       </c>
       <c r="P94">
-        <v>-20332.858023072</v>
+        <v>-19368.246744672</v>
       </c>
       <c r="Q94">
-        <v>-17973.858023072</v>
+        <v>-17009.246744672</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.5119088577665871</v>
+        <v>0.5109179288796509</v>
       </c>
       <c r="T94">
-        <v>10.75771804187135</v>
+        <v>10.74175355380256</v>
       </c>
       <c r="U94">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03674967358496444</v>
+        <v>0.03830818391511561</v>
       </c>
       <c r="W94">
-        <v>0.2367669302328158</v>
+        <v>0.2267669302328157</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1424405952905597</v>
+        <v>0.148481333004324</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2607782844355175</v>
+        <v>0.2513990101245626</v>
       </c>
       <c r="C95">
-        <v>-98621.86706999385</v>
+        <v>-97608.41471910026</v>
       </c>
       <c r="D95">
-        <v>22552.91293000616</v>
+        <v>23566.36528089976</v>
       </c>
       <c r="E95">
         <v>116781.48</v>
@@ -9083,37 +9083,37 @@
         <v>4551.6</v>
       </c>
       <c r="M95">
-        <v>32301.70376400001</v>
+        <v>30987.55796400001</v>
       </c>
       <c r="N95">
-        <v>-27750.10376400001</v>
+        <v>-26435.95796400001</v>
       </c>
       <c r="O95">
-        <v>-7159.526771112002</v>
+        <v>-6820.477154712003</v>
       </c>
       <c r="P95">
-        <v>-20590.576992888</v>
+        <v>-19615.480809288</v>
       </c>
       <c r="Q95">
-        <v>-18231.576992888</v>
+        <v>-17256.480809288</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5784958374475282</v>
+        <v>0.5773633472910296</v>
       </c>
       <c r="T95">
-        <v>12.29453490499583</v>
+        <v>12.27628977577436</v>
       </c>
       <c r="U95">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03635451580448096</v>
+        <v>0.03789626795903909</v>
       </c>
       <c r="W95">
-        <v>0.2368640600152586</v>
+        <v>0.2268640600152586</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1409089759863602</v>
+        <v>0.1468847595311592</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2627782844355174</v>
+        <v>0.2532990101245626</v>
       </c>
       <c r="C96">
-        <v>-100242.8088217432</v>
+        <v>-99237.26415350204</v>
       </c>
       <c r="D96">
-        <v>22345.03117825687</v>
+        <v>23350.57584649797</v>
       </c>
       <c r="E96">
         <v>118194.54</v>
@@ -9165,37 +9165,37 @@
         <v>4551.6</v>
       </c>
       <c r="M96">
-        <v>32649.03391200001</v>
+        <v>31320.757512</v>
       </c>
       <c r="N96">
-        <v>-28097.43391200001</v>
+        <v>-26769.15751200001</v>
       </c>
       <c r="O96">
-        <v>-7249.137949296002</v>
+        <v>-6906.442638096001</v>
       </c>
       <c r="P96">
-        <v>-20848.295962704</v>
+        <v>-19862.71487390401</v>
       </c>
       <c r="Q96">
-        <v>-18489.295962704</v>
+        <v>-17503.71487390401</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.6672784770221162</v>
+        <v>0.6659572385062015</v>
       </c>
       <c r="T96">
-        <v>14.34362405582846</v>
+        <v>14.32233807173676</v>
       </c>
       <c r="U96">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03596776563634817</v>
+        <v>0.03749311617224081</v>
       </c>
       <c r="W96">
-        <v>0.2369591232065856</v>
+        <v>0.2269591232065856</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1394099443269309</v>
+        <v>0.1453221557063596</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2647782844355174</v>
+        <v>0.2551990101245625</v>
       </c>
       <c r="C97">
-        <v>-101859.9532699875</v>
+        <v>-100862.1976197708</v>
       </c>
       <c r="D97">
-        <v>22140.94673001254</v>
+        <v>23138.70238022918</v>
       </c>
       <c r="E97">
         <v>119607.6</v>
@@ -9247,37 +9247,37 @@
         <v>4551.6</v>
       </c>
       <c r="M97">
-        <v>32996.36406000001</v>
+        <v>31653.95706</v>
       </c>
       <c r="N97">
-        <v>-28444.76406000001</v>
+        <v>-27102.35706</v>
       </c>
       <c r="O97">
-        <v>-7338.749127480002</v>
+        <v>-6992.408121480001</v>
       </c>
       <c r="P97">
-        <v>-21106.01493252001</v>
+        <v>-20109.94893852</v>
       </c>
       <c r="Q97">
-        <v>-18747.01493252001</v>
+        <v>-17750.94893852</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.7915741724265399</v>
+        <v>0.7899886862074421</v>
       </c>
       <c r="T97">
-        <v>17.21234886699417</v>
+        <v>17.18680568608412</v>
       </c>
       <c r="U97">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03558915757701819</v>
+        <v>0.03709845179148038</v>
       </c>
       <c r="W97">
-        <v>0.2370521850675689</v>
+        <v>0.2270521850675689</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1379424712287526</v>
+        <v>0.1437924488041875</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2667782844355174</v>
+        <v>0.2570990101245625</v>
       </c>
       <c r="C98">
-        <v>-103473.4035190707</v>
+        <v>-102483.3207550241</v>
       </c>
       <c r="D98">
-        <v>21940.55648092928</v>
+        <v>22930.63924497588</v>
       </c>
       <c r="E98">
         <v>121020.66</v>
@@ -9329,37 +9329,37 @@
         <v>4551.6</v>
       </c>
       <c r="M98">
-        <v>33343.69420800001</v>
+        <v>31987.156608</v>
       </c>
       <c r="N98">
-        <v>-28792.09420800001</v>
+        <v>-27435.55660800001</v>
       </c>
       <c r="O98">
-        <v>-7428.360305664002</v>
+        <v>-7078.373604864002</v>
       </c>
       <c r="P98">
-        <v>-21363.73390233601</v>
+        <v>-20357.183003136</v>
       </c>
       <c r="Q98">
-        <v>-19004.73390233601</v>
+        <v>-17998.183003136</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.9780177155331727</v>
+        <v>0.9760358577593005</v>
       </c>
       <c r="T98">
-        <v>21.51543608374266</v>
+        <v>21.4835071076051</v>
       </c>
       <c r="U98">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03521843718559092</v>
+        <v>0.03671200958531912</v>
       </c>
       <c r="W98">
-        <v>0.2371433081397818</v>
+        <v>0.2271433081397818</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1365055704867865</v>
+        <v>0.1422946107958105</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2687782844355174</v>
+        <v>0.2589990101245626</v>
       </c>
       <c r="C99">
-        <v>-105083.258974166</v>
+        <v>-104100.7354306861</v>
       </c>
       <c r="D99">
-        <v>21743.76102583397</v>
+        <v>22726.28456931392</v>
       </c>
       <c r="E99">
         <v>122433.72</v>
@@ -9411,37 +9411,37 @@
         <v>4551.6</v>
       </c>
       <c r="M99">
-        <v>33691.024356</v>
+        <v>32320.356156</v>
       </c>
       <c r="N99">
-        <v>-29139.424356</v>
+        <v>-27768.756156</v>
       </c>
       <c r="O99">
-        <v>-7517.971483848001</v>
+        <v>-7164.339088248001</v>
       </c>
       <c r="P99">
-        <v>-21621.452872152</v>
+        <v>-20604.417067752</v>
       </c>
       <c r="Q99">
-        <v>-19262.452872152</v>
+        <v>-18245.417067752</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.28875695404423</v>
+        <v>1.286114477012401</v>
       </c>
       <c r="T99">
-        <v>28.68724811165688</v>
+        <v>28.64467614347346</v>
       </c>
       <c r="U99">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03485536051357453</v>
+        <v>0.03633353525969728</v>
       </c>
       <c r="W99">
-        <v>0.2372325523857634</v>
+        <v>0.2272325523857634</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1350982965642423</v>
+        <v>0.1408276560453382</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2707782844355174</v>
+        <v>0.2608990101245626</v>
       </c>
       <c r="C100">
-        <v>-106689.6155056992</v>
+        <v>-105714.539918802</v>
       </c>
       <c r="D100">
-        <v>21550.46449430081</v>
+        <v>22525.54008119801</v>
       </c>
       <c r="E100">
         <v>123846.78</v>
@@ -9493,37 +9493,37 @@
         <v>4551.6</v>
       </c>
       <c r="M100">
-        <v>34038.354504</v>
+        <v>32653.555704</v>
       </c>
       <c r="N100">
-        <v>-29486.754504</v>
+        <v>-28101.955704</v>
       </c>
       <c r="O100">
-        <v>-7607.582662032001</v>
+        <v>-7250.304571632</v>
       </c>
       <c r="P100">
-        <v>-21879.171841968</v>
+        <v>-20851.651132368</v>
       </c>
       <c r="Q100">
-        <v>-19520.171841968</v>
+        <v>-18492.651132368</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.910235431066346</v>
+        <v>1.906271715518601</v>
       </c>
       <c r="T100">
-        <v>43.03087216748532</v>
+        <v>42.96701421521019</v>
       </c>
       <c r="U100">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03449969356955846</v>
+        <v>0.03596278489990445</v>
       </c>
       <c r="W100">
-        <v>0.2373199753206025</v>
+        <v>0.2273199753206026</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1337197425176684</v>
+        <v>0.1393906391469165</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2727782844355174</v>
+        <v>0.2627990101245625</v>
       </c>
       <c r="C101">
-        <v>-108292.5656050794</v>
+        <v>-107324.8290496156</v>
       </c>
       <c r="D101">
-        <v>21360.57439492063</v>
+        <v>22328.31095038442</v>
       </c>
       <c r="E101">
         <v>125259.84</v>
@@ -9575,37 +9575,37 @@
         <v>4551.6</v>
       </c>
       <c r="M101">
-        <v>34385.684652</v>
+        <v>32986.755252</v>
       </c>
       <c r="N101">
-        <v>-29834.08465200001</v>
+        <v>-28435.155252</v>
       </c>
       <c r="O101">
-        <v>-7697.193840216001</v>
+        <v>-7336.270055016002</v>
       </c>
       <c r="P101">
-        <v>-22136.890811784</v>
+        <v>-21098.885196984</v>
       </c>
       <c r="Q101">
-        <v>-19777.890811784</v>
+        <v>-18739.885196984</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.774670862132691</v>
+        <v>3.766743431037202</v>
       </c>
       <c r="T101">
-        <v>86.06174433497064</v>
+        <v>85.93402843042038</v>
       </c>
       <c r="U101">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V101">
-        <v>0.0341512118163306</v>
+        <v>0.03559952444637006</v>
       </c>
       <c r="W101">
-        <v>0.2374056321355459</v>
+        <v>0.227405632135546</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.132369038047793</v>
+        <v>0.1379826528929071</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/netherlands/netherlands_aerospace_defense.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_aerospace_defense.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08436873256272703</v>
+        <v>0.08418445123271522</v>
       </c>
       <c r="C2">
-        <v>135865.4312313797</v>
+        <v>135055.4919655159</v>
       </c>
       <c r="D2">
-        <v>125625.6312313797</v>
+        <v>126228.7519655159</v>
       </c>
       <c r="E2">
-        <v>-14633.1</v>
+        <v>-13220.04</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1413.06</v>
       </c>
       <c r="G2">
         <v>10239.8</v>
@@ -1457,28 +1457,28 @@
         <v>4551.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>71.07691799999999</v>
       </c>
       <c r="N2">
-        <v>4551.6</v>
+        <v>4480.523082000001</v>
       </c>
       <c r="O2">
-        <v>1174.3128</v>
+        <v>1155.974955156</v>
       </c>
       <c r="P2">
-        <v>3377.2872</v>
+        <v>3324.548126844001</v>
       </c>
       <c r="Q2">
-        <v>5736.287200000001</v>
+        <v>5683.548126844001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08436873256272703</v>
+        <v>0.0846578032653689</v>
       </c>
       <c r="T2">
-        <v>0.890732853642657</v>
+        <v>0.8974088513942009</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>64.03766691178143</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08418445123271522</v>
+        <v>0.08400016990270337</v>
       </c>
       <c r="C3">
-        <v>135055.4919655159</v>
+        <v>134251.371725658</v>
       </c>
       <c r="D3">
-        <v>126228.7519655159</v>
+        <v>126837.691725658</v>
       </c>
       <c r="E3">
-        <v>-13220.04</v>
+        <v>-11806.98</v>
       </c>
       <c r="F3">
-        <v>1413.06</v>
+        <v>2826.12</v>
       </c>
       <c r="G3">
         <v>10239.8</v>
@@ -1539,28 +1539,28 @@
         <v>4551.6</v>
       </c>
       <c r="M3">
-        <v>71.07691799999999</v>
+        <v>142.153836</v>
       </c>
       <c r="N3">
-        <v>4480.523082000001</v>
+        <v>4409.446164</v>
       </c>
       <c r="O3">
-        <v>1155.974955156</v>
+        <v>1137.637110312</v>
       </c>
       <c r="P3">
-        <v>3324.548126844001</v>
+        <v>3271.809053688</v>
       </c>
       <c r="Q3">
-        <v>5683.548126844001</v>
+        <v>5630.809053688</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0846578032653689</v>
+        <v>0.08495277337010548</v>
       </c>
       <c r="T3">
-        <v>0.8974088513942009</v>
+        <v>0.9042210939978171</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>64.03766691178143</v>
+        <v>32.0188334558907</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08400016990270337</v>
+        <v>0.08381588857269152</v>
       </c>
       <c r="C4">
-        <v>134251.371725658</v>
+        <v>133453.1551346749</v>
       </c>
       <c r="D4">
-        <v>126837.691725658</v>
+        <v>127452.5351346749</v>
       </c>
       <c r="E4">
-        <v>-11806.98</v>
+        <v>-10393.92</v>
       </c>
       <c r="F4">
-        <v>2826.12</v>
+        <v>4239.18</v>
       </c>
       <c r="G4">
         <v>10239.8</v>
@@ -1621,28 +1621,28 @@
         <v>4551.6</v>
       </c>
       <c r="M4">
-        <v>142.153836</v>
+        <v>213.230754</v>
       </c>
       <c r="N4">
-        <v>4409.446164</v>
+        <v>4338.369246</v>
       </c>
       <c r="O4">
-        <v>1137.637110312</v>
+        <v>1119.299265468</v>
       </c>
       <c r="P4">
-        <v>3271.809053688</v>
+        <v>3219.069980532</v>
       </c>
       <c r="Q4">
-        <v>5630.809053688</v>
+        <v>5578.069980532</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08495277337010548</v>
+        <v>0.08525382533267167</v>
       </c>
       <c r="T4">
-        <v>0.9042210939978171</v>
+        <v>0.9111737952118173</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>32.0188334558907</v>
+        <v>21.3458889705938</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08381588857269152</v>
+        <v>0.08363160724267969</v>
       </c>
       <c r="C5">
-        <v>133453.1551346749</v>
+        <v>132660.9284642591</v>
       </c>
       <c r="D5">
-        <v>127452.5351346749</v>
+        <v>128073.3684642591</v>
       </c>
       <c r="E5">
-        <v>-10393.92</v>
+        <v>-8980.860000000001</v>
       </c>
       <c r="F5">
-        <v>4239.18</v>
+        <v>5652.24</v>
       </c>
       <c r="G5">
         <v>10239.8</v>
@@ -1703,28 +1703,28 @@
         <v>4551.6</v>
       </c>
       <c r="M5">
-        <v>213.230754</v>
+        <v>284.307672</v>
       </c>
       <c r="N5">
-        <v>4338.369246</v>
+        <v>4267.292328</v>
       </c>
       <c r="O5">
-        <v>1119.299265468</v>
+        <v>1100.961420624</v>
       </c>
       <c r="P5">
-        <v>3219.069980532</v>
+        <v>3166.330907376</v>
       </c>
       <c r="Q5">
-        <v>5578.069980532</v>
+        <v>5525.330907376</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08525382533267167</v>
+        <v>0.08556114921112468</v>
       </c>
       <c r="T5">
-        <v>0.9111737952118173</v>
+        <v>0.9182713443677758</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>21.3458889705938</v>
+        <v>16.00941672794535</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08363160724267969</v>
+        <v>0.08344732591266785</v>
       </c>
       <c r="C6">
-        <v>132660.9284642591</v>
+        <v>131874.7796752822</v>
       </c>
       <c r="D6">
-        <v>128073.3684642591</v>
+        <v>128700.2796752822</v>
       </c>
       <c r="E6">
-        <v>-8980.860000000001</v>
+        <v>-7567.8</v>
       </c>
       <c r="F6">
-        <v>5652.24</v>
+        <v>7065.3</v>
       </c>
       <c r="G6">
         <v>10239.8</v>
@@ -1785,28 +1785,28 @@
         <v>4551.6</v>
       </c>
       <c r="M6">
-        <v>284.307672</v>
+        <v>355.38459</v>
       </c>
       <c r="N6">
-        <v>4267.292328</v>
+        <v>4196.215410000001</v>
       </c>
       <c r="O6">
-        <v>1100.961420624</v>
+        <v>1082.62357578</v>
       </c>
       <c r="P6">
-        <v>3166.330907376</v>
+        <v>3113.59183422</v>
       </c>
       <c r="Q6">
-        <v>5525.330907376</v>
+        <v>5472.59183422</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08556114921112468</v>
+        <v>0.08587494306596617</v>
       </c>
       <c r="T6">
-        <v>0.9182713443677758</v>
+        <v>0.9255183156112282</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>16.00941672794535</v>
+        <v>12.80753338235628</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08344732591266785</v>
+        <v>0.08326304458265602</v>
       </c>
       <c r="C7">
-        <v>131874.7796752822</v>
+        <v>131094.7984593391</v>
       </c>
       <c r="D7">
-        <v>128700.2796752822</v>
+        <v>129333.3584593391</v>
       </c>
       <c r="E7">
-        <v>-7567.8</v>
+        <v>-6154.74</v>
       </c>
       <c r="F7">
-        <v>7065.3</v>
+        <v>8478.360000000001</v>
       </c>
       <c r="G7">
         <v>10239.8</v>
@@ -1867,28 +1867,28 @@
         <v>4551.6</v>
       </c>
       <c r="M7">
-        <v>355.38459</v>
+        <v>426.461508</v>
       </c>
       <c r="N7">
-        <v>4196.215410000001</v>
+        <v>4125.138492</v>
       </c>
       <c r="O7">
-        <v>1082.62357578</v>
+        <v>1064.285730936</v>
       </c>
       <c r="P7">
-        <v>3113.59183422</v>
+        <v>3060.852761064</v>
       </c>
       <c r="Q7">
-        <v>5472.59183422</v>
+        <v>5419.852761064</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08587494306596617</v>
+        <v>0.08619541338580428</v>
       </c>
       <c r="T7">
-        <v>0.9255183156112282</v>
+        <v>0.9329194777322006</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>12.80753338235628</v>
+        <v>10.6729444852969</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08326304458265602</v>
+        <v>0.0830787632526442</v>
       </c>
       <c r="C8">
-        <v>131094.7984593391</v>
+        <v>130321.0762815264</v>
       </c>
       <c r="D8">
-        <v>129333.3584593391</v>
+        <v>129972.6962815264</v>
       </c>
       <c r="E8">
-        <v>-6154.74</v>
+        <v>-4741.680000000002</v>
       </c>
       <c r="F8">
-        <v>8478.360000000001</v>
+        <v>9891.419999999998</v>
       </c>
       <c r="G8">
         <v>10239.8</v>
@@ -1949,28 +1949,28 @@
         <v>4551.6</v>
       </c>
       <c r="M8">
-        <v>426.461508</v>
+        <v>497.5384259999999</v>
       </c>
       <c r="N8">
-        <v>4125.138492</v>
+        <v>4054.061574</v>
       </c>
       <c r="O8">
-        <v>1064.285730936</v>
+        <v>1045.947886092</v>
       </c>
       <c r="P8">
-        <v>3060.852761064</v>
+        <v>3008.113687908</v>
       </c>
       <c r="Q8">
-        <v>5419.852761064</v>
+        <v>5367.113687908</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08619541338580428</v>
+        <v>0.08652277554047763</v>
       </c>
       <c r="T8">
-        <v>0.9329194777322006</v>
+        <v>0.9404798046299684</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>10.6729444852969</v>
+        <v>9.148238130254489</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0830787632526442</v>
+        <v>0.08298352192263235</v>
       </c>
       <c r="C9">
-        <v>130321.0762815264</v>
+        <v>129240.9264476165</v>
       </c>
       <c r="D9">
-        <v>129972.6962815264</v>
+        <v>130305.6064476165</v>
       </c>
       <c r="E9">
-        <v>-4741.68</v>
+        <v>-3328.620000000001</v>
       </c>
       <c r="F9">
-        <v>9891.42</v>
+        <v>11304.48</v>
       </c>
       <c r="G9">
         <v>10239.8</v>
@@ -2031,45 +2031,45 @@
         <v>4551.6</v>
       </c>
       <c r="M9">
-        <v>497.538426</v>
+        <v>585.572064</v>
       </c>
       <c r="N9">
-        <v>4054.061574</v>
+        <v>3966.027936</v>
       </c>
       <c r="O9">
-        <v>1045.947886092</v>
+        <v>1023.235207488</v>
       </c>
       <c r="P9">
-        <v>3008.113687908</v>
+        <v>2942.792728512</v>
       </c>
       <c r="Q9">
-        <v>5367.113687908</v>
+        <v>5301.792728512</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08652277554047763</v>
+        <v>0.08685725426373081</v>
       </c>
       <c r="T9">
-        <v>0.9404798046299684</v>
+        <v>0.9482044864602961</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.258</v>
       </c>
       <c r="W9">
-        <v>0.0373226</v>
+        <v>0.0384356</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>9.148238130254487</v>
+        <v>7.772911789726364</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08298352192263235</v>
+        <v>0.08281037059262052</v>
       </c>
       <c r="C10">
-        <v>129240.9264476165</v>
+        <v>128437.4952814575</v>
       </c>
       <c r="D10">
-        <v>130305.6064476165</v>
+        <v>130915.2352814575</v>
       </c>
       <c r="E10">
-        <v>-3328.620000000001</v>
+        <v>-1915.560000000001</v>
       </c>
       <c r="F10">
-        <v>11304.48</v>
+        <v>12717.54</v>
       </c>
       <c r="G10">
         <v>10239.8</v>
@@ -2113,28 +2113,28 @@
         <v>4551.6</v>
       </c>
       <c r="M10">
-        <v>585.572064</v>
+        <v>658.7685719999999</v>
       </c>
       <c r="N10">
-        <v>3966.027936</v>
+        <v>3892.831428</v>
       </c>
       <c r="O10">
-        <v>1023.235207488</v>
+        <v>1004.350508424</v>
       </c>
       <c r="P10">
-        <v>2942.792728512</v>
+        <v>2888.480919576</v>
       </c>
       <c r="Q10">
-        <v>5301.792728512</v>
+        <v>5247.480919576001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08685725426373081</v>
+        <v>0.08719908416771485</v>
       </c>
       <c r="T10">
-        <v>0.9482044864602961</v>
+        <v>0.9560989415176643</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>7.772911789726364</v>
+        <v>6.909254924201212</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08281037059262052</v>
+        <v>0.08276335926260869</v>
       </c>
       <c r="C11">
-        <v>128437.4952814575</v>
+        <v>127190.9379871685</v>
       </c>
       <c r="D11">
-        <v>130915.2352814575</v>
+        <v>131081.7379871685</v>
       </c>
       <c r="E11">
-        <v>-1915.560000000001</v>
+        <v>-502.5000000000018</v>
       </c>
       <c r="F11">
-        <v>12717.54</v>
+        <v>14130.6</v>
       </c>
       <c r="G11">
         <v>10239.8</v>
@@ -2195,45 +2195,45 @@
         <v>4551.6</v>
       </c>
       <c r="M11">
-        <v>658.7685719999999</v>
+        <v>755.9870999999999</v>
       </c>
       <c r="N11">
-        <v>3892.831428</v>
+        <v>3795.612900000001</v>
       </c>
       <c r="O11">
-        <v>1004.350508424</v>
+        <v>979.2681282000002</v>
       </c>
       <c r="P11">
-        <v>2888.480919576</v>
+        <v>2816.3447718</v>
       </c>
       <c r="Q11">
-        <v>5247.480919576001</v>
+        <v>5175.344771800001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08719908416771485</v>
+        <v>0.08754851029178742</v>
       </c>
       <c r="T11">
-        <v>0.9560989415176643</v>
+        <v>0.9641688289096405</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.258</v>
       </c>
       <c r="W11">
-        <v>0.0384356</v>
+        <v>0.039697</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>6.909254924201212</v>
+        <v>6.020737655444122</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08276335926260869</v>
+        <v>0.08266811793259685</v>
       </c>
       <c r="C12">
-        <v>127190.9379871685</v>
+        <v>126116.501159878</v>
       </c>
       <c r="D12">
-        <v>131081.7379871685</v>
+        <v>131420.361159878</v>
       </c>
       <c r="E12">
-        <v>-502.5</v>
+        <v>910.5599999999995</v>
       </c>
       <c r="F12">
-        <v>14130.6</v>
+        <v>15543.66</v>
       </c>
       <c r="G12">
         <v>10239.8</v>
@@ -2277,45 +2277,45 @@
         <v>4551.6</v>
       </c>
       <c r="M12">
-        <v>755.9871000000001</v>
+        <v>844.0207380000001</v>
       </c>
       <c r="N12">
-        <v>3795.6129</v>
+        <v>3707.579262</v>
       </c>
       <c r="O12">
-        <v>979.2681282000001</v>
+        <v>956.5554495960001</v>
       </c>
       <c r="P12">
-        <v>2816.3447718</v>
+        <v>2751.023812404</v>
       </c>
       <c r="Q12">
-        <v>5175.3447718</v>
+        <v>5110.023812404001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08754851029178742</v>
+        <v>0.08790578868831106</v>
       </c>
       <c r="T12">
-        <v>0.9641688289096405</v>
+        <v>0.972420062085706</v>
       </c>
       <c r="U12">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V12">
         <v>0.258</v>
       </c>
       <c r="W12">
-        <v>0.039697</v>
+        <v>0.0402906</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>6.020737655444121</v>
+        <v>5.392758489306219</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08266811793259685</v>
+        <v>0.08251351660258502</v>
       </c>
       <c r="C13">
-        <v>126116.501159878</v>
+        <v>125256.8548479724</v>
       </c>
       <c r="D13">
-        <v>131420.361159878</v>
+        <v>131973.7748479724</v>
       </c>
       <c r="E13">
-        <v>910.5599999999995</v>
+        <v>2323.620000000001</v>
       </c>
       <c r="F13">
-        <v>15543.66</v>
+        <v>16956.72</v>
       </c>
       <c r="G13">
         <v>10239.8</v>
@@ -2359,28 +2359,28 @@
         <v>4551.6</v>
       </c>
       <c r="M13">
-        <v>844.0207380000001</v>
+        <v>920.749896</v>
       </c>
       <c r="N13">
-        <v>3707.579262</v>
+        <v>3630.850104</v>
       </c>
       <c r="O13">
-        <v>956.5554495960001</v>
+        <v>936.7593268320001</v>
       </c>
       <c r="P13">
-        <v>2751.023812404</v>
+        <v>2694.090777168</v>
       </c>
       <c r="Q13">
-        <v>5110.023812404001</v>
+        <v>5053.090777167999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08790578868831106</v>
+        <v>0.08827118704839206</v>
       </c>
       <c r="T13">
-        <v>0.972420062085706</v>
+        <v>0.9808588232885004</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.392758489306219</v>
+        <v>4.943361948530701</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08251351660258502</v>
+        <v>0.08235891527257316</v>
       </c>
       <c r="C14">
-        <v>125256.8548479724</v>
+        <v>124401.8891176207</v>
       </c>
       <c r="D14">
-        <v>131973.7748479724</v>
+        <v>132531.8691176207</v>
       </c>
       <c r="E14">
-        <v>2323.620000000001</v>
+        <v>3736.679999999998</v>
       </c>
       <c r="F14">
-        <v>16956.72</v>
+        <v>18369.78</v>
       </c>
       <c r="G14">
         <v>10239.8</v>
@@ -2441,28 +2441,28 @@
         <v>4551.6</v>
       </c>
       <c r="M14">
-        <v>920.749896</v>
+        <v>997.4790539999999</v>
       </c>
       <c r="N14">
-        <v>3630.850104</v>
+        <v>3554.120946</v>
       </c>
       <c r="O14">
-        <v>936.7593268320001</v>
+        <v>916.9632040680001</v>
       </c>
       <c r="P14">
-        <v>2694.090777168</v>
+        <v>2637.157741932</v>
       </c>
       <c r="Q14">
-        <v>5053.090777167999</v>
+        <v>4996.157741932</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08827118704839206</v>
+        <v>0.08864498537077375</v>
       </c>
       <c r="T14">
-        <v>0.9808588232885004</v>
+        <v>0.9894915790017037</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>4.943361948530701</v>
+        <v>4.563103337105263</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08235891527257316</v>
+        <v>0.08230819394256134</v>
       </c>
       <c r="C15">
-        <v>124401.8891176207</v>
+        <v>123172.9574445704</v>
       </c>
       <c r="D15">
-        <v>132531.8691176207</v>
+        <v>132715.9974445704</v>
       </c>
       <c r="E15">
-        <v>3736.679999999998</v>
+        <v>5149.74</v>
       </c>
       <c r="F15">
-        <v>18369.78</v>
+        <v>19782.84</v>
       </c>
       <c r="G15">
         <v>10239.8</v>
@@ -2523,45 +2523,45 @@
         <v>4551.6</v>
       </c>
       <c r="M15">
-        <v>997.4790539999999</v>
+        <v>1093.991052</v>
       </c>
       <c r="N15">
-        <v>3554.120946</v>
+        <v>3457.608948</v>
       </c>
       <c r="O15">
-        <v>916.9632040680001</v>
+        <v>892.063108584</v>
       </c>
       <c r="P15">
-        <v>2637.157741932</v>
+        <v>2565.545839416</v>
       </c>
       <c r="Q15">
-        <v>4996.157741932</v>
+        <v>4924.545839416</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08864498537077375</v>
+        <v>0.08902747667739691</v>
       </c>
       <c r="T15">
-        <v>0.9894915790017037</v>
+        <v>0.9983250964756794</v>
       </c>
       <c r="U15">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V15">
         <v>0.258</v>
       </c>
       <c r="W15">
-        <v>0.0402906</v>
+        <v>0.0410326</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y15">
-        <v>4.563103337105263</v>
+        <v>4.160545912764924</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08230819394256134</v>
+        <v>0.0821610126125495</v>
       </c>
       <c r="C16">
-        <v>123172.9574445704</v>
+        <v>122297.1024235923</v>
       </c>
       <c r="D16">
-        <v>132715.9974445704</v>
+        <v>133253.2024235923</v>
       </c>
       <c r="E16">
-        <v>5149.74</v>
+        <v>6562.800000000001</v>
       </c>
       <c r="F16">
-        <v>19782.84</v>
+        <v>21195.9</v>
       </c>
       <c r="G16">
         <v>10239.8</v>
@@ -2605,28 +2605,28 @@
         <v>4551.6</v>
       </c>
       <c r="M16">
-        <v>1093.991052</v>
+        <v>1172.13327</v>
       </c>
       <c r="N16">
-        <v>3457.608948</v>
+        <v>3379.46673</v>
       </c>
       <c r="O16">
-        <v>892.063108584</v>
+        <v>871.9024163400001</v>
       </c>
       <c r="P16">
-        <v>2565.545839416</v>
+        <v>2507.56431366</v>
       </c>
       <c r="Q16">
-        <v>4924.545839416</v>
+        <v>4866.56431366</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08902747667739691</v>
+        <v>0.08941896777947</v>
       </c>
       <c r="T16">
-        <v>0.9983250964756794</v>
+        <v>1.007366461419631</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>4.160545912764924</v>
+        <v>3.883176185247263</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0821610126125495</v>
+        <v>0.08201383128253767</v>
       </c>
       <c r="C17">
-        <v>122297.1024235923</v>
+        <v>121425.6140515161</v>
       </c>
       <c r="D17">
-        <v>133253.2024235923</v>
+        <v>133794.7740515161</v>
       </c>
       <c r="E17">
-        <v>6562.799999999997</v>
+        <v>7975.859999999999</v>
       </c>
       <c r="F17">
-        <v>21195.9</v>
+        <v>22608.96</v>
       </c>
       <c r="G17">
         <v>10239.8</v>
@@ -2687,28 +2687,28 @@
         <v>4551.6</v>
       </c>
       <c r="M17">
-        <v>1172.13327</v>
+        <v>1250.275488</v>
       </c>
       <c r="N17">
-        <v>3379.466730000001</v>
+        <v>3301.324512</v>
       </c>
       <c r="O17">
-        <v>871.9024163400002</v>
+        <v>851.7417240960001</v>
       </c>
       <c r="P17">
-        <v>2507.56431366</v>
+        <v>2449.582787904</v>
       </c>
       <c r="Q17">
-        <v>4866.56431366</v>
+        <v>4808.582787904</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08941896777947</v>
+        <v>0.08981978009825914</v>
       </c>
       <c r="T17">
-        <v>1.007366461419631</v>
+        <v>1.016623096957486</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>3.883176185247264</v>
+        <v>3.640477673669309</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08201383128253767</v>
+        <v>0.08186664995252584</v>
       </c>
       <c r="C18">
-        <v>121425.6140515161</v>
+        <v>120558.5457868021</v>
       </c>
       <c r="D18">
-        <v>133794.7740515161</v>
+        <v>134340.7657868021</v>
       </c>
       <c r="E18">
-        <v>7975.859999999999</v>
+        <v>9388.92</v>
       </c>
       <c r="F18">
-        <v>22608.96</v>
+        <v>24022.02</v>
       </c>
       <c r="G18">
         <v>10239.8</v>
@@ -2769,28 +2769,28 @@
         <v>4551.6</v>
       </c>
       <c r="M18">
-        <v>1250.275488</v>
+        <v>1328.417706</v>
       </c>
       <c r="N18">
-        <v>3301.324512</v>
+        <v>3223.182294</v>
       </c>
       <c r="O18">
-        <v>851.7417240960001</v>
+        <v>831.581031852</v>
       </c>
       <c r="P18">
-        <v>2449.582787904</v>
+        <v>2391.601262148</v>
       </c>
       <c r="Q18">
-        <v>4808.582787904</v>
+        <v>4750.601262148</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08981978009825914</v>
+        <v>0.09023025054521185</v>
       </c>
       <c r="T18">
-        <v>1.016623096957486</v>
+        <v>1.026102783954084</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.640477673669309</v>
+        <v>3.42633192815935</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08186664995252584</v>
+        <v>0.08171946862251399</v>
       </c>
       <c r="C19">
-        <v>120558.5457868021</v>
+        <v>119695.9519641029</v>
       </c>
       <c r="D19">
-        <v>134340.7657868021</v>
+        <v>134891.2319641029</v>
       </c>
       <c r="E19">
-        <v>9388.92</v>
+        <v>10801.98</v>
       </c>
       <c r="F19">
-        <v>24022.02</v>
+        <v>25435.08</v>
       </c>
       <c r="G19">
         <v>10239.8</v>
@@ -2851,28 +2851,28 @@
         <v>4551.6</v>
       </c>
       <c r="M19">
-        <v>1328.417706</v>
+        <v>1406.559924</v>
       </c>
       <c r="N19">
-        <v>3223.182294</v>
+        <v>3145.040076</v>
       </c>
       <c r="O19">
-        <v>831.581031852</v>
+        <v>811.4203396080001</v>
       </c>
       <c r="P19">
-        <v>2391.601262148</v>
+        <v>2333.619736392</v>
       </c>
       <c r="Q19">
-        <v>4750.601262148</v>
+        <v>4692.619736392</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09023025054521185</v>
+        <v>0.09065073246648048</v>
       </c>
       <c r="T19">
-        <v>1.026102783954084</v>
+        <v>1.035813682828649</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.42633192815935</v>
+        <v>3.235980154372719</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.081719468622514</v>
+        <v>0.08157228729250218</v>
       </c>
       <c r="C20">
-        <v>119695.9519641029</v>
+        <v>118837.8878122876</v>
       </c>
       <c r="D20">
-        <v>134891.2319641029</v>
+        <v>135446.2278122876</v>
       </c>
       <c r="E20">
-        <v>10801.98</v>
+        <v>12215.04</v>
       </c>
       <c r="F20">
-        <v>25435.08</v>
+        <v>26848.14</v>
       </c>
       <c r="G20">
         <v>10239.8</v>
@@ -2933,28 +2933,28 @@
         <v>4551.6</v>
       </c>
       <c r="M20">
-        <v>1406.559924</v>
+        <v>1484.702142</v>
       </c>
       <c r="N20">
-        <v>3145.040076</v>
+        <v>3066.897858</v>
       </c>
       <c r="O20">
-        <v>811.4203396080001</v>
+        <v>791.2596473640001</v>
       </c>
       <c r="P20">
-        <v>2333.619736392</v>
+        <v>2275.638210636</v>
       </c>
       <c r="Q20">
-        <v>4692.619736392</v>
+        <v>4634.638210636</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09065073246648048</v>
+        <v>0.09108159665741009</v>
       </c>
       <c r="T20">
-        <v>1.035813682828649</v>
+        <v>1.045764356984067</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.23598015437272</v>
+        <v>3.065665409405734</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08157228729250218</v>
+        <v>0.08179610596249033</v>
       </c>
       <c r="C21">
-        <v>118837.8878122876</v>
+        <v>116582.6424215831</v>
       </c>
       <c r="D21">
-        <v>135446.2278122876</v>
+        <v>134604.0424215831</v>
       </c>
       <c r="E21">
-        <v>12215.04</v>
+        <v>13628.1</v>
       </c>
       <c r="F21">
-        <v>26848.14</v>
+        <v>28261.2</v>
       </c>
       <c r="G21">
         <v>10239.8</v>
@@ -3015,45 +3015,45 @@
         <v>4551.6</v>
       </c>
       <c r="M21">
-        <v>1484.702142</v>
+        <v>1633.49736</v>
       </c>
       <c r="N21">
-        <v>3066.897858</v>
+        <v>2918.10264</v>
       </c>
       <c r="O21">
-        <v>791.2596473640001</v>
+        <v>752.87048112</v>
       </c>
       <c r="P21">
-        <v>2275.638210636</v>
+        <v>2165.23215888</v>
       </c>
       <c r="Q21">
-        <v>4634.638210636</v>
+        <v>4524.23215888</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09108159665741009</v>
+        <v>0.0915232324531129</v>
       </c>
       <c r="T21">
-        <v>1.045764356984067</v>
+        <v>1.05596379799337</v>
       </c>
       <c r="U21">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V21">
         <v>0.258</v>
       </c>
       <c r="W21">
-        <v>0.0410326</v>
+        <v>0.0428876</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>3.065665409405734</v>
+        <v>2.786414053341353</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08179610596249033</v>
+        <v>0.0816674746324785</v>
       </c>
       <c r="C22">
-        <v>116582.6424215831</v>
+        <v>115652.3121698877</v>
       </c>
       <c r="D22">
-        <v>134604.0424215831</v>
+        <v>135086.7721698877</v>
       </c>
       <c r="E22">
-        <v>13628.1</v>
+        <v>15041.16</v>
       </c>
       <c r="F22">
-        <v>28261.2</v>
+        <v>29674.26</v>
       </c>
       <c r="G22">
         <v>10239.8</v>
@@ -3097,28 +3097,28 @@
         <v>4551.6</v>
       </c>
       <c r="M22">
-        <v>1633.49736</v>
+        <v>1715.172228</v>
       </c>
       <c r="N22">
-        <v>2918.10264</v>
+        <v>2836.427772</v>
       </c>
       <c r="O22">
-        <v>752.87048112</v>
+        <v>731.7983651760001</v>
       </c>
       <c r="P22">
-        <v>2165.23215888</v>
+        <v>2104.629406824</v>
       </c>
       <c r="Q22">
-        <v>4524.23215888</v>
+        <v>4463.629406824</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0915232324531129</v>
+        <v>0.09197604890187151</v>
       </c>
       <c r="T22">
-        <v>1.05596379799337</v>
+        <v>1.066421452699111</v>
       </c>
       <c r="U22">
         <v>0.0578</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>2.786414053341353</v>
+        <v>2.653727669848908</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08166747463247849</v>
+        <v>0.08153884330246666</v>
       </c>
       <c r="C23">
-        <v>115652.3121698878</v>
+        <v>114725.4568023141</v>
       </c>
       <c r="D23">
-        <v>135086.7721698878</v>
+        <v>135572.9768023141</v>
       </c>
       <c r="E23">
-        <v>15041.16</v>
+        <v>16454.22</v>
       </c>
       <c r="F23">
-        <v>29674.26</v>
+        <v>31087.32</v>
       </c>
       <c r="G23">
         <v>10239.8</v>
@@ -3179,28 +3179,28 @@
         <v>4551.6</v>
       </c>
       <c r="M23">
-        <v>1715.172228</v>
+        <v>1796.847096</v>
       </c>
       <c r="N23">
-        <v>2836.427772</v>
+        <v>2754.752904</v>
       </c>
       <c r="O23">
-        <v>731.7983651760001</v>
+        <v>710.726249232</v>
       </c>
       <c r="P23">
-        <v>2104.629406824</v>
+        <v>2044.026654768</v>
       </c>
       <c r="Q23">
-        <v>4463.629406824</v>
+        <v>4403.026654768</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0919760489018715</v>
+        <v>0.0924404760288034</v>
       </c>
       <c r="T23">
-        <v>1.066421452699111</v>
+        <v>1.077147252397307</v>
       </c>
       <c r="U23">
         <v>0.0578</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.653727669848908</v>
+        <v>2.533103684855776</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08153884330246666</v>
+        <v>0.08200752197245484</v>
       </c>
       <c r="C24">
-        <v>114725.4568023141</v>
+        <v>111557.5083428833</v>
       </c>
       <c r="D24">
-        <v>135572.9768023141</v>
+        <v>133818.0883428833</v>
       </c>
       <c r="E24">
-        <v>16454.22</v>
+        <v>17867.28</v>
       </c>
       <c r="F24">
-        <v>31087.32</v>
+        <v>32500.38</v>
       </c>
       <c r="G24">
         <v>10239.8</v>
@@ -3261,45 +3261,45 @@
         <v>4551.6</v>
       </c>
       <c r="M24">
-        <v>1796.847096</v>
+        <v>1992.273294</v>
       </c>
       <c r="N24">
-        <v>2754.752904</v>
+        <v>2559.326706</v>
       </c>
       <c r="O24">
-        <v>710.726249232</v>
+        <v>660.3062901480001</v>
       </c>
       <c r="P24">
-        <v>2044.026654768</v>
+        <v>1899.020415852</v>
       </c>
       <c r="Q24">
-        <v>4403.026654768</v>
+        <v>4258.020415852</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.0924404760288034</v>
+        <v>0.09291696619799328</v>
       </c>
       <c r="T24">
-        <v>1.077147252397307</v>
+        <v>1.088151644295457</v>
       </c>
       <c r="U24">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V24">
         <v>0.258</v>
       </c>
       <c r="W24">
-        <v>0.0428876</v>
+        <v>0.0454846</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.533103684855776</v>
+        <v>2.28462631793929</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08200752197245484</v>
+        <v>0.08240348464244299</v>
       </c>
       <c r="C25">
-        <v>111557.5083428833</v>
+        <v>108696.8548126346</v>
       </c>
       <c r="D25">
-        <v>133818.0883428833</v>
+        <v>132370.4948126346</v>
       </c>
       <c r="E25">
-        <v>17867.28</v>
+        <v>19280.34</v>
       </c>
       <c r="F25">
-        <v>32500.38</v>
+        <v>33913.44</v>
       </c>
       <c r="G25">
         <v>10239.8</v>
@@ -3343,45 +3343,45 @@
         <v>4551.6</v>
       </c>
       <c r="M25">
-        <v>1992.273294</v>
+        <v>2173.851504</v>
       </c>
       <c r="N25">
-        <v>2559.326706</v>
+        <v>2377.748496</v>
       </c>
       <c r="O25">
-        <v>660.3062901480001</v>
+        <v>613.459111968</v>
       </c>
       <c r="P25">
-        <v>1899.020415852</v>
+        <v>1764.289384032</v>
       </c>
       <c r="Q25">
-        <v>4258.020415852</v>
+        <v>4123.289384032</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09291696619799328</v>
+        <v>0.09340599558216182</v>
       </c>
       <c r="T25">
-        <v>1.088151644295457</v>
+        <v>1.099445625454084</v>
       </c>
       <c r="U25">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V25">
         <v>0.258</v>
       </c>
       <c r="W25">
-        <v>0.0454846</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.28462631793929</v>
+        <v>2.093795271491553</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08240348464244299</v>
+        <v>0.08232159931243116</v>
       </c>
       <c r="C26">
-        <v>108696.8548126346</v>
+        <v>107580.583613115</v>
       </c>
       <c r="D26">
-        <v>132370.4948126346</v>
+        <v>132667.283613115</v>
       </c>
       <c r="E26">
-        <v>19280.34</v>
+        <v>20693.4</v>
       </c>
       <c r="F26">
-        <v>33913.44</v>
+        <v>35326.5</v>
       </c>
       <c r="G26">
         <v>10239.8</v>
@@ -3425,28 +3425,28 @@
         <v>4551.6</v>
       </c>
       <c r="M26">
-        <v>2173.851504</v>
+        <v>2264.42865</v>
       </c>
       <c r="N26">
-        <v>2377.748496</v>
+        <v>2287.17135</v>
       </c>
       <c r="O26">
-        <v>613.459111968</v>
+        <v>590.0902083000001</v>
       </c>
       <c r="P26">
-        <v>1764.289384032</v>
+        <v>1697.0811417</v>
       </c>
       <c r="Q26">
-        <v>4123.289384032</v>
+        <v>4056.0811417</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09340599558216182</v>
+        <v>0.0939080657499082</v>
       </c>
       <c r="T26">
-        <v>1.099445625454084</v>
+        <v>1.111040779443607</v>
       </c>
       <c r="U26">
         <v>0.0641</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.093795271491553</v>
+        <v>2.01004346063189</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08232159931243116</v>
+        <v>0.08449687798241931</v>
       </c>
       <c r="C27">
-        <v>107580.583613115</v>
+        <v>98709.85965428123</v>
       </c>
       <c r="D27">
-        <v>132667.283613115</v>
+        <v>125209.6196542812</v>
       </c>
       <c r="E27">
-        <v>20693.4</v>
+        <v>22106.46</v>
       </c>
       <c r="F27">
-        <v>35326.5</v>
+        <v>36739.56</v>
       </c>
       <c r="G27">
         <v>10239.8</v>
@@ -3507,45 +3507,45 @@
         <v>4551.6</v>
       </c>
       <c r="M27">
-        <v>2264.42865</v>
+        <v>2784.858648</v>
       </c>
       <c r="N27">
-        <v>2287.17135</v>
+        <v>1766.741352</v>
       </c>
       <c r="O27">
-        <v>590.0902083000001</v>
+        <v>455.8192688160001</v>
       </c>
       <c r="P27">
-        <v>1697.0811417</v>
+        <v>1310.922083184</v>
       </c>
       <c r="Q27">
-        <v>4056.0811417</v>
+        <v>3669.922083184</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0939080657499082</v>
+        <v>0.09442370538164771</v>
       </c>
       <c r="T27">
-        <v>1.111040779443607</v>
+        <v>1.122949315973389</v>
       </c>
       <c r="U27">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V27">
         <v>0.258</v>
       </c>
       <c r="W27">
-        <v>0.04756220000000001</v>
+        <v>0.0562436</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y27">
-        <v>2.01004346063189</v>
+        <v>1.634409704517255</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08449687798241931</v>
+        <v>0.08450180665240747</v>
       </c>
       <c r="C28">
-        <v>98709.85965428123</v>
+        <v>97280.85422568244</v>
       </c>
       <c r="D28">
-        <v>125209.6196542812</v>
+        <v>125193.6742256824</v>
       </c>
       <c r="E28">
-        <v>22106.46</v>
+        <v>23519.52</v>
       </c>
       <c r="F28">
-        <v>36739.56</v>
+        <v>38152.62</v>
       </c>
       <c r="G28">
         <v>10239.8</v>
@@ -3589,28 +3589,28 @@
         <v>4551.6</v>
       </c>
       <c r="M28">
-        <v>2784.858648</v>
+        <v>2891.968596000001</v>
       </c>
       <c r="N28">
-        <v>1766.741352</v>
+        <v>1659.631404</v>
       </c>
       <c r="O28">
-        <v>455.8192688160001</v>
+        <v>428.184902232</v>
       </c>
       <c r="P28">
-        <v>1310.922083184</v>
+        <v>1231.446501768</v>
       </c>
       <c r="Q28">
-        <v>3669.922083184</v>
+        <v>3590.446501768</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09442370538164771</v>
+        <v>0.09495347212658559</v>
       </c>
       <c r="T28">
-        <v>1.122949315973389</v>
+        <v>1.135184113777958</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>1.634409704517255</v>
+        <v>1.573876011757356</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08450180665240747</v>
+        <v>0.08450673532239564</v>
       </c>
       <c r="C29">
-        <v>97280.85422568244</v>
+        <v>95851.85285786301</v>
       </c>
       <c r="D29">
-        <v>125193.6742256824</v>
+        <v>125177.732857863</v>
       </c>
       <c r="E29">
-        <v>23519.52</v>
+        <v>24932.58</v>
       </c>
       <c r="F29">
-        <v>38152.62</v>
+        <v>39565.68</v>
       </c>
       <c r="G29">
         <v>10239.8</v>
@@ -3671,28 +3671,28 @@
         <v>4551.6</v>
       </c>
       <c r="M29">
-        <v>2891.968596000001</v>
+        <v>2999.078544</v>
       </c>
       <c r="N29">
-        <v>1659.631404</v>
+        <v>1552.521456</v>
       </c>
       <c r="O29">
-        <v>428.184902232</v>
+        <v>400.550535648</v>
       </c>
       <c r="P29">
-        <v>1231.446501768</v>
+        <v>1151.970920352</v>
       </c>
       <c r="Q29">
-        <v>3590.446501768</v>
+        <v>3510.970920352</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09495347212658559</v>
+        <v>0.09549795461443839</v>
       </c>
       <c r="T29">
-        <v>1.135184113777958</v>
+        <v>1.147758767077099</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>1.573876011757356</v>
+        <v>1.517666154194593</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08450673532239564</v>
+        <v>0.09446775755140904</v>
       </c>
       <c r="C30">
-        <v>95851.85285786301</v>
+        <v>68818.17168464491</v>
       </c>
       <c r="D30">
-        <v>125177.732857863</v>
+        <v>99557.11168464491</v>
       </c>
       <c r="E30">
-        <v>24932.58</v>
+        <v>26345.64000000001</v>
       </c>
       <c r="F30">
-        <v>39565.68</v>
+        <v>40978.74000000001</v>
       </c>
       <c r="G30">
         <v>10239.8</v>
@@ -3753,45 +3753,45 @@
         <v>4551.6</v>
       </c>
       <c r="M30">
-        <v>2999.078544</v>
+        <v>4860.078564000001</v>
       </c>
       <c r="N30">
-        <v>1552.521456</v>
+        <v>-308.4785640000009</v>
       </c>
       <c r="O30">
-        <v>400.550535648</v>
+        <v>-79.58746951200024</v>
       </c>
       <c r="P30">
-        <v>1151.970920352</v>
+        <v>-228.8910944880007</v>
       </c>
       <c r="Q30">
-        <v>3510.970920352</v>
+        <v>2130.108905511999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09549795461443839</v>
+        <v>0.09631574892565994</v>
       </c>
       <c r="T30">
-        <v>1.147758767077099</v>
+        <v>1.166645471724248</v>
       </c>
       <c r="U30">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V30">
-        <v>0.258</v>
+        <v>0.2416242421878676</v>
       </c>
       <c r="W30">
-        <v>0.0562436</v>
+        <v>0.08994336487651891</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y30">
-        <v>1.517666154194593</v>
+        <v>0.9365280704956108</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09446775755140904</v>
+        <v>0.09519575755140904</v>
       </c>
       <c r="C31">
-        <v>68818.17168464491</v>
+        <v>65937.82823968533</v>
       </c>
       <c r="D31">
-        <v>99557.11168464491</v>
+        <v>98089.82823968532</v>
       </c>
       <c r="E31">
-        <v>26345.64</v>
+        <v>27758.7</v>
       </c>
       <c r="F31">
-        <v>40978.74</v>
+        <v>42391.8</v>
       </c>
       <c r="G31">
         <v>10239.8</v>
@@ -3835,37 +3835,37 @@
         <v>4551.6</v>
       </c>
       <c r="M31">
-        <v>4860.078564</v>
+        <v>5027.66748</v>
       </c>
       <c r="N31">
-        <v>-308.478564</v>
+        <v>-476.0674799999997</v>
       </c>
       <c r="O31">
-        <v>-79.587469512</v>
+        <v>-122.8254098399999</v>
       </c>
       <c r="P31">
-        <v>-228.891094488</v>
+        <v>-353.2420701599998</v>
       </c>
       <c r="Q31">
-        <v>2130.108905512</v>
+        <v>2005.75792984</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09631574892565994</v>
+        <v>0.09703740248174079</v>
       </c>
       <c r="T31">
-        <v>1.166645471724248</v>
+        <v>1.183311835606023</v>
       </c>
       <c r="U31">
         <v>0.1186</v>
       </c>
       <c r="V31">
-        <v>0.2416242421878677</v>
+        <v>0.2335701007816054</v>
       </c>
       <c r="W31">
-        <v>0.08994336487651891</v>
+        <v>0.09089858604730161</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.936528070495611</v>
+        <v>0.9053104681457573</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09519575755140904</v>
+        <v>0.09592375755140904</v>
       </c>
       <c r="C32">
-        <v>65937.82823968533</v>
+        <v>63100.10659325446</v>
       </c>
       <c r="D32">
-        <v>98089.82823968532</v>
+        <v>96665.16659325446</v>
       </c>
       <c r="E32">
-        <v>27758.7</v>
+        <v>29171.76</v>
       </c>
       <c r="F32">
-        <v>42391.8</v>
+        <v>43804.86</v>
       </c>
       <c r="G32">
         <v>10239.8</v>
@@ -3917,37 +3917,37 @@
         <v>4551.6</v>
       </c>
       <c r="M32">
-        <v>5027.66748</v>
+        <v>5195.256396000001</v>
       </c>
       <c r="N32">
-        <v>-476.0674799999997</v>
+        <v>-643.6563960000003</v>
       </c>
       <c r="O32">
-        <v>-122.8254098399999</v>
+        <v>-166.0633501680001</v>
       </c>
       <c r="P32">
-        <v>-353.2420701599998</v>
+        <v>-477.5930458320003</v>
       </c>
       <c r="Q32">
-        <v>2005.75792984</v>
+        <v>1881.406954168</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09703740248174079</v>
+        <v>0.0977799735322008</v>
       </c>
       <c r="T32">
-        <v>1.183311835606023</v>
+        <v>1.200461282498864</v>
       </c>
       <c r="U32">
         <v>0.1186</v>
       </c>
       <c r="V32">
-        <v>0.2335701007816054</v>
+        <v>0.2260355814015536</v>
       </c>
       <c r="W32">
-        <v>0.09089858604730161</v>
+        <v>0.09179218004577576</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.9053104681457573</v>
+        <v>0.8761069046571844</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09592375755140904</v>
+        <v>0.09665175755140903</v>
       </c>
       <c r="C33">
-        <v>63100.10659325446</v>
+        <v>60303.17620866165</v>
       </c>
       <c r="D33">
-        <v>96665.16659325446</v>
+        <v>95281.29620866165</v>
       </c>
       <c r="E33">
-        <v>29171.76</v>
+        <v>30584.82</v>
       </c>
       <c r="F33">
-        <v>43804.86</v>
+        <v>45217.92</v>
       </c>
       <c r="G33">
         <v>10239.8</v>
@@ -3999,37 +3999,37 @@
         <v>4551.6</v>
       </c>
       <c r="M33">
-        <v>5195.256396000001</v>
+        <v>5362.845312</v>
       </c>
       <c r="N33">
-        <v>-643.6563960000003</v>
+        <v>-811.245312</v>
       </c>
       <c r="O33">
-        <v>-166.0633501680001</v>
+        <v>-209.301290496</v>
       </c>
       <c r="P33">
-        <v>-477.5930458320003</v>
+        <v>-601.944021504</v>
       </c>
       <c r="Q33">
-        <v>1881.406954168</v>
+        <v>1757.055978496</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.0977799735322008</v>
+        <v>0.09854438490767435</v>
       </c>
       <c r="T33">
-        <v>1.200461282498864</v>
+        <v>1.218115124888553</v>
       </c>
       <c r="U33">
         <v>0.1186</v>
       </c>
       <c r="V33">
-        <v>0.2260355814015536</v>
+        <v>0.2189719694827551</v>
       </c>
       <c r="W33">
-        <v>0.09179218004577576</v>
+        <v>0.09262992441934526</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.8761069046571844</v>
+        <v>0.8487285638866475</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09665175755140903</v>
+        <v>0.09737975755140904</v>
       </c>
       <c r="C34">
-        <v>60303.17620866165</v>
+        <v>57545.30989446423</v>
       </c>
       <c r="D34">
-        <v>95281.29620866165</v>
+        <v>93936.48989446423</v>
       </c>
       <c r="E34">
-        <v>30584.82</v>
+        <v>31997.88</v>
       </c>
       <c r="F34">
-        <v>45217.92</v>
+        <v>46630.98</v>
       </c>
       <c r="G34">
         <v>10239.8</v>
@@ -4081,37 +4081,37 @@
         <v>4551.6</v>
       </c>
       <c r="M34">
-        <v>5362.845312</v>
+        <v>5530.434228000001</v>
       </c>
       <c r="N34">
-        <v>-811.245312</v>
+        <v>-978.8342280000006</v>
       </c>
       <c r="O34">
-        <v>-209.301290496</v>
+        <v>-252.5392308240002</v>
       </c>
       <c r="P34">
-        <v>-601.944021504</v>
+        <v>-726.2949971760005</v>
       </c>
       <c r="Q34">
-        <v>1757.055978496</v>
+        <v>1632.705002824</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09854438490767435</v>
+        <v>0.09933161453316203</v>
       </c>
       <c r="T34">
-        <v>1.218115124888553</v>
+        <v>1.236295947648084</v>
       </c>
       <c r="U34">
         <v>0.1186</v>
       </c>
       <c r="V34">
-        <v>0.2189719694827551</v>
+        <v>0.2123364552560049</v>
       </c>
       <c r="W34">
-        <v>0.09262992441934526</v>
+        <v>0.09341689640663783</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.8487285638866475</v>
+        <v>0.823009516496143</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09737975755140904</v>
+        <v>0.1271620806483054</v>
       </c>
       <c r="C35">
-        <v>57545.30989446423</v>
+        <v>21747.10548403124</v>
       </c>
       <c r="D35">
-        <v>93936.48989446423</v>
+        <v>59551.34548403124</v>
       </c>
       <c r="E35">
-        <v>31997.88</v>
+        <v>33410.94</v>
       </c>
       <c r="F35">
-        <v>46630.98</v>
+        <v>48044.04</v>
       </c>
       <c r="G35">
         <v>10239.8</v>
@@ -4163,45 +4163,45 @@
         <v>4551.6</v>
       </c>
       <c r="M35">
-        <v>5530.434228000001</v>
+        <v>9647.243232000001</v>
       </c>
       <c r="N35">
-        <v>-978.8342280000006</v>
+        <v>-5095.643232</v>
       </c>
       <c r="O35">
-        <v>-252.5392308240002</v>
+        <v>-1314.675953856</v>
       </c>
       <c r="P35">
-        <v>-726.2949971760005</v>
+        <v>-3780.967278144</v>
       </c>
       <c r="Q35">
-        <v>1632.705002824</v>
+        <v>-1421.967278144</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09933161453316203</v>
+        <v>0.101818946718356</v>
       </c>
       <c r="T35">
-        <v>1.236295947648084</v>
+        <v>1.293740108968961</v>
       </c>
       <c r="U35">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.2123364552560049</v>
+        <v>0.1217252195015456</v>
       </c>
       <c r="W35">
-        <v>0.09341689640663783</v>
+        <v>0.1763575759240897</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.823009516496143</v>
+        <v>0.4718031763625797</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1271620806483054</v>
+        <v>0.1287120806483054</v>
       </c>
       <c r="C36">
-        <v>21747.10548403124</v>
+        <v>19220.76277807934</v>
       </c>
       <c r="D36">
-        <v>59551.34548403124</v>
+        <v>58438.06277807934</v>
       </c>
       <c r="E36">
-        <v>33410.94</v>
+        <v>34824.00000000001</v>
       </c>
       <c r="F36">
-        <v>48044.04</v>
+        <v>49457.10000000001</v>
       </c>
       <c r="G36">
         <v>10239.8</v>
@@ -4245,37 +4245,37 @@
         <v>4551.6</v>
       </c>
       <c r="M36">
-        <v>9647.243232000001</v>
+        <v>9930.985680000002</v>
       </c>
       <c r="N36">
-        <v>-5095.643232</v>
+        <v>-5379.385680000001</v>
       </c>
       <c r="O36">
-        <v>-1314.675953856</v>
+        <v>-1387.88150544</v>
       </c>
       <c r="P36">
-        <v>-3780.967278144</v>
+        <v>-3991.504174560001</v>
       </c>
       <c r="Q36">
-        <v>-1421.967278144</v>
+        <v>-1632.504174560001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.101818946718356</v>
+        <v>0.1026807766678692</v>
       </c>
       <c r="T36">
-        <v>1.293740108968961</v>
+        <v>1.313643802953099</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.1217252195015456</v>
+        <v>0.1182473560872157</v>
       </c>
       <c r="W36">
-        <v>0.1763575759240897</v>
+        <v>0.1770559308976871</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.4718031763625797</v>
+        <v>0.4583230856093632</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1287120806483054</v>
+        <v>0.1302620806483054</v>
       </c>
       <c r="C37">
-        <v>19220.76277807934</v>
+        <v>16735.28073246116</v>
       </c>
       <c r="D37">
-        <v>58438.06277807934</v>
+        <v>57365.64073246117</v>
       </c>
       <c r="E37">
-        <v>34824.00000000001</v>
+        <v>36237.06</v>
       </c>
       <c r="F37">
-        <v>49457.10000000001</v>
+        <v>50870.16</v>
       </c>
       <c r="G37">
         <v>10239.8</v>
@@ -4327,37 +4327,37 @@
         <v>4551.6</v>
       </c>
       <c r="M37">
-        <v>9930.985680000002</v>
+        <v>10214.728128</v>
       </c>
       <c r="N37">
-        <v>-5379.385680000001</v>
+        <v>-5663.128128</v>
       </c>
       <c r="O37">
-        <v>-1387.88150544</v>
+        <v>-1461.087057024</v>
       </c>
       <c r="P37">
-        <v>-3991.504174560001</v>
+        <v>-4202.041070976</v>
       </c>
       <c r="Q37">
-        <v>-1632.504174560001</v>
+        <v>-1843.041070976</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1026807766678692</v>
+        <v>0.1035695388033046</v>
       </c>
       <c r="T37">
-        <v>1.313643802953099</v>
+        <v>1.334169487374241</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.1182473560872157</v>
+        <v>0.1149627073070153</v>
       </c>
       <c r="W37">
-        <v>0.1770559308976871</v>
+        <v>0.1777154883727513</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.4583230856093632</v>
+        <v>0.4455918887868809</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1302620806483054</v>
+        <v>0.1318120806483055</v>
       </c>
       <c r="C38">
-        <v>16735.28073246119</v>
+        <v>14288.45033108129</v>
       </c>
       <c r="D38">
-        <v>57365.64073246119</v>
+        <v>56331.87033108129</v>
       </c>
       <c r="E38">
-        <v>36237.06</v>
+        <v>37650.12</v>
       </c>
       <c r="F38">
-        <v>50870.16</v>
+        <v>52283.22</v>
       </c>
       <c r="G38">
         <v>10239.8</v>
@@ -4409,37 +4409,37 @@
         <v>4551.6</v>
       </c>
       <c r="M38">
-        <v>10214.728128</v>
+        <v>10498.470576</v>
       </c>
       <c r="N38">
-        <v>-5663.128127999998</v>
+        <v>-5946.870575999999</v>
       </c>
       <c r="O38">
-        <v>-1461.087057024</v>
+        <v>-1534.292608608</v>
       </c>
       <c r="P38">
-        <v>-4202.041070975999</v>
+        <v>-4412.577967392</v>
       </c>
       <c r="Q38">
-        <v>-1843.041070975999</v>
+        <v>-2053.577967392</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1035695388033046</v>
+        <v>0.1044865156097063</v>
       </c>
       <c r="T38">
-        <v>1.334169487374241</v>
+        <v>1.355346780824626</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.1149627073070153</v>
+        <v>0.1118556071095284</v>
       </c>
       <c r="W38">
-        <v>0.1777154883727513</v>
+        <v>0.1783393940924067</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.4455918887868809</v>
+        <v>0.4335488647656138</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1318120806483055</v>
+        <v>0.1333620806483055</v>
       </c>
       <c r="C39">
-        <v>14288.45033108129</v>
+        <v>11878.21897143904</v>
       </c>
       <c r="D39">
-        <v>56331.87033108129</v>
+        <v>55334.69897143904</v>
       </c>
       <c r="E39">
-        <v>37650.12</v>
+        <v>39063.18</v>
       </c>
       <c r="F39">
-        <v>52283.22</v>
+        <v>53696.28</v>
       </c>
       <c r="G39">
         <v>10239.8</v>
@@ -4491,37 +4491,37 @@
         <v>4551.6</v>
       </c>
       <c r="M39">
-        <v>10498.470576</v>
+        <v>10782.213024</v>
       </c>
       <c r="N39">
-        <v>-5946.870575999999</v>
+        <v>-6230.613024</v>
       </c>
       <c r="O39">
-        <v>-1534.292608608</v>
+        <v>-1607.498160192</v>
       </c>
       <c r="P39">
-        <v>-4412.577967392</v>
+        <v>-4623.114863808</v>
       </c>
       <c r="Q39">
-        <v>-2053.577967392</v>
+        <v>-2264.114863808</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1044865156097063</v>
+        <v>0.1054330723130887</v>
       </c>
       <c r="T39">
-        <v>1.355346780824626</v>
+        <v>1.37720721277341</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.1118556071095284</v>
+        <v>0.1089120385013829</v>
       </c>
       <c r="W39">
-        <v>0.1783393940924067</v>
+        <v>0.1789304626689223</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.4335488647656138</v>
+        <v>0.4221396841138871</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1333620806483055</v>
+        <v>0.1349120806483055</v>
       </c>
       <c r="C40">
-        <v>11878.21897143904</v>
+        <v>9502.676861474283</v>
       </c>
       <c r="D40">
-        <v>55334.69897143904</v>
+        <v>54372.21686147428</v>
       </c>
       <c r="E40">
-        <v>39063.18</v>
+        <v>40476.24000000001</v>
       </c>
       <c r="F40">
-        <v>53696.28</v>
+        <v>55109.34</v>
       </c>
       <c r="G40">
         <v>10239.8</v>
@@ -4573,37 +4573,37 @@
         <v>4551.6</v>
       </c>
       <c r="M40">
-        <v>10782.213024</v>
+        <v>11065.955472</v>
       </c>
       <c r="N40">
-        <v>-6230.613024</v>
+        <v>-6514.355472000001</v>
       </c>
       <c r="O40">
-        <v>-1607.498160192</v>
+        <v>-1680.703711776</v>
       </c>
       <c r="P40">
-        <v>-4623.114863808</v>
+        <v>-4833.651760224001</v>
       </c>
       <c r="Q40">
-        <v>-2264.114863808</v>
+        <v>-2474.651760224001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1054330723130887</v>
+        <v>0.1064106636624835</v>
       </c>
       <c r="T40">
-        <v>1.37720721277341</v>
+        <v>1.399784380195925</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.1089120385013829</v>
+        <v>0.1061194221295526</v>
       </c>
       <c r="W40">
-        <v>0.1789304626689223</v>
+        <v>0.1794912200363859</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4221396841138871</v>
+        <v>0.4113155896494285</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1349120806483055</v>
+        <v>0.1364620806483055</v>
       </c>
       <c r="C41">
-        <v>9502.676861474283</v>
+        <v>7160.044811807667</v>
       </c>
       <c r="D41">
-        <v>54372.21686147428</v>
+        <v>53442.64481180767</v>
       </c>
       <c r="E41">
-        <v>40476.24000000001</v>
+        <v>41889.3</v>
       </c>
       <c r="F41">
-        <v>55109.34</v>
+        <v>56522.4</v>
       </c>
       <c r="G41">
         <v>10239.8</v>
@@ -4655,37 +4655,37 @@
         <v>4551.6</v>
       </c>
       <c r="M41">
-        <v>11065.955472</v>
+        <v>11349.69792</v>
       </c>
       <c r="N41">
-        <v>-6514.355472000001</v>
+        <v>-6798.09792</v>
       </c>
       <c r="O41">
-        <v>-1680.703711776</v>
+        <v>-1753.90926336</v>
       </c>
       <c r="P41">
-        <v>-4833.651760224001</v>
+        <v>-5044.18865664</v>
       </c>
       <c r="Q41">
-        <v>-2474.651760224001</v>
+        <v>-2685.18865664</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1064106636624835</v>
+        <v>0.1074208413901916</v>
       </c>
       <c r="T41">
-        <v>1.399784380195925</v>
+        <v>1.423114119865857</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.1061194221295526</v>
+        <v>0.1034664365763137</v>
       </c>
       <c r="W41">
-        <v>0.1794912200363859</v>
+        <v>0.1800239395354762</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.4113155896494285</v>
+        <v>0.4010326999081928</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1364620806483055</v>
+        <v>0.1380120806483054</v>
       </c>
       <c r="C42">
-        <v>7160.044811807667</v>
+        <v>4848.663259187728</v>
       </c>
       <c r="D42">
-        <v>53442.64481180767</v>
+        <v>52544.32325918773</v>
       </c>
       <c r="E42">
-        <v>41889.3</v>
+        <v>43302.36000000001</v>
       </c>
       <c r="F42">
-        <v>56522.4</v>
+        <v>57935.46000000001</v>
       </c>
       <c r="G42">
         <v>10239.8</v>
@@ -4737,37 +4737,37 @@
         <v>4551.6</v>
       </c>
       <c r="M42">
-        <v>11349.69792</v>
+        <v>11633.440368</v>
       </c>
       <c r="N42">
-        <v>-6798.09792</v>
+        <v>-7081.840368000001</v>
       </c>
       <c r="O42">
-        <v>-1753.90926336</v>
+        <v>-1827.114814944</v>
       </c>
       <c r="P42">
-        <v>-5044.18865664</v>
+        <v>-5254.725553056001</v>
       </c>
       <c r="Q42">
-        <v>-2685.18865664</v>
+        <v>-2895.725553056001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1074208413901916</v>
+        <v>0.1084652624307033</v>
       </c>
       <c r="T42">
-        <v>1.423114119865857</v>
+        <v>1.447234698168668</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.1034664365763137</v>
+        <v>0.1009428649525012</v>
       </c>
       <c r="W42">
-        <v>0.1800239395354762</v>
+        <v>0.1805306727175378</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.4010326999081928</v>
+        <v>0.3912514145445783</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1380120806483054</v>
+        <v>0.1395620806483054</v>
       </c>
       <c r="C43">
-        <v>4848.663259187728</v>
+        <v>2566.982378671746</v>
       </c>
       <c r="D43">
-        <v>52544.32325918773</v>
+        <v>51675.70237867175</v>
       </c>
       <c r="E43">
-        <v>43302.36000000001</v>
+        <v>44715.42000000001</v>
       </c>
       <c r="F43">
-        <v>57935.46000000001</v>
+        <v>59348.52</v>
       </c>
       <c r="G43">
         <v>10239.8</v>
@@ -4819,37 +4819,37 @@
         <v>4551.6</v>
       </c>
       <c r="M43">
-        <v>11633.440368</v>
+        <v>11917.182816</v>
       </c>
       <c r="N43">
-        <v>-7081.840368000001</v>
+        <v>-7365.582816</v>
       </c>
       <c r="O43">
-        <v>-1827.114814944</v>
+        <v>-1900.320366528</v>
       </c>
       <c r="P43">
-        <v>-5254.725553056001</v>
+        <v>-5465.262449472</v>
       </c>
       <c r="Q43">
-        <v>-2895.725553056001</v>
+        <v>-3106.262449472</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1084652624307033</v>
+        <v>0.1095456979898534</v>
       </c>
       <c r="T43">
-        <v>1.447234698168668</v>
+        <v>1.472187020550887</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.1009428649525012</v>
+        <v>0.09853946340601309</v>
       </c>
       <c r="W43">
-        <v>0.1805306727175378</v>
+        <v>0.1810132757480726</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3912514145445783</v>
+        <v>0.3819359046744694</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1395620806483054</v>
+        <v>0.1411120806483054</v>
       </c>
       <c r="C44">
-        <v>2566.982378671753</v>
+        <v>313.5531606027944</v>
       </c>
       <c r="D44">
-        <v>51675.70237867175</v>
+        <v>50835.3331606028</v>
       </c>
       <c r="E44">
-        <v>44715.42</v>
+        <v>46128.48</v>
       </c>
       <c r="F44">
-        <v>59348.52</v>
+        <v>60761.58</v>
       </c>
       <c r="G44">
         <v>10239.8</v>
@@ -4901,37 +4901,37 @@
         <v>4551.6</v>
       </c>
       <c r="M44">
-        <v>11917.182816</v>
+        <v>12200.925264</v>
       </c>
       <c r="N44">
-        <v>-7365.582816</v>
+        <v>-7649.325264000001</v>
       </c>
       <c r="O44">
-        <v>-1900.320366528</v>
+        <v>-1973.525918112</v>
       </c>
       <c r="P44">
-        <v>-5465.262449472</v>
+        <v>-5675.799345888001</v>
       </c>
       <c r="Q44">
-        <v>-3106.262449472</v>
+        <v>-3316.799345888001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1095456979898534</v>
+        <v>0.1106640435686227</v>
       </c>
       <c r="T44">
-        <v>1.472187020550886</v>
+        <v>1.498014863016692</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.09853946340601309</v>
+        <v>0.09624784797796626</v>
       </c>
       <c r="W44">
-        <v>0.1810132757480726</v>
+        <v>0.1814734321260244</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3819359046744694</v>
+        <v>0.3730536743332026</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1411120806483054</v>
+        <v>0.1426620806483054</v>
       </c>
       <c r="C45">
-        <v>313.5531606027944</v>
+        <v>-1912.980655688923</v>
       </c>
       <c r="D45">
-        <v>50835.3331606028</v>
+        <v>50021.85934431108</v>
       </c>
       <c r="E45">
-        <v>46128.48</v>
+        <v>47541.54</v>
       </c>
       <c r="F45">
-        <v>60761.58</v>
+        <v>62174.64</v>
       </c>
       <c r="G45">
         <v>10239.8</v>
@@ -4983,37 +4983,37 @@
         <v>4551.6</v>
       </c>
       <c r="M45">
-        <v>12200.925264</v>
+        <v>12484.667712</v>
       </c>
       <c r="N45">
-        <v>-7649.325264000001</v>
+        <v>-7933.067712</v>
       </c>
       <c r="O45">
-        <v>-1973.525918112</v>
+        <v>-2046.731469696</v>
       </c>
       <c r="P45">
-        <v>-5675.799345888001</v>
+        <v>-5886.336242304</v>
       </c>
       <c r="Q45">
-        <v>-3316.799345888001</v>
+        <v>-3527.336242304</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1106640435686227</v>
+        <v>0.1118223300609196</v>
       </c>
       <c r="T45">
-        <v>1.498014863016692</v>
+        <v>1.524765128427704</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.09624784797796626</v>
+        <v>0.09406039688755796</v>
       </c>
       <c r="W45">
-        <v>0.1814734321260244</v>
+        <v>0.1819126723049784</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3730536743332026</v>
+        <v>0.3645751817347207</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1426620806483054</v>
+        <v>0.1442120806483054</v>
       </c>
       <c r="C46">
-        <v>-1912.980655688923</v>
+        <v>-4113.889885914679</v>
       </c>
       <c r="D46">
-        <v>50021.85934431108</v>
+        <v>49234.01011408532</v>
       </c>
       <c r="E46">
-        <v>47541.54</v>
+        <v>48954.60000000001</v>
       </c>
       <c r="F46">
-        <v>62174.64</v>
+        <v>63587.7</v>
       </c>
       <c r="G46">
         <v>10239.8</v>
@@ -5065,37 +5065,37 @@
         <v>4551.6</v>
       </c>
       <c r="M46">
-        <v>12484.667712</v>
+        <v>12768.41016</v>
       </c>
       <c r="N46">
-        <v>-7933.067712</v>
+        <v>-8216.810160000001</v>
       </c>
       <c r="O46">
-        <v>-2046.731469696</v>
+        <v>-2119.93702128</v>
       </c>
       <c r="P46">
-        <v>-5886.336242304</v>
+        <v>-6096.87313872</v>
       </c>
       <c r="Q46">
-        <v>-3527.336242304</v>
+        <v>-3737.87313872</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1118223300609196</v>
+        <v>0.1130227360620272</v>
       </c>
       <c r="T46">
-        <v>1.524765128427704</v>
+        <v>1.552488130762753</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.09406039688755796</v>
+        <v>0.09197016584561221</v>
       </c>
       <c r="W46">
-        <v>0.1819126723049784</v>
+        <v>0.1823323906982011</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3645751817347207</v>
+        <v>0.3564735110295048</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1442120806483054</v>
+        <v>0.1457620806483055</v>
       </c>
       <c r="C47">
-        <v>-4113.889885914679</v>
+        <v>-6290.366525323414</v>
       </c>
       <c r="D47">
-        <v>49234.01011408532</v>
+        <v>48470.59347467659</v>
       </c>
       <c r="E47">
-        <v>48954.60000000001</v>
+        <v>50367.66</v>
       </c>
       <c r="F47">
-        <v>63587.7</v>
+        <v>65000.76</v>
       </c>
       <c r="G47">
         <v>10239.8</v>
@@ -5147,37 +5147,37 @@
         <v>4551.6</v>
       </c>
       <c r="M47">
-        <v>12768.41016</v>
+        <v>13052.152608</v>
       </c>
       <c r="N47">
-        <v>-8216.810160000001</v>
+        <v>-8500.552608</v>
       </c>
       <c r="O47">
-        <v>-2119.93702128</v>
+        <v>-2193.142572864</v>
       </c>
       <c r="P47">
-        <v>-6096.87313872</v>
+        <v>-6307.410035135999</v>
       </c>
       <c r="Q47">
-        <v>-3737.87313872</v>
+        <v>-3948.410035135999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1130227360620272</v>
+        <v>0.1142676015446573</v>
       </c>
       <c r="T47">
-        <v>1.552488130762753</v>
+        <v>1.581237910962063</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.09197016584561221</v>
+        <v>0.08997081441418588</v>
       </c>
       <c r="W47">
-        <v>0.1823323906982011</v>
+        <v>0.1827338604656315</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3564735110295048</v>
+        <v>0.3487240868766894</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1457620806483055</v>
+        <v>0.1473120806483054</v>
       </c>
       <c r="C48">
-        <v>-6290.366525323414</v>
+        <v>-8443.529766296648</v>
       </c>
       <c r="D48">
-        <v>48470.59347467659</v>
+        <v>47730.49023370336</v>
       </c>
       <c r="E48">
-        <v>50367.66</v>
+        <v>51780.72000000001</v>
       </c>
       <c r="F48">
-        <v>65000.76</v>
+        <v>66413.82000000001</v>
       </c>
       <c r="G48">
         <v>10239.8</v>
@@ -5229,37 +5229,37 @@
         <v>4551.6</v>
       </c>
       <c r="M48">
-        <v>13052.152608</v>
+        <v>13335.895056</v>
       </c>
       <c r="N48">
-        <v>-8500.552608</v>
+        <v>-8784.295056000001</v>
       </c>
       <c r="O48">
-        <v>-2193.142572864</v>
+        <v>-2266.348124448</v>
       </c>
       <c r="P48">
-        <v>-6307.410035135999</v>
+        <v>-6517.946931552</v>
       </c>
       <c r="Q48">
-        <v>-3948.410035135999</v>
+        <v>-4158.946931552</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1142676015446573</v>
+        <v>0.1155594430832358</v>
       </c>
       <c r="T48">
-        <v>1.581237910962063</v>
+        <v>1.611072588527385</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.08997081441418588</v>
+        <v>0.08805654176707553</v>
       </c>
       <c r="W48">
-        <v>0.1827338604656315</v>
+        <v>0.1831182464131712</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3487240868766894</v>
+        <v>0.3413044254537811</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1473120806483054</v>
+        <v>0.1488620806483054</v>
       </c>
       <c r="C49">
-        <v>-8443.529766296648</v>
+        <v>-10574.43147293462</v>
       </c>
       <c r="D49">
-        <v>47730.49023370336</v>
+        <v>47012.64852706539</v>
       </c>
       <c r="E49">
-        <v>51780.72000000001</v>
+        <v>53193.78000000001</v>
       </c>
       <c r="F49">
-        <v>66413.82000000001</v>
+        <v>67826.88</v>
       </c>
       <c r="G49">
         <v>10239.8</v>
@@ -5311,37 +5311,37 @@
         <v>4551.6</v>
       </c>
       <c r="M49">
-        <v>13335.895056</v>
+        <v>13619.637504</v>
       </c>
       <c r="N49">
-        <v>-8784.295056000001</v>
+        <v>-9068.037504000002</v>
       </c>
       <c r="O49">
-        <v>-2266.348124448</v>
+        <v>-2339.553676032001</v>
       </c>
       <c r="P49">
-        <v>-6517.946931552</v>
+        <v>-6728.483827968001</v>
       </c>
       <c r="Q49">
-        <v>-4158.946931552</v>
+        <v>-4369.483827968001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1155594430832358</v>
+        <v>0.1169009708348364</v>
       </c>
       <c r="T49">
-        <v>1.611072588527385</v>
+        <v>1.642054753691373</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.08805654176707553</v>
+        <v>0.08622203048026145</v>
       </c>
       <c r="W49">
-        <v>0.1831182464131712</v>
+        <v>0.1834866162795635</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3413044254537811</v>
+        <v>0.3341939165901606</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1488620806483054</v>
+        <v>0.1504120806483054</v>
       </c>
       <c r="C50">
-        <v>-10574.43147293461</v>
+        <v>-12684.06116895213</v>
       </c>
       <c r="D50">
-        <v>47012.6485270654</v>
+        <v>46316.07883104787</v>
       </c>
       <c r="E50">
-        <v>53193.78000000001</v>
+        <v>54606.84</v>
       </c>
       <c r="F50">
-        <v>67826.88</v>
+        <v>69239.94</v>
       </c>
       <c r="G50">
         <v>10239.8</v>
@@ -5393,37 +5393,37 @@
         <v>4551.6</v>
       </c>
       <c r="M50">
-        <v>13619.637504</v>
+        <v>13903.379952</v>
       </c>
       <c r="N50">
-        <v>-9068.037504000002</v>
+        <v>-9351.779952000001</v>
       </c>
       <c r="O50">
-        <v>-2339.553676032001</v>
+        <v>-2412.759227616</v>
       </c>
       <c r="P50">
-        <v>-6728.483827968001</v>
+        <v>-6939.020724384</v>
       </c>
       <c r="Q50">
-        <v>-4369.483827968001</v>
+        <v>-4580.020724384</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1169009708348364</v>
+        <v>0.1182951075178724</v>
       </c>
       <c r="T50">
-        <v>1.642054753691373</v>
+        <v>1.674251905724538</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.08622203048026145</v>
+        <v>0.08446239720515408</v>
       </c>
       <c r="W50">
-        <v>0.1834866162795635</v>
+        <v>0.1838399506412051</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3341939165901606</v>
+        <v>0.3273736325781166</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1504120806483054</v>
+        <v>0.1519620806483054</v>
       </c>
       <c r="C51">
-        <v>-12684.06116895213</v>
+        <v>-14773.35058862554</v>
       </c>
       <c r="D51">
-        <v>46316.07883104787</v>
+        <v>45639.84941137446</v>
       </c>
       <c r="E51">
-        <v>54606.84</v>
+        <v>56019.9</v>
       </c>
       <c r="F51">
-        <v>69239.94</v>
+        <v>70653</v>
       </c>
       <c r="G51">
         <v>10239.8</v>
@@ -5475,37 +5475,37 @@
         <v>4551.6</v>
       </c>
       <c r="M51">
-        <v>13903.379952</v>
+        <v>14187.1224</v>
       </c>
       <c r="N51">
-        <v>-9351.779952000001</v>
+        <v>-9635.5224</v>
       </c>
       <c r="O51">
-        <v>-2412.759227616</v>
+        <v>-2485.9647792</v>
       </c>
       <c r="P51">
-        <v>-6939.020724384</v>
+        <v>-7149.5576208</v>
       </c>
       <c r="Q51">
-        <v>-4580.020724384</v>
+        <v>-4790.5576208</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1182951075178724</v>
+        <v>0.1197450096682299</v>
       </c>
       <c r="T51">
-        <v>1.674251905724538</v>
+        <v>1.707736943839028</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.08446239720515408</v>
+        <v>0.082773149261051</v>
       </c>
       <c r="W51">
-        <v>0.1838399506412051</v>
+        <v>0.1841791516283809</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3273736325781166</v>
+        <v>0.3208261599265543</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1519620806483054</v>
+        <v>0.1535120806483055</v>
       </c>
       <c r="C52">
-        <v>-14773.35058862554</v>
+        <v>-16843.17783480485</v>
       </c>
       <c r="D52">
-        <v>45639.84941137446</v>
+        <v>44983.08216519515</v>
       </c>
       <c r="E52">
-        <v>56019.9</v>
+        <v>57432.96</v>
       </c>
       <c r="F52">
-        <v>70653</v>
+        <v>72066.06</v>
       </c>
       <c r="G52">
         <v>10239.8</v>
@@ -5557,37 +5557,37 @@
         <v>4551.6</v>
       </c>
       <c r="M52">
-        <v>14187.1224</v>
+        <v>14470.864848</v>
       </c>
       <c r="N52">
-        <v>-9635.5224</v>
+        <v>-9919.264847999999</v>
       </c>
       <c r="O52">
-        <v>-2485.9647792</v>
+        <v>-2559.170330784</v>
       </c>
       <c r="P52">
-        <v>-7149.5576208</v>
+        <v>-7360.094517215999</v>
       </c>
       <c r="Q52">
-        <v>-4790.5576208</v>
+        <v>-5001.094517215999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1197450096682299</v>
+        <v>0.1212540914981938</v>
       </c>
       <c r="T52">
-        <v>1.707736943839028</v>
+        <v>1.74258871820309</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.082773149261051</v>
+        <v>0.08115014633436372</v>
       </c>
       <c r="W52">
-        <v>0.1841791516283809</v>
+        <v>0.1845050506160598</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3208261599265543</v>
+        <v>0.3145354509083865</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1535120806483055</v>
+        <v>0.1550620806483054</v>
       </c>
       <c r="C53">
-        <v>-16843.17783480485</v>
+        <v>-18894.37118301079</v>
       </c>
       <c r="D53">
-        <v>44983.08216519515</v>
+        <v>44344.94881698921</v>
       </c>
       <c r="E53">
-        <v>57432.96</v>
+        <v>58846.02</v>
       </c>
       <c r="F53">
-        <v>72066.06</v>
+        <v>73479.12</v>
       </c>
       <c r="G53">
         <v>10239.8</v>
@@ -5639,37 +5639,37 @@
         <v>4551.6</v>
       </c>
       <c r="M53">
-        <v>14470.864848</v>
+        <v>14754.607296</v>
       </c>
       <c r="N53">
-        <v>-9919.264847999999</v>
+        <v>-10203.007296</v>
       </c>
       <c r="O53">
-        <v>-2559.170330784</v>
+        <v>-2632.375882368</v>
       </c>
       <c r="P53">
-        <v>-7360.094517215999</v>
+        <v>-7570.631413632</v>
       </c>
       <c r="Q53">
-        <v>-5001.094517215999</v>
+        <v>-5211.631413632</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1212540914981938</v>
+        <v>0.1228260517377395</v>
       </c>
       <c r="T53">
-        <v>1.74258871820309</v>
+        <v>1.778892649832321</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.08115014633436372</v>
+        <v>0.07958956659716443</v>
       </c>
       <c r="W53">
-        <v>0.1845050506160598</v>
+        <v>0.1848184150272894</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3145354509083865</v>
+        <v>0.3084866922370714</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1550620806483054</v>
+        <v>0.1566120806483055</v>
       </c>
       <c r="C54">
-        <v>-18894.37118301079</v>
+        <v>-20927.71256626977</v>
       </c>
       <c r="D54">
-        <v>44344.94881698921</v>
+        <v>43724.66743373024</v>
       </c>
       <c r="E54">
-        <v>58846.02</v>
+        <v>60259.08000000001</v>
       </c>
       <c r="F54">
-        <v>73479.12</v>
+        <v>74892.18000000001</v>
       </c>
       <c r="G54">
         <v>10239.8</v>
@@ -5721,37 +5721,37 @@
         <v>4551.6</v>
       </c>
       <c r="M54">
-        <v>14754.607296</v>
+        <v>15038.349744</v>
       </c>
       <c r="N54">
-        <v>-10203.007296</v>
+        <v>-10486.749744</v>
       </c>
       <c r="O54">
-        <v>-2632.375882368</v>
+        <v>-2705.581433952001</v>
       </c>
       <c r="P54">
-        <v>-7570.631413632</v>
+        <v>-7781.168310048002</v>
       </c>
       <c r="Q54">
-        <v>-5211.631413632</v>
+        <v>-5422.168310048002</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1228260517377395</v>
+        <v>0.1244649039023722</v>
       </c>
       <c r="T54">
-        <v>1.778892649832321</v>
+        <v>1.816741429615988</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.07958956659716443</v>
+        <v>0.07808787666136886</v>
       </c>
       <c r="W54">
-        <v>0.1848184150272894</v>
+        <v>0.1851199543663971</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3084866922370714</v>
+        <v>0.3026661886099568</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1566120806483055</v>
+        <v>0.1581620806483054</v>
       </c>
       <c r="C55">
-        <v>-20927.71256626977</v>
+        <v>-22943.9407715152</v>
       </c>
       <c r="D55">
-        <v>43724.66743373024</v>
+        <v>43121.4992284848</v>
       </c>
       <c r="E55">
-        <v>60259.08000000001</v>
+        <v>61672.14000000001</v>
       </c>
       <c r="F55">
-        <v>74892.18000000001</v>
+        <v>76305.24000000001</v>
       </c>
       <c r="G55">
         <v>10239.8</v>
@@ -5803,37 +5803,37 @@
         <v>4551.6</v>
       </c>
       <c r="M55">
-        <v>15038.349744</v>
+        <v>15322.092192</v>
       </c>
       <c r="N55">
-        <v>-10486.749744</v>
+        <v>-10770.492192</v>
       </c>
       <c r="O55">
-        <v>-2705.581433952001</v>
+        <v>-2778.786985536</v>
       </c>
       <c r="P55">
-        <v>-7781.168310048002</v>
+        <v>-7991.705206464001</v>
       </c>
       <c r="Q55">
-        <v>-5422.168310048002</v>
+        <v>-5632.705206464001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1244649039023722</v>
+        <v>0.1261750105089456</v>
       </c>
       <c r="T55">
-        <v>1.816741429615988</v>
+        <v>1.856235808520683</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.07808787666136886</v>
+        <v>0.07664180487134352</v>
       </c>
       <c r="W55">
-        <v>0.1851199543663971</v>
+        <v>0.1854103255818342</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3026661886099568</v>
+        <v>0.2970612591912539</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1581620806483054</v>
+        <v>0.1597120806483054</v>
       </c>
       <c r="C56">
-        <v>-22943.9407715152</v>
+        <v>-24943.75437502902</v>
       </c>
       <c r="D56">
-        <v>43121.4992284848</v>
+        <v>42534.74562497098</v>
       </c>
       <c r="E56">
-        <v>61672.14000000001</v>
+        <v>63085.2</v>
       </c>
       <c r="F56">
-        <v>76305.24000000001</v>
+        <v>77718.3</v>
       </c>
       <c r="G56">
         <v>10239.8</v>
@@ -5885,37 +5885,37 @@
         <v>4551.6</v>
       </c>
       <c r="M56">
-        <v>15322.092192</v>
+        <v>15605.83464</v>
       </c>
       <c r="N56">
-        <v>-10770.492192</v>
+        <v>-11054.23464</v>
       </c>
       <c r="O56">
-        <v>-2778.786985536</v>
+        <v>-2851.99253712</v>
       </c>
       <c r="P56">
-        <v>-7991.705206464001</v>
+        <v>-8202.24210288</v>
       </c>
       <c r="Q56">
-        <v>-5632.705206464001</v>
+        <v>-5843.24210288</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1261750105089456</v>
+        <v>0.1279611218535888</v>
       </c>
       <c r="T56">
-        <v>1.856235808520683</v>
+        <v>1.897485493154476</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.07664180487134352</v>
+        <v>0.07524831751004636</v>
       </c>
       <c r="W56">
-        <v>0.1854103255818342</v>
+        <v>0.1856901378439827</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2970612591912539</v>
+        <v>0.2916601453877766</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1597120806483054</v>
+        <v>0.1612620806483054</v>
       </c>
       <c r="C57">
-        <v>-24943.75437502902</v>
+        <v>-26927.81444144496</v>
       </c>
       <c r="D57">
-        <v>42534.74562497098</v>
+        <v>41963.74555855504</v>
       </c>
       <c r="E57">
-        <v>63085.2</v>
+        <v>64498.26</v>
       </c>
       <c r="F57">
-        <v>77718.3</v>
+        <v>79131.36</v>
       </c>
       <c r="G57">
         <v>10239.8</v>
@@ -5967,37 +5967,37 @@
         <v>4551.6</v>
       </c>
       <c r="M57">
-        <v>15605.83464</v>
+        <v>15889.577088</v>
       </c>
       <c r="N57">
-        <v>-11054.23464</v>
+        <v>-11337.977088</v>
       </c>
       <c r="O57">
-        <v>-2851.99253712</v>
+        <v>-2925.198088704</v>
       </c>
       <c r="P57">
-        <v>-8202.24210288</v>
+        <v>-8412.778999295999</v>
       </c>
       <c r="Q57">
-        <v>-5843.24210288</v>
+        <v>-6053.778999295999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1279611218535888</v>
+        <v>0.129828420077534</v>
       </c>
       <c r="T57">
-        <v>1.897485493154476</v>
+        <v>1.940610163453442</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.07524831751004636</v>
+        <v>0.07390459755450983</v>
       </c>
       <c r="W57">
-        <v>0.1856901378439827</v>
+        <v>0.1859599568110544</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2916601453877766</v>
+        <v>0.286451928505852</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1612620806483054</v>
+        <v>0.1628120806483055</v>
       </c>
       <c r="C58">
-        <v>-26927.81444144496</v>
+        <v>-28896.74700823797</v>
       </c>
       <c r="D58">
-        <v>41963.74555855504</v>
+        <v>41407.87299176204</v>
       </c>
       <c r="E58">
-        <v>64498.26</v>
+        <v>65911.32000000001</v>
       </c>
       <c r="F58">
-        <v>79131.36</v>
+        <v>80544.42000000001</v>
       </c>
       <c r="G58">
         <v>10239.8</v>
@@ -6049,37 +6049,37 @@
         <v>4551.6</v>
       </c>
       <c r="M58">
-        <v>15889.577088</v>
+        <v>16173.319536</v>
       </c>
       <c r="N58">
-        <v>-11337.977088</v>
+        <v>-11621.719536</v>
       </c>
       <c r="O58">
-        <v>-2925.198088704</v>
+        <v>-2998.403640288001</v>
       </c>
       <c r="P58">
-        <v>-8412.778999295999</v>
+        <v>-8623.315895712001</v>
       </c>
       <c r="Q58">
-        <v>-6053.778999295999</v>
+        <v>-6264.315895712001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.129828420077534</v>
+        <v>0.1317825693816627</v>
       </c>
       <c r="T58">
-        <v>1.940610163453442</v>
+        <v>1.985740632370964</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.07390459755450983</v>
+        <v>0.07260802566758859</v>
       </c>
       <c r="W58">
-        <v>0.1859599568110544</v>
+        <v>0.1862203084459482</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.286451928505852</v>
+        <v>0.2814264560759248</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1628120806483055</v>
+        <v>0.1643620806483055</v>
       </c>
       <c r="C59">
-        <v>-28896.74700823797</v>
+        <v>-30851.14537533036</v>
       </c>
       <c r="D59">
-        <v>41407.87299176204</v>
+        <v>40866.53462466964</v>
       </c>
       <c r="E59">
-        <v>65911.32000000001</v>
+        <v>67324.38</v>
       </c>
       <c r="F59">
-        <v>80544.42000000001</v>
+        <v>81957.48000000001</v>
       </c>
       <c r="G59">
         <v>10239.8</v>
@@ -6131,37 +6131,37 @@
         <v>4551.6</v>
       </c>
       <c r="M59">
-        <v>16173.319536</v>
+        <v>16457.061984</v>
       </c>
       <c r="N59">
-        <v>-11621.719536</v>
+        <v>-11905.461984</v>
       </c>
       <c r="O59">
-        <v>-2998.403640288001</v>
+        <v>-3071.609191872001</v>
       </c>
       <c r="P59">
-        <v>-8623.315895712001</v>
+        <v>-8833.852792128002</v>
       </c>
       <c r="Q59">
-        <v>-6264.315895712001</v>
+        <v>-6474.852792128002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1317825693816627</v>
+        <v>0.1338297734145595</v>
       </c>
       <c r="T59">
-        <v>1.985740632370964</v>
+        <v>2.033020171236939</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.07260802566758859</v>
+        <v>0.07135616315607843</v>
       </c>
       <c r="W59">
-        <v>0.1862203084459482</v>
+        <v>0.1864716824382595</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2814264560759248</v>
+        <v>0.2765742757987536</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1643620806483054</v>
+        <v>0.1659120806483054</v>
       </c>
       <c r="C60">
-        <v>-30851.14537533034</v>
+        <v>-32791.57221741935</v>
       </c>
       <c r="D60">
-        <v>40866.53462466966</v>
+        <v>40339.16778258065</v>
       </c>
       <c r="E60">
-        <v>67324.37999999999</v>
+        <v>68737.43999999999</v>
       </c>
       <c r="F60">
-        <v>81957.48</v>
+        <v>83370.53999999999</v>
       </c>
       <c r="G60">
         <v>10239.8</v>
@@ -6213,37 +6213,37 @@
         <v>4551.6</v>
       </c>
       <c r="M60">
-        <v>16457.061984</v>
+        <v>16740.804432</v>
       </c>
       <c r="N60">
-        <v>-11905.461984</v>
+        <v>-12189.204432</v>
       </c>
       <c r="O60">
-        <v>-3071.609191872</v>
+        <v>-3144.814743456</v>
       </c>
       <c r="P60">
-        <v>-8833.852792128</v>
+        <v>-9044.389688544001</v>
       </c>
       <c r="Q60">
-        <v>-6474.852792128</v>
+        <v>-6685.389688544001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1338297734145594</v>
+        <v>0.1359768410588169</v>
       </c>
       <c r="T60">
-        <v>2.033020171236938</v>
+        <v>2.082606029071985</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.07135616315607844</v>
+        <v>0.07014673666190763</v>
       </c>
       <c r="W60">
-        <v>0.1864716824382595</v>
+        <v>0.186714535278289</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2765742757987537</v>
+        <v>0.2718865762089443</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1659120806483054</v>
+        <v>0.1674620806483054</v>
       </c>
       <c r="C61">
-        <v>-32791.57221741935</v>
+        <v>-34718.56153483539</v>
       </c>
       <c r="D61">
-        <v>40339.16778258065</v>
+        <v>39825.2384651646</v>
       </c>
       <c r="E61">
-        <v>68737.43999999999</v>
+        <v>70150.49999999999</v>
       </c>
       <c r="F61">
-        <v>83370.53999999999</v>
+        <v>84783.59999999999</v>
       </c>
       <c r="G61">
         <v>10239.8</v>
@@ -6295,37 +6295,37 @@
         <v>4551.6</v>
       </c>
       <c r="M61">
-        <v>16740.804432</v>
+        <v>17024.54688</v>
       </c>
       <c r="N61">
-        <v>-12189.204432</v>
+        <v>-12472.94688</v>
       </c>
       <c r="O61">
-        <v>-3144.814743456</v>
+        <v>-3218.020295039999</v>
       </c>
       <c r="P61">
-        <v>-9044.389688544001</v>
+        <v>-9254.926584959998</v>
       </c>
       <c r="Q61">
-        <v>-6685.389688544001</v>
+        <v>-6895.926584959998</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1359768410588169</v>
+        <v>0.1382312620852874</v>
       </c>
       <c r="T61">
-        <v>2.082606029071985</v>
+        <v>2.134671179798786</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.07014673666190763</v>
+        <v>0.06897762438420917</v>
       </c>
       <c r="W61">
-        <v>0.186714535278289</v>
+        <v>0.1869492930236508</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2718865762089443</v>
+        <v>0.2673551332721286</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1674620806483054</v>
+        <v>0.1690120806483054</v>
       </c>
       <c r="C62">
-        <v>-34718.56153483539</v>
+        <v>-36632.62045715055</v>
       </c>
       <c r="D62">
-        <v>39825.2384651646</v>
+        <v>39324.23954284946</v>
       </c>
       <c r="E62">
-        <v>70150.49999999999</v>
+        <v>71563.56</v>
       </c>
       <c r="F62">
-        <v>84783.59999999999</v>
+        <v>86196.66</v>
       </c>
       <c r="G62">
         <v>10239.8</v>
@@ -6377,37 +6377,37 @@
         <v>4551.6</v>
       </c>
       <c r="M62">
-        <v>17024.54688</v>
+        <v>17308.289328</v>
       </c>
       <c r="N62">
-        <v>-12472.94688</v>
+        <v>-12756.689328</v>
       </c>
       <c r="O62">
-        <v>-3218.020295039999</v>
+        <v>-3291.225846624</v>
       </c>
       <c r="P62">
-        <v>-9254.926584959998</v>
+        <v>-9465.463481376002</v>
       </c>
       <c r="Q62">
-        <v>-6895.926584959998</v>
+        <v>-7106.463481376002</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1382312620852874</v>
+        <v>0.1406012944464486</v>
       </c>
       <c r="T62">
-        <v>2.134671179798786</v>
+        <v>2.189406338255165</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.06897762438420917</v>
+        <v>0.06784684365659918</v>
       </c>
       <c r="W62">
-        <v>0.1869492930236508</v>
+        <v>0.1871763537937549</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2673551332721286</v>
+        <v>0.2629722622348805</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1690120806483054</v>
+        <v>0.1705620806483054</v>
       </c>
       <c r="C63">
-        <v>-36632.62045715055</v>
+        <v>-38534.23091234242</v>
       </c>
       <c r="D63">
-        <v>39324.23954284946</v>
+        <v>38835.68908765758</v>
       </c>
       <c r="E63">
-        <v>71563.56</v>
+        <v>72976.62</v>
       </c>
       <c r="F63">
-        <v>86196.66</v>
+        <v>87609.72</v>
       </c>
       <c r="G63">
         <v>10239.8</v>
@@ -6459,37 +6459,37 @@
         <v>4551.6</v>
       </c>
       <c r="M63">
-        <v>17308.289328</v>
+        <v>17592.031776</v>
       </c>
       <c r="N63">
-        <v>-12756.689328</v>
+        <v>-13040.431776</v>
       </c>
       <c r="O63">
-        <v>-3291.225846624</v>
+        <v>-3364.431398208</v>
       </c>
       <c r="P63">
-        <v>-9465.463481376002</v>
+        <v>-9676.000377791999</v>
       </c>
       <c r="Q63">
-        <v>-7106.463481376002</v>
+        <v>-7317.000377791999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1406012944464486</v>
+        <v>0.1430960653529341</v>
       </c>
       <c r="T63">
-        <v>2.189406338255165</v>
+        <v>2.247022294525038</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.06784684365659918</v>
+        <v>0.06675253972665403</v>
       </c>
       <c r="W63">
-        <v>0.1871763537937549</v>
+        <v>0.1873960900228879</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2629722622348805</v>
+        <v>0.258730774134318</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1705620806483054</v>
+        <v>0.1721120806483054</v>
       </c>
       <c r="C64">
-        <v>-38534.23091234242</v>
+        <v>-40423.85117306263</v>
       </c>
       <c r="D64">
-        <v>38835.68908765758</v>
+        <v>38359.12882693737</v>
       </c>
       <c r="E64">
-        <v>72976.62</v>
+        <v>74389.67999999999</v>
       </c>
       <c r="F64">
-        <v>87609.72</v>
+        <v>89022.78</v>
       </c>
       <c r="G64">
         <v>10239.8</v>
@@ -6541,37 +6541,37 @@
         <v>4551.6</v>
       </c>
       <c r="M64">
-        <v>17592.031776</v>
+        <v>17875.774224</v>
       </c>
       <c r="N64">
-        <v>-13040.431776</v>
+        <v>-13324.174224</v>
       </c>
       <c r="O64">
-        <v>-3364.431398208</v>
+        <v>-3437.636949792</v>
       </c>
       <c r="P64">
-        <v>-9676.000377791999</v>
+        <v>-9886.537274208</v>
       </c>
       <c r="Q64">
-        <v>-7317.000377791999</v>
+        <v>-7527.537274208</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1430960653529341</v>
+        <v>0.1457256887408512</v>
       </c>
       <c r="T64">
-        <v>2.247022294525038</v>
+        <v>2.307752626809498</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.06675253972665403</v>
+        <v>0.06569297560400872</v>
       </c>
       <c r="W64">
-        <v>0.1873960900228879</v>
+        <v>0.187608850498715</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.258730774134318</v>
+        <v>0.2546239364496462</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1721120806483054</v>
+        <v>0.1736620806483054</v>
       </c>
       <c r="C65">
-        <v>-40423.85117306263</v>
+        <v>-42301.9172904376</v>
       </c>
       <c r="D65">
-        <v>38359.12882693737</v>
+        <v>37894.1227095624</v>
       </c>
       <c r="E65">
-        <v>74389.67999999999</v>
+        <v>75802.73999999999</v>
       </c>
       <c r="F65">
-        <v>89022.78</v>
+        <v>90435.84</v>
       </c>
       <c r="G65">
         <v>10239.8</v>
@@ -6623,37 +6623,37 @@
         <v>4551.6</v>
       </c>
       <c r="M65">
-        <v>17875.774224</v>
+        <v>18159.516672</v>
       </c>
       <c r="N65">
-        <v>-13324.174224</v>
+        <v>-13607.916672</v>
       </c>
       <c r="O65">
-        <v>-3437.636949792</v>
+        <v>-3510.842501376</v>
       </c>
       <c r="P65">
-        <v>-9886.537274208</v>
+        <v>-10097.074170624</v>
       </c>
       <c r="Q65">
-        <v>-7527.537274208</v>
+        <v>-7738.074170624001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1457256887408512</v>
+        <v>0.148501402316986</v>
       </c>
       <c r="T65">
-        <v>2.307752626809498</v>
+        <v>2.371856866443095</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.06569297560400872</v>
+        <v>0.0646665228601961</v>
       </c>
       <c r="W65">
-        <v>0.187608850498715</v>
+        <v>0.1878149622096726</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2546239364496462</v>
+        <v>0.2506454374426205</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1736620806483054</v>
+        <v>0.1752120806483055</v>
       </c>
       <c r="C66">
-        <v>-42301.9172904376</v>
+        <v>-44168.8444248317</v>
       </c>
       <c r="D66">
-        <v>37894.1227095624</v>
+        <v>37440.25557516831</v>
       </c>
       <c r="E66">
-        <v>75802.73999999999</v>
+        <v>77215.8</v>
       </c>
       <c r="F66">
-        <v>90435.84</v>
+        <v>91848.90000000001</v>
       </c>
       <c r="G66">
         <v>10239.8</v>
@@ -6705,37 +6705,37 @@
         <v>4551.6</v>
       </c>
       <c r="M66">
-        <v>18159.516672</v>
+        <v>18443.25912</v>
       </c>
       <c r="N66">
-        <v>-13607.916672</v>
+        <v>-13891.65912</v>
       </c>
       <c r="O66">
-        <v>-3510.842501376</v>
+        <v>-3584.048052960001</v>
       </c>
       <c r="P66">
-        <v>-10097.074170624</v>
+        <v>-10307.61106704</v>
       </c>
       <c r="Q66">
-        <v>-7738.074170624001</v>
+        <v>-7948.611067040001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.148501402316986</v>
+        <v>0.1514357280974713</v>
       </c>
       <c r="T66">
-        <v>2.371856866443095</v>
+        <v>2.439624205484327</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.0646665228601961</v>
+        <v>0.06367165327773154</v>
       </c>
       <c r="W66">
-        <v>0.1878149622096726</v>
+        <v>0.1880147320218315</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2506454374426205</v>
+        <v>0.2467893537896571</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1752120806483055</v>
+        <v>0.1767620806483055</v>
       </c>
       <c r="C67">
-        <v>-44168.8444248317</v>
+        <v>-46025.02808210891</v>
       </c>
       <c r="D67">
-        <v>37440.25557516831</v>
+        <v>36997.1319178911</v>
       </c>
       <c r="E67">
-        <v>77215.8</v>
+        <v>78628.86</v>
       </c>
       <c r="F67">
-        <v>91848.90000000001</v>
+        <v>93261.96000000001</v>
       </c>
       <c r="G67">
         <v>10239.8</v>
@@ -6787,37 +6787,37 @@
         <v>4551.6</v>
       </c>
       <c r="M67">
-        <v>18443.25912</v>
+        <v>18727.001568</v>
       </c>
       <c r="N67">
-        <v>-13891.65912</v>
+        <v>-14175.401568</v>
       </c>
       <c r="O67">
-        <v>-3584.048052960001</v>
+        <v>-3657.253604544001</v>
       </c>
       <c r="P67">
-        <v>-10307.61106704</v>
+        <v>-10518.147963456</v>
       </c>
       <c r="Q67">
-        <v>-7948.611067040001</v>
+        <v>-8159.147963456002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1514357280974713</v>
+        <v>0.1545426612768087</v>
       </c>
       <c r="T67">
-        <v>2.439624205484327</v>
+        <v>2.511377858586807</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.06367165327773154</v>
+        <v>0.06270693125837196</v>
       </c>
       <c r="W67">
-        <v>0.1880147320218315</v>
+        <v>0.1882084482033189</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2467893537896571</v>
+        <v>0.2430501211564805</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1767620806483055</v>
+        <v>0.1783120806483054</v>
       </c>
       <c r="C68">
-        <v>-46025.02808210891</v>
+        <v>-47870.84526313098</v>
       </c>
       <c r="D68">
-        <v>36997.1319178911</v>
+        <v>36564.37473686902</v>
       </c>
       <c r="E68">
-        <v>78628.86</v>
+        <v>80041.92</v>
       </c>
       <c r="F68">
-        <v>93261.96000000001</v>
+        <v>94675.02</v>
       </c>
       <c r="G68">
         <v>10239.8</v>
@@ -6869,37 +6869,37 @@
         <v>4551.6</v>
       </c>
       <c r="M68">
-        <v>18727.001568</v>
+        <v>19010.744016</v>
       </c>
       <c r="N68">
-        <v>-14175.401568</v>
+        <v>-14459.144016</v>
       </c>
       <c r="O68">
-        <v>-3657.253604544001</v>
+        <v>-3730.459156128</v>
       </c>
       <c r="P68">
-        <v>-10518.147963456</v>
+        <v>-10728.684859872</v>
       </c>
       <c r="Q68">
-        <v>-8159.147963456002</v>
+        <v>-8369.684859871999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1545426612768087</v>
+        <v>0.157837893436712</v>
       </c>
       <c r="T68">
-        <v>2.511377858586807</v>
+        <v>2.587480217937922</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.06270693125837196</v>
+        <v>0.06177100691123209</v>
       </c>
       <c r="W68">
-        <v>0.1882084482033189</v>
+        <v>0.1883963818122246</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2430501211564805</v>
+        <v>0.2394225074078763</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1783120806483054</v>
+        <v>0.1798620806483054</v>
       </c>
       <c r="C69">
-        <v>-47870.84526313098</v>
+        <v>-49706.65553351375</v>
       </c>
       <c r="D69">
-        <v>36564.37473686902</v>
+        <v>36141.62446648625</v>
       </c>
       <c r="E69">
-        <v>80041.92</v>
+        <v>81454.98</v>
       </c>
       <c r="F69">
-        <v>94675.02</v>
+        <v>96088.08</v>
       </c>
       <c r="G69">
         <v>10239.8</v>
@@ -6951,37 +6951,37 @@
         <v>4551.6</v>
       </c>
       <c r="M69">
-        <v>19010.744016</v>
+        <v>19294.486464</v>
       </c>
       <c r="N69">
-        <v>-14459.144016</v>
+        <v>-14742.886464</v>
       </c>
       <c r="O69">
-        <v>-3730.459156128</v>
+        <v>-3803.664707712001</v>
       </c>
       <c r="P69">
-        <v>-10728.684859872</v>
+        <v>-10939.221756288</v>
       </c>
       <c r="Q69">
-        <v>-8369.684859871999</v>
+        <v>-8580.221756288</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.157837893436712</v>
+        <v>0.1613390776066093</v>
       </c>
       <c r="T69">
-        <v>2.587480217937922</v>
+        <v>2.668338974748482</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.06177100691123209</v>
+        <v>0.0608626097507728</v>
       </c>
       <c r="W69">
-        <v>0.1883963818122246</v>
+        <v>0.1885787879620448</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2394225074078763</v>
+        <v>0.2359015881812899</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1798620806483054</v>
+        <v>0.1814120806483054</v>
       </c>
       <c r="C70">
-        <v>-49706.65553351375</v>
+        <v>-51532.8020200218</v>
       </c>
       <c r="D70">
-        <v>36141.62446648625</v>
+        <v>35728.53797997822</v>
       </c>
       <c r="E70">
-        <v>81454.98</v>
+        <v>82868.04000000001</v>
       </c>
       <c r="F70">
-        <v>96088.08</v>
+        <v>97501.14000000001</v>
       </c>
       <c r="G70">
         <v>10239.8</v>
@@ -7033,37 +7033,37 @@
         <v>4551.6</v>
       </c>
       <c r="M70">
-        <v>19294.486464</v>
+        <v>19578.228912</v>
       </c>
       <c r="N70">
-        <v>-14742.886464</v>
+        <v>-15026.628912</v>
       </c>
       <c r="O70">
-        <v>-3803.664707712001</v>
+        <v>-3876.870259296001</v>
       </c>
       <c r="P70">
-        <v>-10939.221756288</v>
+        <v>-11149.758652704</v>
       </c>
       <c r="Q70">
-        <v>-8580.221756288</v>
+        <v>-8790.758652704</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1613390776066093</v>
+        <v>0.1650661446261773</v>
       </c>
       <c r="T70">
-        <v>2.668338974748482</v>
+        <v>2.754414425546821</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.0608626097507728</v>
+        <v>0.05998054294279058</v>
       </c>
       <c r="W70">
-        <v>0.1885787879620448</v>
+        <v>0.1887559069770877</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2359015881812899</v>
+        <v>0.2324827245844596</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1814120806483054</v>
+        <v>0.1829620806483055</v>
       </c>
       <c r="C71">
-        <v>-51532.8020200218</v>
+        <v>-53349.61233940462</v>
       </c>
       <c r="D71">
-        <v>35728.53797997822</v>
+        <v>35324.78766059539</v>
       </c>
       <c r="E71">
-        <v>82868.04000000001</v>
+        <v>84281.10000000001</v>
       </c>
       <c r="F71">
-        <v>97501.14000000001</v>
+        <v>98914.20000000001</v>
       </c>
       <c r="G71">
         <v>10239.8</v>
@@ -7115,37 +7115,37 @@
         <v>4551.6</v>
       </c>
       <c r="M71">
-        <v>19578.228912</v>
+        <v>19861.97136</v>
       </c>
       <c r="N71">
-        <v>-15026.628912</v>
+        <v>-15310.37136</v>
       </c>
       <c r="O71">
-        <v>-3876.870259296001</v>
+        <v>-3950.075810880001</v>
       </c>
       <c r="P71">
-        <v>-11149.758652704</v>
+        <v>-11360.29554912</v>
       </c>
       <c r="Q71">
-        <v>-8790.758652704</v>
+        <v>-9001.295549120001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1650661446261773</v>
+        <v>0.1690416827803832</v>
       </c>
       <c r="T71">
-        <v>2.754414425546821</v>
+        <v>2.846228239731715</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.05998054294279058</v>
+        <v>0.05912367804360785</v>
       </c>
       <c r="W71">
-        <v>0.1887559069770877</v>
+        <v>0.1889279654488435</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2324827245844596</v>
+        <v>0.2291615428046816</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1829620806483055</v>
+        <v>0.1845120806483055</v>
       </c>
       <c r="C72">
-        <v>-53349.61233940462</v>
+        <v>-55157.39946495864</v>
       </c>
       <c r="D72">
-        <v>35324.78766059539</v>
+        <v>34930.06053504137</v>
       </c>
       <c r="E72">
-        <v>84281.10000000001</v>
+        <v>85694.16</v>
       </c>
       <c r="F72">
-        <v>98914.20000000001</v>
+        <v>100327.26</v>
       </c>
       <c r="G72">
         <v>10239.8</v>
@@ -7197,37 +7197,37 @@
         <v>4551.6</v>
       </c>
       <c r="M72">
-        <v>19861.97136</v>
+        <v>20145.713808</v>
       </c>
       <c r="N72">
-        <v>-15310.37136</v>
+        <v>-15594.113808</v>
       </c>
       <c r="O72">
-        <v>-3950.075810880001</v>
+        <v>-4023.281362464001</v>
       </c>
       <c r="P72">
-        <v>-11360.29554912</v>
+        <v>-11570.832445536</v>
       </c>
       <c r="Q72">
-        <v>-9001.295549120001</v>
+        <v>-9211.832445536002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1690416827803832</v>
+        <v>0.1732913959797068</v>
       </c>
       <c r="T72">
-        <v>2.846228239731715</v>
+        <v>2.944374041101774</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.05912367804360785</v>
+        <v>0.05829095018383872</v>
       </c>
       <c r="W72">
-        <v>0.1889279654488435</v>
+        <v>0.1890951772030852</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2291615428046816</v>
+        <v>0.2259339154412353</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1845120806483054</v>
+        <v>0.1860620806483054</v>
       </c>
       <c r="C73">
-        <v>-55157.39946495861</v>
+        <v>-56956.46253563222</v>
       </c>
       <c r="D73">
-        <v>34930.06053504138</v>
+        <v>34544.05746436778</v>
       </c>
       <c r="E73">
-        <v>85694.15999999999</v>
+        <v>87107.21999999999</v>
       </c>
       <c r="F73">
-        <v>100327.26</v>
+        <v>101740.32</v>
       </c>
       <c r="G73">
         <v>10239.8</v>
@@ -7279,37 +7279,37 @@
         <v>4551.6</v>
       </c>
       <c r="M73">
-        <v>20145.713808</v>
+        <v>20429.456256</v>
       </c>
       <c r="N73">
-        <v>-15594.113808</v>
+        <v>-15877.856256</v>
       </c>
       <c r="O73">
-        <v>-4023.281362464</v>
+        <v>-4096.486914048</v>
       </c>
       <c r="P73">
-        <v>-11570.832445536</v>
+        <v>-11781.369341952</v>
       </c>
       <c r="Q73">
-        <v>-9211.832445536</v>
+        <v>-9422.369341951999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1732913959797067</v>
+        <v>0.1778446601218391</v>
       </c>
       <c r="T73">
-        <v>2.944374041101773</v>
+        <v>3.049530256855407</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.05829095018383873</v>
+        <v>0.05748135365350765</v>
       </c>
       <c r="W73">
-        <v>0.1890951772030852</v>
+        <v>0.1892577441863757</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2259339154412354</v>
+        <v>0.2227959443934405</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1860620806483054</v>
+        <v>0.1876120806483054</v>
       </c>
       <c r="C74">
-        <v>-56956.46253563222</v>
+        <v>-58747.08761206994</v>
       </c>
       <c r="D74">
-        <v>34544.05746436778</v>
+        <v>34166.49238793006</v>
       </c>
       <c r="E74">
-        <v>87107.21999999999</v>
+        <v>88520.28</v>
       </c>
       <c r="F74">
-        <v>101740.32</v>
+        <v>103153.38</v>
       </c>
       <c r="G74">
         <v>10239.8</v>
@@ -7361,37 +7361,37 @@
         <v>4551.6</v>
       </c>
       <c r="M74">
-        <v>20429.456256</v>
+        <v>20713.198704</v>
       </c>
       <c r="N74">
-        <v>-15877.856256</v>
+        <v>-16161.598704</v>
       </c>
       <c r="O74">
-        <v>-4096.486914048</v>
+        <v>-4169.692465632001</v>
       </c>
       <c r="P74">
-        <v>-11781.369341952</v>
+        <v>-11991.906238368</v>
       </c>
       <c r="Q74">
-        <v>-9422.369341951999</v>
+        <v>-9632.906238368001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1778446601218391</v>
+        <v>0.1827352030893147</v>
       </c>
       <c r="T74">
-        <v>3.049530256855407</v>
+        <v>3.162475821924126</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.05748135365350765</v>
+        <v>0.05669393785003492</v>
       </c>
       <c r="W74">
-        <v>0.1892577441863757</v>
+        <v>0.189415857279713</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2227959443934405</v>
+        <v>0.2197439451551741</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1876120806483054</v>
+        <v>0.1891620806483054</v>
       </c>
       <c r="C75">
-        <v>-58747.08761206994</v>
+        <v>-60529.54838361155</v>
       </c>
       <c r="D75">
-        <v>34166.49238793006</v>
+        <v>33797.09161638846</v>
       </c>
       <c r="E75">
-        <v>88520.28</v>
+        <v>89933.34</v>
       </c>
       <c r="F75">
-        <v>103153.38</v>
+        <v>104566.44</v>
       </c>
       <c r="G75">
         <v>10239.8</v>
@@ -7443,37 +7443,37 @@
         <v>4551.6</v>
       </c>
       <c r="M75">
-        <v>20713.198704</v>
+        <v>20996.941152</v>
       </c>
       <c r="N75">
-        <v>-16161.598704</v>
+        <v>-16445.341152</v>
       </c>
       <c r="O75">
-        <v>-4169.692465632001</v>
+        <v>-4242.898017216</v>
       </c>
       <c r="P75">
-        <v>-11991.906238368</v>
+        <v>-12202.443134784</v>
       </c>
       <c r="Q75">
-        <v>-9632.906238368001</v>
+        <v>-9843.443134784</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1827352030893147</v>
+        <v>0.1880019416696729</v>
       </c>
       <c r="T75">
-        <v>3.162475821924126</v>
+        <v>3.284109507382746</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.05669393785003492</v>
+        <v>0.05592780355476419</v>
       </c>
       <c r="W75">
-        <v>0.189415857279713</v>
+        <v>0.1895696970462034</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2197439451551741</v>
+        <v>0.2167744323828068</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1891620806483054</v>
+        <v>0.1907120806483055</v>
       </c>
       <c r="C76">
-        <v>-60529.54838361155</v>
+        <v>-62304.10682991803</v>
       </c>
       <c r="D76">
-        <v>33797.09161638846</v>
+        <v>33435.59317008196</v>
       </c>
       <c r="E76">
-        <v>89933.34</v>
+        <v>91346.39999999999</v>
       </c>
       <c r="F76">
-        <v>104566.44</v>
+        <v>105979.5</v>
       </c>
       <c r="G76">
         <v>10239.8</v>
@@ -7525,37 +7525,37 @@
         <v>4551.6</v>
       </c>
       <c r="M76">
-        <v>20996.941152</v>
+        <v>21280.6836</v>
       </c>
       <c r="N76">
-        <v>-16445.341152</v>
+        <v>-16729.0836</v>
       </c>
       <c r="O76">
-        <v>-4242.898017216</v>
+        <v>-4316.103568799999</v>
       </c>
       <c r="P76">
-        <v>-12202.443134784</v>
+        <v>-12412.9800312</v>
       </c>
       <c r="Q76">
-        <v>-9843.443134784</v>
+        <v>-10053.9800312</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1880019416696729</v>
+        <v>0.1936900193364599</v>
       </c>
       <c r="T76">
-        <v>3.284109507382746</v>
+        <v>3.415473887678057</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.05592780355476419</v>
+        <v>0.05518209950736733</v>
       </c>
       <c r="W76">
-        <v>0.1895696970462034</v>
+        <v>0.1897194344189206</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2167744323828068</v>
+        <v>0.213884106617703</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1907120806483055</v>
+        <v>0.1922620806483055</v>
       </c>
       <c r="C77">
-        <v>-62304.10682991803</v>
+        <v>-64071.01384058609</v>
       </c>
       <c r="D77">
-        <v>33435.59317008196</v>
+        <v>33081.74615941391</v>
       </c>
       <c r="E77">
-        <v>91346.39999999999</v>
+        <v>92759.45999999999</v>
       </c>
       <c r="F77">
-        <v>105979.5</v>
+        <v>107392.56</v>
       </c>
       <c r="G77">
         <v>10239.8</v>
@@ -7607,37 +7607,37 @@
         <v>4551.6</v>
       </c>
       <c r="M77">
-        <v>21280.6836</v>
+        <v>21564.426048</v>
       </c>
       <c r="N77">
-        <v>-16729.0836</v>
+        <v>-17012.826048</v>
       </c>
       <c r="O77">
-        <v>-4316.103568799999</v>
+        <v>-4389.309120384</v>
       </c>
       <c r="P77">
-        <v>-12412.9800312</v>
+        <v>-12623.516927616</v>
       </c>
       <c r="Q77">
-        <v>-10053.9800312</v>
+        <v>-10264.516927616</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1936900193364599</v>
+        <v>0.199852103475479</v>
       </c>
       <c r="T77">
-        <v>3.415473887678057</v>
+        <v>3.557785299664643</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.05518209950736733</v>
+        <v>0.05445601925069145</v>
       </c>
       <c r="W77">
-        <v>0.1897194344189206</v>
+        <v>0.1898652313344612</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.213884106617703</v>
+        <v>0.2110698420569435</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1922620806483055</v>
+        <v>0.1938120806483054</v>
       </c>
       <c r="C78">
-        <v>-64071.01384058609</v>
+        <v>-65830.50979583037</v>
       </c>
       <c r="D78">
-        <v>33081.74615941391</v>
+        <v>32735.31020416963</v>
       </c>
       <c r="E78">
-        <v>92759.45999999999</v>
+        <v>94172.51999999999</v>
       </c>
       <c r="F78">
-        <v>107392.56</v>
+        <v>108805.62</v>
       </c>
       <c r="G78">
         <v>10239.8</v>
@@ -7689,37 +7689,37 @@
         <v>4551.6</v>
       </c>
       <c r="M78">
-        <v>21564.426048</v>
+        <v>21848.168496</v>
       </c>
       <c r="N78">
-        <v>-17012.826048</v>
+        <v>-17296.568496</v>
       </c>
       <c r="O78">
-        <v>-4389.309120384</v>
+        <v>-4462.514671968</v>
       </c>
       <c r="P78">
-        <v>-12623.516927616</v>
+        <v>-12834.053824032</v>
       </c>
       <c r="Q78">
-        <v>-10264.516927616</v>
+        <v>-10475.053824032</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.199852103475479</v>
+        <v>0.2065500210178911</v>
       </c>
       <c r="T78">
-        <v>3.557785299664643</v>
+        <v>3.712471617041366</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.05445601925069145</v>
+        <v>0.0537487982214617</v>
       </c>
       <c r="W78">
-        <v>0.1898652313344612</v>
+        <v>0.1900072413171305</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2110698420569435</v>
+        <v>0.2083286752769832</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1938120806483054</v>
+        <v>0.1953620806483055</v>
       </c>
       <c r="C79">
-        <v>-65830.50979583037</v>
+        <v>-67582.82511105816</v>
       </c>
       <c r="D79">
-        <v>32735.31020416963</v>
+        <v>32396.05488894185</v>
       </c>
       <c r="E79">
-        <v>94172.51999999999</v>
+        <v>95585.58</v>
       </c>
       <c r="F79">
-        <v>108805.62</v>
+        <v>110218.68</v>
       </c>
       <c r="G79">
         <v>10239.8</v>
@@ -7771,37 +7771,37 @@
         <v>4551.6</v>
       </c>
       <c r="M79">
-        <v>21848.168496</v>
+        <v>22131.910944</v>
       </c>
       <c r="N79">
-        <v>-17296.568496</v>
+        <v>-17580.310944</v>
       </c>
       <c r="O79">
-        <v>-4462.514671968</v>
+        <v>-4535.720223552002</v>
       </c>
       <c r="P79">
-        <v>-12834.053824032</v>
+        <v>-13044.590720448</v>
       </c>
       <c r="Q79">
-        <v>-10475.053824032</v>
+        <v>-10685.590720448</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2065500210178911</v>
+        <v>0.213856840155068</v>
       </c>
       <c r="T79">
-        <v>3.712471617041366</v>
+        <v>3.881220326906884</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.0537487982214617</v>
+        <v>0.05305971106477628</v>
       </c>
       <c r="W79">
-        <v>0.1900072413171305</v>
+        <v>0.1901456100181929</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2083286752769832</v>
+        <v>0.2056577948247141</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1953620806483055</v>
+        <v>0.1969120806483055</v>
       </c>
       <c r="C80">
-        <v>-67582.82511105816</v>
+        <v>-69328.18074792869</v>
       </c>
       <c r="D80">
-        <v>32396.05488894185</v>
+        <v>32063.75925207131</v>
       </c>
       <c r="E80">
-        <v>95585.58</v>
+        <v>96998.64</v>
       </c>
       <c r="F80">
-        <v>110218.68</v>
+        <v>111631.74</v>
       </c>
       <c r="G80">
         <v>10239.8</v>
@@ -7853,37 +7853,37 @@
         <v>4551.6</v>
       </c>
       <c r="M80">
-        <v>22131.910944</v>
+        <v>22415.653392</v>
       </c>
       <c r="N80">
-        <v>-17580.310944</v>
+        <v>-17864.053392</v>
       </c>
       <c r="O80">
-        <v>-4535.720223552002</v>
+        <v>-4608.925775136001</v>
       </c>
       <c r="P80">
-        <v>-13044.590720448</v>
+        <v>-13255.127616864</v>
       </c>
       <c r="Q80">
-        <v>-10685.590720448</v>
+        <v>-10896.127616864</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.213856840155068</v>
+        <v>0.2218595468291189</v>
       </c>
       <c r="T80">
-        <v>3.881220326906884</v>
+        <v>4.066040342473879</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.05305971106477628</v>
+        <v>0.05238806915256393</v>
       </c>
       <c r="W80">
-        <v>0.1901456100181929</v>
+        <v>0.1902804757141652</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2056577948247141</v>
+        <v>0.2030545315990849</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1969120806483055</v>
+        <v>0.1984620806483055</v>
       </c>
       <c r="C81">
-        <v>-69328.18074792869</v>
+        <v>-71066.78869427959</v>
       </c>
       <c r="D81">
-        <v>32063.75925207131</v>
+        <v>31738.21130572042</v>
       </c>
       <c r="E81">
-        <v>96998.64</v>
+        <v>98411.7</v>
       </c>
       <c r="F81">
-        <v>111631.74</v>
+        <v>113044.8</v>
       </c>
       <c r="G81">
         <v>10239.8</v>
@@ -7935,37 +7935,37 @@
         <v>4551.6</v>
       </c>
       <c r="M81">
-        <v>22415.653392</v>
+        <v>22699.39584</v>
       </c>
       <c r="N81">
-        <v>-17864.053392</v>
+        <v>-18147.79584</v>
       </c>
       <c r="O81">
-        <v>-4608.925775136001</v>
+        <v>-4682.13132672</v>
       </c>
       <c r="P81">
-        <v>-13255.127616864</v>
+        <v>-13465.66451328</v>
       </c>
       <c r="Q81">
-        <v>-10896.127616864</v>
+        <v>-11106.66451328</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2218595468291189</v>
+        <v>0.2306625241705748</v>
       </c>
       <c r="T81">
-        <v>4.066040342473879</v>
+        <v>4.269342359597571</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.05238806915256393</v>
+        <v>0.05173321828815687</v>
       </c>
       <c r="W81">
-        <v>0.1902804757141652</v>
+        <v>0.1904119697677381</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2030545315990849</v>
+        <v>0.2005163499540965</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1984620806483055</v>
+        <v>0.2285990101245626</v>
       </c>
       <c r="C82">
-        <v>-71066.78869427959</v>
+        <v>-77712.32908447027</v>
       </c>
       <c r="D82">
-        <v>31738.21130572042</v>
+        <v>26505.73091552973</v>
       </c>
       <c r="E82">
-        <v>98411.7</v>
+        <v>99824.75999999999</v>
       </c>
       <c r="F82">
-        <v>113044.8</v>
+        <v>114457.86</v>
       </c>
       <c r="G82">
         <v>10239.8</v>
@@ -8017,45 +8017,45 @@
         <v>4551.6</v>
       </c>
       <c r="M82">
-        <v>22699.39584</v>
+        <v>26989.163388</v>
       </c>
       <c r="N82">
-        <v>-18147.79584</v>
+        <v>-22437.563388</v>
       </c>
       <c r="O82">
-        <v>-4682.13132672</v>
+        <v>-5788.891354104001</v>
       </c>
       <c r="P82">
-        <v>-13465.66451328</v>
+        <v>-16648.672033896</v>
       </c>
       <c r="Q82">
-        <v>-11106.66451328</v>
+        <v>-14289.672033896</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2306625241705748</v>
+        <v>0.2416391279493266</v>
       </c>
       <c r="T82">
-        <v>4.269342359597571</v>
+        <v>4.522843601601077</v>
       </c>
       <c r="U82">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05173321828815687</v>
+        <v>0.04351052987889674</v>
       </c>
       <c r="W82">
-        <v>0.1904119697677381</v>
+        <v>0.2255402170545562</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.2005163499540965</v>
+        <v>0.1686454646468866</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2285990101245626</v>
+        <v>0.2304990101245626</v>
       </c>
       <c r="C83">
-        <v>-77712.32908447027</v>
+        <v>-79398.05372249699</v>
       </c>
       <c r="D83">
-        <v>26505.73091552973</v>
+        <v>26233.06627750302</v>
       </c>
       <c r="E83">
-        <v>99824.75999999999</v>
+        <v>101237.82</v>
       </c>
       <c r="F83">
-        <v>114457.86</v>
+        <v>115870.92</v>
       </c>
       <c r="G83">
         <v>10239.8</v>
@@ -8099,37 +8099,37 @@
         <v>4551.6</v>
       </c>
       <c r="M83">
-        <v>26989.163388</v>
+        <v>27322.362936</v>
       </c>
       <c r="N83">
-        <v>-22437.563388</v>
+        <v>-22770.76293600001</v>
       </c>
       <c r="O83">
-        <v>-5788.891354104001</v>
+        <v>-5874.856837488001</v>
       </c>
       <c r="P83">
-        <v>-16648.672033896</v>
+        <v>-16895.906098512</v>
       </c>
       <c r="Q83">
-        <v>-14289.672033896</v>
+        <v>-14536.906098512</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2416391279493266</v>
+        <v>0.252519079502067</v>
       </c>
       <c r="T83">
-        <v>4.522843601601077</v>
+        <v>4.774112690578916</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04351052987889674</v>
+        <v>0.04297991366086142</v>
       </c>
       <c r="W83">
-        <v>0.2255402170545562</v>
+        <v>0.2256653363587689</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1686454646468866</v>
+        <v>0.1665888126389976</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2304990101245626</v>
+        <v>0.2323990101245625</v>
       </c>
       <c r="C84">
-        <v>-79398.05372249699</v>
+        <v>-81078.22567498797</v>
       </c>
       <c r="D84">
-        <v>26233.06627750302</v>
+        <v>25965.95432501204</v>
       </c>
       <c r="E84">
-        <v>101237.82</v>
+        <v>102650.88</v>
       </c>
       <c r="F84">
-        <v>115870.92</v>
+        <v>117283.98</v>
       </c>
       <c r="G84">
         <v>10239.8</v>
@@ -8181,37 +8181,37 @@
         <v>4551.6</v>
       </c>
       <c r="M84">
-        <v>27322.362936</v>
+        <v>27655.562484</v>
       </c>
       <c r="N84">
-        <v>-22770.76293600001</v>
+        <v>-23103.962484</v>
       </c>
       <c r="O84">
-        <v>-5874.856837488001</v>
+        <v>-5960.822320872001</v>
       </c>
       <c r="P84">
-        <v>-16895.906098512</v>
+        <v>-17143.140163128</v>
       </c>
       <c r="Q84">
-        <v>-14536.906098512</v>
+        <v>-14784.140163128</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.252519079502067</v>
+        <v>0.2646790253551298</v>
       </c>
       <c r="T84">
-        <v>4.774112690578916</v>
+        <v>5.054942848848264</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04297991366086142</v>
+        <v>0.0424620833757908</v>
       </c>
       <c r="W84">
-        <v>0.2256653363587689</v>
+        <v>0.2257874407399885</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1665888126389976</v>
+        <v>0.1645817185108169</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2323990101245625</v>
+        <v>0.2342990101245625</v>
       </c>
       <c r="C85">
-        <v>-81078.22567498797</v>
+        <v>-82753.01284896582</v>
       </c>
       <c r="D85">
-        <v>25965.95432501204</v>
+        <v>25704.22715103419</v>
       </c>
       <c r="E85">
-        <v>102650.88</v>
+        <v>104063.94</v>
       </c>
       <c r="F85">
-        <v>117283.98</v>
+        <v>118697.04</v>
       </c>
       <c r="G85">
         <v>10239.8</v>
@@ -8263,37 +8263,37 @@
         <v>4551.6</v>
       </c>
       <c r="M85">
-        <v>27655.562484</v>
+        <v>27988.762032</v>
       </c>
       <c r="N85">
-        <v>-23103.962484</v>
+        <v>-23437.162032</v>
       </c>
       <c r="O85">
-        <v>-5960.822320872001</v>
+        <v>-6046.787804256001</v>
       </c>
       <c r="P85">
-        <v>-17143.140163128</v>
+        <v>-17390.374227744</v>
       </c>
       <c r="Q85">
-        <v>-14784.140163128</v>
+        <v>-15031.374227744</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2646790253551298</v>
+        <v>0.2783589644398254</v>
       </c>
       <c r="T85">
-        <v>5.054942848848264</v>
+        <v>5.370876776901282</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0424620833757908</v>
+        <v>0.04195658238322186</v>
       </c>
       <c r="W85">
-        <v>0.2257874407399885</v>
+        <v>0.2259066378740363</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1645817185108169</v>
+        <v>0.1626224123380693</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2342990101245625</v>
+        <v>0.2361990101245625</v>
       </c>
       <c r="C86">
-        <v>-82753.01284896579</v>
+        <v>-84422.57644924719</v>
       </c>
       <c r="D86">
-        <v>25704.22715103419</v>
+        <v>25447.72355075279</v>
       </c>
       <c r="E86">
-        <v>104063.94</v>
+        <v>105477</v>
       </c>
       <c r="F86">
-        <v>118697.04</v>
+        <v>120110.1</v>
       </c>
       <c r="G86">
         <v>10239.8</v>
@@ -8345,37 +8345,37 @@
         <v>4551.6</v>
       </c>
       <c r="M86">
-        <v>27988.762032</v>
+        <v>28321.96158</v>
       </c>
       <c r="N86">
-        <v>-23437.162032</v>
+        <v>-23770.36158</v>
       </c>
       <c r="O86">
-        <v>-6046.787804256001</v>
+        <v>-6132.753287639999</v>
       </c>
       <c r="P86">
-        <v>-17390.374227744</v>
+        <v>-17637.60829236</v>
       </c>
       <c r="Q86">
-        <v>-15031.374227744</v>
+        <v>-15278.60829236</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2783589644398253</v>
+        <v>0.2938628954024803</v>
       </c>
       <c r="T86">
-        <v>5.370876776901278</v>
+        <v>5.728935228694697</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04195658238322186</v>
+        <v>0.04146297553165455</v>
       </c>
       <c r="W86">
-        <v>0.2259066378740363</v>
+        <v>0.2260230303696359</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1626224123380692</v>
+        <v>0.1607092074870332</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2361990101245625</v>
+        <v>0.2380990101245625</v>
       </c>
       <c r="C87">
-        <v>-84422.57644924719</v>
+        <v>-86087.07130954685</v>
       </c>
       <c r="D87">
-        <v>25447.72355075279</v>
+        <v>25196.28869045314</v>
       </c>
       <c r="E87">
-        <v>105477</v>
+        <v>106890.06</v>
       </c>
       <c r="F87">
-        <v>120110.1</v>
+        <v>121523.16</v>
       </c>
       <c r="G87">
         <v>10239.8</v>
@@ -8427,37 +8427,37 @@
         <v>4551.6</v>
       </c>
       <c r="M87">
-        <v>28321.96158</v>
+        <v>28655.161128</v>
       </c>
       <c r="N87">
-        <v>-23770.36158</v>
+        <v>-24103.561128</v>
       </c>
       <c r="O87">
-        <v>-6132.753287639999</v>
+        <v>-6218.718771024</v>
       </c>
       <c r="P87">
-        <v>-17637.60829236</v>
+        <v>-17884.842356976</v>
       </c>
       <c r="Q87">
-        <v>-15278.60829236</v>
+        <v>-15525.842356976</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2938628954024803</v>
+        <v>0.3115816736455146</v>
       </c>
       <c r="T87">
-        <v>5.728935228694697</v>
+        <v>6.138144887887176</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04146297553165455</v>
+        <v>0.04098084790919344</v>
       </c>
       <c r="W87">
-        <v>0.2260230303696359</v>
+        <v>0.2261367160630122</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1607092074870332</v>
+        <v>0.1588404957720677</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2380990101245625</v>
+        <v>0.2399990101245625</v>
       </c>
       <c r="C88">
-        <v>-86087.07130954685</v>
+        <v>-87746.64620414469</v>
       </c>
       <c r="D88">
-        <v>25196.28869045314</v>
+        <v>24949.77379585531</v>
       </c>
       <c r="E88">
-        <v>106890.06</v>
+        <v>108303.12</v>
       </c>
       <c r="F88">
-        <v>121523.16</v>
+        <v>122936.22</v>
       </c>
       <c r="G88">
         <v>10239.8</v>
@@ -8509,37 +8509,37 @@
         <v>4551.6</v>
       </c>
       <c r="M88">
-        <v>28655.161128</v>
+        <v>28988.360676</v>
       </c>
       <c r="N88">
-        <v>-24103.561128</v>
+        <v>-24436.760676</v>
       </c>
       <c r="O88">
-        <v>-6218.718771024</v>
+        <v>-6304.684254408</v>
       </c>
       <c r="P88">
-        <v>-17884.842356976</v>
+        <v>-18132.076421592</v>
       </c>
       <c r="Q88">
-        <v>-15525.842356976</v>
+        <v>-15773.076421592</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3115816736455146</v>
+        <v>0.3320264177720927</v>
       </c>
       <c r="T88">
-        <v>6.138144887887176</v>
+        <v>6.610309879263111</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04098084790919344</v>
+        <v>0.04050980368035215</v>
       </c>
       <c r="W88">
-        <v>0.2261367160630122</v>
+        <v>0.226247788292173</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1588404957720677</v>
+        <v>0.1570147429471014</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2399990101245625</v>
+        <v>0.2418990101245625</v>
       </c>
       <c r="C89">
-        <v>-87746.64620414469</v>
+        <v>-89401.44414143469</v>
       </c>
       <c r="D89">
-        <v>24949.77379585531</v>
+        <v>24708.0358585653</v>
       </c>
       <c r="E89">
-        <v>108303.12</v>
+        <v>109716.18</v>
       </c>
       <c r="F89">
-        <v>122936.22</v>
+        <v>124349.28</v>
       </c>
       <c r="G89">
         <v>10239.8</v>
@@ -8591,37 +8591,37 @@
         <v>4551.6</v>
       </c>
       <c r="M89">
-        <v>28988.360676</v>
+        <v>29321.560224</v>
       </c>
       <c r="N89">
-        <v>-24436.760676</v>
+        <v>-24769.960224</v>
       </c>
       <c r="O89">
-        <v>-6304.684254408</v>
+        <v>-6390.649737792</v>
       </c>
       <c r="P89">
-        <v>-18132.076421592</v>
+        <v>-18379.310486208</v>
       </c>
       <c r="Q89">
-        <v>-15773.076421592</v>
+        <v>-16020.310486208</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3320264177720927</v>
+        <v>0.3558786192531005</v>
       </c>
       <c r="T89">
-        <v>6.610309879263111</v>
+        <v>7.161169035868372</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04050980368035215</v>
+        <v>0.04004946500216632</v>
       </c>
       <c r="W89">
-        <v>0.226247788292173</v>
+        <v>0.2263563361524892</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1570147429471014</v>
+        <v>0.1552304845045206</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2418990101245625</v>
+        <v>0.2437990101245626</v>
       </c>
       <c r="C90">
-        <v>-89401.44414143469</v>
+        <v>-91051.60264057235</v>
       </c>
       <c r="D90">
-        <v>24708.0358585653</v>
+        <v>24470.93735942765</v>
       </c>
       <c r="E90">
-        <v>109716.18</v>
+        <v>111129.24</v>
       </c>
       <c r="F90">
-        <v>124349.28</v>
+        <v>125762.34</v>
       </c>
       <c r="G90">
         <v>10239.8</v>
@@ -8673,37 +8673,37 @@
         <v>4551.6</v>
       </c>
       <c r="M90">
-        <v>29321.560224</v>
+        <v>29654.759772</v>
       </c>
       <c r="N90">
-        <v>-24769.960224</v>
+        <v>-25103.159772</v>
       </c>
       <c r="O90">
-        <v>-6390.649737792</v>
+        <v>-6476.615221176</v>
       </c>
       <c r="P90">
-        <v>-18379.310486208</v>
+        <v>-18626.544550824</v>
       </c>
       <c r="Q90">
-        <v>-16020.310486208</v>
+        <v>-16267.544550824</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3558786192531005</v>
+        <v>0.3840675846397459</v>
       </c>
       <c r="T90">
-        <v>7.161169035868372</v>
+        <v>7.812184402765497</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04004946500216632</v>
+        <v>0.03959947101337793</v>
       </c>
       <c r="W90">
-        <v>0.2263563361524892</v>
+        <v>0.2264624447350455</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1552304845045206</v>
+        <v>0.1534863217572788</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2437990101245626</v>
+        <v>0.2456990101245626</v>
       </c>
       <c r="C91">
-        <v>-91051.60264057235</v>
+        <v>-92697.25399234514</v>
       </c>
       <c r="D91">
-        <v>24470.93735942765</v>
+        <v>24238.34600765487</v>
       </c>
       <c r="E91">
-        <v>111129.24</v>
+        <v>112542.3</v>
       </c>
       <c r="F91">
-        <v>125762.34</v>
+        <v>127175.4</v>
       </c>
       <c r="G91">
         <v>10239.8</v>
@@ -8755,37 +8755,37 @@
         <v>4551.6</v>
       </c>
       <c r="M91">
-        <v>29654.759772</v>
+        <v>29987.95932</v>
       </c>
       <c r="N91">
-        <v>-25103.159772</v>
+        <v>-25436.35932</v>
       </c>
       <c r="O91">
-        <v>-6476.615221176</v>
+        <v>-6562.580704560001</v>
       </c>
       <c r="P91">
-        <v>-18626.544550824</v>
+        <v>-18873.77861544</v>
       </c>
       <c r="Q91">
-        <v>-16267.544550824</v>
+        <v>-16514.77861544</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3840675846397459</v>
+        <v>0.4178943431037206</v>
       </c>
       <c r="T91">
-        <v>7.812184402765497</v>
+        <v>8.593402843042048</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03959947101337793</v>
+        <v>0.03915947689100707</v>
       </c>
       <c r="W91">
-        <v>0.2264624447350455</v>
+        <v>0.2265661953491006</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1534863217572788</v>
+        <v>0.1517809181821979</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2456990101245626</v>
+        <v>0.2475990101245625</v>
       </c>
       <c r="C92">
-        <v>-92697.25399234514</v>
+        <v>-94338.52550530607</v>
       </c>
       <c r="D92">
-        <v>24238.34600765487</v>
+        <v>24010.13449469394</v>
       </c>
       <c r="E92">
-        <v>112542.3</v>
+        <v>113955.36</v>
       </c>
       <c r="F92">
-        <v>127175.4</v>
+        <v>128588.46</v>
       </c>
       <c r="G92">
         <v>10239.8</v>
@@ -8837,37 +8837,37 @@
         <v>4551.6</v>
       </c>
       <c r="M92">
-        <v>29987.95932</v>
+        <v>30321.158868</v>
       </c>
       <c r="N92">
-        <v>-25436.35932</v>
+        <v>-25769.558868</v>
       </c>
       <c r="O92">
-        <v>-6562.580704560001</v>
+        <v>-6648.546187944</v>
       </c>
       <c r="P92">
-        <v>-18873.77861544</v>
+        <v>-19121.012680056</v>
       </c>
       <c r="Q92">
-        <v>-16514.77861544</v>
+        <v>-16762.012680056</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4178943431037206</v>
+        <v>0.459238159004134</v>
       </c>
       <c r="T92">
-        <v>8.593402843042048</v>
+        <v>9.548225381157831</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03915947689100707</v>
+        <v>0.03872915296912787</v>
       </c>
       <c r="W92">
-        <v>0.2265661953491006</v>
+        <v>0.2266676657298797</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1517809181821979</v>
+        <v>0.1501129960043717</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2475990101245625</v>
+        <v>0.2494990101245625</v>
       </c>
       <c r="C93">
-        <v>-94338.52550530607</v>
+        <v>-95975.53973813236</v>
       </c>
       <c r="D93">
-        <v>24010.13449469394</v>
+        <v>23786.18026186765</v>
       </c>
       <c r="E93">
-        <v>113955.36</v>
+        <v>115368.42</v>
       </c>
       <c r="F93">
-        <v>128588.46</v>
+        <v>130001.52</v>
       </c>
       <c r="G93">
         <v>10239.8</v>
@@ -8919,37 +8919,37 @@
         <v>4551.6</v>
       </c>
       <c r="M93">
-        <v>30321.158868</v>
+        <v>30654.358416</v>
       </c>
       <c r="N93">
-        <v>-25769.558868</v>
+        <v>-26102.758416</v>
       </c>
       <c r="O93">
-        <v>-6648.546187944</v>
+        <v>-6734.511671328001</v>
       </c>
       <c r="P93">
-        <v>-19121.012680056</v>
+        <v>-19368.246744672</v>
       </c>
       <c r="Q93">
-        <v>-16762.012680056</v>
+        <v>-17009.246744672</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.459238159004134</v>
+        <v>0.5109179288796509</v>
       </c>
       <c r="T93">
-        <v>9.548225381157831</v>
+        <v>10.74175355380256</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03872915296912787</v>
+        <v>0.03830818391511561</v>
       </c>
       <c r="W93">
-        <v>0.2266676657298797</v>
+        <v>0.2267669302328157</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1501129960043717</v>
+        <v>0.148481333004324</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2494990101245625</v>
+        <v>0.2513990101245626</v>
       </c>
       <c r="C94">
-        <v>-95975.53973813236</v>
+        <v>-97608.41471910026</v>
       </c>
       <c r="D94">
-        <v>23786.18026186765</v>
+        <v>23566.36528089976</v>
       </c>
       <c r="E94">
-        <v>115368.42</v>
+        <v>116781.48</v>
       </c>
       <c r="F94">
-        <v>130001.52</v>
+        <v>131414.58</v>
       </c>
       <c r="G94">
         <v>10239.8</v>
@@ -9001,37 +9001,37 @@
         <v>4551.6</v>
       </c>
       <c r="M94">
-        <v>30654.358416</v>
+        <v>30987.55796400001</v>
       </c>
       <c r="N94">
-        <v>-26102.758416</v>
+        <v>-26435.95796400001</v>
       </c>
       <c r="O94">
-        <v>-6734.511671328001</v>
+        <v>-6820.477154712003</v>
       </c>
       <c r="P94">
-        <v>-19368.246744672</v>
+        <v>-19615.480809288</v>
       </c>
       <c r="Q94">
-        <v>-17009.246744672</v>
+        <v>-17256.480809288</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5109179288796509</v>
+        <v>0.5773633472910296</v>
       </c>
       <c r="T94">
-        <v>10.74175355380256</v>
+        <v>12.27628977577436</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03830818391511561</v>
+        <v>0.03789626795903909</v>
       </c>
       <c r="W94">
-        <v>0.2267669302328157</v>
+        <v>0.2268640600152586</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.148481333004324</v>
+        <v>0.1468847595311592</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2513990101245626</v>
+        <v>0.2532990101245626</v>
       </c>
       <c r="C95">
-        <v>-97608.41471910026</v>
+        <v>-99237.26415350204</v>
       </c>
       <c r="D95">
-        <v>23566.36528089976</v>
+        <v>23350.57584649797</v>
       </c>
       <c r="E95">
-        <v>116781.48</v>
+        <v>118194.54</v>
       </c>
       <c r="F95">
-        <v>131414.58</v>
+        <v>132827.64</v>
       </c>
       <c r="G95">
         <v>10239.8</v>
@@ -9083,37 +9083,37 @@
         <v>4551.6</v>
       </c>
       <c r="M95">
-        <v>30987.55796400001</v>
+        <v>31320.757512</v>
       </c>
       <c r="N95">
-        <v>-26435.95796400001</v>
+        <v>-26769.15751200001</v>
       </c>
       <c r="O95">
-        <v>-6820.477154712003</v>
+        <v>-6906.442638096001</v>
       </c>
       <c r="P95">
-        <v>-19615.480809288</v>
+        <v>-19862.71487390401</v>
       </c>
       <c r="Q95">
-        <v>-17256.480809288</v>
+        <v>-17503.71487390401</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5773633472910296</v>
+        <v>0.6659572385062015</v>
       </c>
       <c r="T95">
-        <v>12.27628977577436</v>
+        <v>14.32233807173676</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03789626795903909</v>
+        <v>0.03749311617224081</v>
       </c>
       <c r="W95">
-        <v>0.2268640600152586</v>
+        <v>0.2269591232065856</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1468847595311592</v>
+        <v>0.1453221557063596</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2532990101245626</v>
+        <v>0.2551990101245625</v>
       </c>
       <c r="C96">
-        <v>-99237.26415350204</v>
+        <v>-100862.1976197708</v>
       </c>
       <c r="D96">
-        <v>23350.57584649797</v>
+        <v>23138.70238022918</v>
       </c>
       <c r="E96">
-        <v>118194.54</v>
+        <v>119607.6</v>
       </c>
       <c r="F96">
-        <v>132827.64</v>
+        <v>134240.7</v>
       </c>
       <c r="G96">
         <v>10239.8</v>
@@ -9165,37 +9165,37 @@
         <v>4551.6</v>
       </c>
       <c r="M96">
-        <v>31320.757512</v>
+        <v>31653.95706</v>
       </c>
       <c r="N96">
-        <v>-26769.15751200001</v>
+        <v>-27102.35706</v>
       </c>
       <c r="O96">
-        <v>-6906.442638096001</v>
+        <v>-6992.408121480001</v>
       </c>
       <c r="P96">
-        <v>-19862.71487390401</v>
+        <v>-20109.94893852</v>
       </c>
       <c r="Q96">
-        <v>-17503.71487390401</v>
+        <v>-17750.94893852</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6659572385062015</v>
+        <v>0.7899886862074421</v>
       </c>
       <c r="T96">
-        <v>14.32233807173676</v>
+        <v>17.18680568608412</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03749311617224081</v>
+        <v>0.03709845179148038</v>
       </c>
       <c r="W96">
-        <v>0.2269591232065856</v>
+        <v>0.2270521850675689</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1453221557063596</v>
+        <v>0.1437924488041875</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2551990101245625</v>
+        <v>0.2570990101245625</v>
       </c>
       <c r="C97">
-        <v>-100862.1976197708</v>
+        <v>-102483.3207550241</v>
       </c>
       <c r="D97">
-        <v>23138.70238022918</v>
+        <v>22930.63924497588</v>
       </c>
       <c r="E97">
-        <v>119607.6</v>
+        <v>121020.66</v>
       </c>
       <c r="F97">
-        <v>134240.7</v>
+        <v>135653.76</v>
       </c>
       <c r="G97">
         <v>10239.8</v>
@@ -9247,37 +9247,37 @@
         <v>4551.6</v>
       </c>
       <c r="M97">
-        <v>31653.95706</v>
+        <v>31987.156608</v>
       </c>
       <c r="N97">
-        <v>-27102.35706</v>
+        <v>-27435.55660800001</v>
       </c>
       <c r="O97">
-        <v>-6992.408121480001</v>
+        <v>-7078.373604864002</v>
       </c>
       <c r="P97">
-        <v>-20109.94893852</v>
+        <v>-20357.183003136</v>
       </c>
       <c r="Q97">
-        <v>-17750.94893852</v>
+        <v>-17998.183003136</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7899886862074421</v>
+        <v>0.9760358577593029</v>
       </c>
       <c r="T97">
-        <v>17.18680568608412</v>
+        <v>21.48350710760515</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03709845179148038</v>
+        <v>0.03671200958531912</v>
       </c>
       <c r="W97">
-        <v>0.2270521850675689</v>
+        <v>0.2271433081397818</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1437924488041875</v>
+        <v>0.1422946107958105</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2570990101245625</v>
+        <v>0.2589990101245626</v>
       </c>
       <c r="C98">
-        <v>-102483.3207550241</v>
+        <v>-104100.7354306861</v>
       </c>
       <c r="D98">
-        <v>22930.63924497588</v>
+        <v>22726.28456931392</v>
       </c>
       <c r="E98">
-        <v>121020.66</v>
+        <v>122433.72</v>
       </c>
       <c r="F98">
-        <v>135653.76</v>
+        <v>137066.82</v>
       </c>
       <c r="G98">
         <v>10239.8</v>
@@ -9329,37 +9329,37 @@
         <v>4551.6</v>
       </c>
       <c r="M98">
-        <v>31987.156608</v>
+        <v>32320.356156</v>
       </c>
       <c r="N98">
-        <v>-27435.55660800001</v>
+        <v>-27768.756156</v>
       </c>
       <c r="O98">
-        <v>-7078.373604864002</v>
+        <v>-7164.339088248001</v>
       </c>
       <c r="P98">
-        <v>-20357.183003136</v>
+        <v>-20604.417067752</v>
       </c>
       <c r="Q98">
-        <v>-17998.183003136</v>
+        <v>-18245.417067752</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9760358577593005</v>
+        <v>1.286114477012401</v>
       </c>
       <c r="T98">
-        <v>21.4835071076051</v>
+        <v>28.64467614347346</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03671200958531912</v>
+        <v>0.03633353525969728</v>
       </c>
       <c r="W98">
-        <v>0.2271433081397818</v>
+        <v>0.2272325523857634</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1422946107958105</v>
+        <v>0.1408276560453382</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2589990101245626</v>
+        <v>0.2608990101245626</v>
       </c>
       <c r="C99">
-        <v>-104100.7354306861</v>
+        <v>-105714.539918802</v>
       </c>
       <c r="D99">
-        <v>22726.28456931392</v>
+        <v>22525.54008119801</v>
       </c>
       <c r="E99">
-        <v>122433.72</v>
+        <v>123846.78</v>
       </c>
       <c r="F99">
-        <v>137066.82</v>
+        <v>138479.88</v>
       </c>
       <c r="G99">
         <v>10239.8</v>
@@ -9411,37 +9411,37 @@
         <v>4551.6</v>
       </c>
       <c r="M99">
-        <v>32320.356156</v>
+        <v>32653.555704</v>
       </c>
       <c r="N99">
-        <v>-27768.756156</v>
+        <v>-28101.955704</v>
       </c>
       <c r="O99">
-        <v>-7164.339088248001</v>
+        <v>-7250.304571632</v>
       </c>
       <c r="P99">
-        <v>-20604.417067752</v>
+        <v>-20851.651132368</v>
       </c>
       <c r="Q99">
-        <v>-18245.417067752</v>
+        <v>-18492.651132368</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.286114477012401</v>
+        <v>1.906271715518601</v>
       </c>
       <c r="T99">
-        <v>28.64467614347346</v>
+        <v>42.96701421521019</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03633353525969728</v>
+        <v>0.03596278489990445</v>
       </c>
       <c r="W99">
-        <v>0.2272325523857634</v>
+        <v>0.2273199753206026</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1408276560453382</v>
+        <v>0.1393906391469165</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2608990101245626</v>
+        <v>0.2627990101245625</v>
       </c>
       <c r="C100">
-        <v>-105714.539918802</v>
+        <v>-107324.8290496156</v>
       </c>
       <c r="D100">
-        <v>22525.54008119801</v>
+        <v>22328.31095038442</v>
       </c>
       <c r="E100">
-        <v>123846.78</v>
+        <v>125259.84</v>
       </c>
       <c r="F100">
-        <v>138479.88</v>
+        <v>139892.94</v>
       </c>
       <c r="G100">
         <v>10239.8</v>
@@ -9493,37 +9493,37 @@
         <v>4551.6</v>
       </c>
       <c r="M100">
-        <v>32653.555704</v>
+        <v>32986.755252</v>
       </c>
       <c r="N100">
-        <v>-28101.955704</v>
+        <v>-28435.155252</v>
       </c>
       <c r="O100">
-        <v>-7250.304571632</v>
+        <v>-7336.270055016002</v>
       </c>
       <c r="P100">
-        <v>-20851.651132368</v>
+        <v>-21098.885196984</v>
       </c>
       <c r="Q100">
-        <v>-18492.651132368</v>
+        <v>-18739.885196984</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.906271715518601</v>
+        <v>3.766743431037202</v>
       </c>
       <c r="T100">
-        <v>42.96701421521019</v>
+        <v>85.93402843042038</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03596278489990445</v>
+        <v>0.03559952444637006</v>
       </c>
       <c r="W100">
-        <v>0.2273199753206026</v>
+        <v>0.227405632135546</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1393906391469165</v>
+        <v>0.1379826528929071</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2627990101245625</v>
-      </c>
-      <c r="C101">
-        <v>-107324.8290496156</v>
-      </c>
-      <c r="D101">
-        <v>22328.31095038442</v>
-      </c>
-      <c r="E101">
-        <v>125259.84</v>
-      </c>
-      <c r="F101">
-        <v>139892.94</v>
-      </c>
-      <c r="G101">
-        <v>10239.8</v>
-      </c>
-      <c r="H101">
-        <v>126672.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>6910.6</v>
-      </c>
-      <c r="K101">
-        <v>2359</v>
-      </c>
-      <c r="L101">
-        <v>4551.6</v>
-      </c>
-      <c r="M101">
-        <v>32986.755252</v>
-      </c>
-      <c r="N101">
-        <v>-28435.155252</v>
-      </c>
-      <c r="O101">
-        <v>-7336.270055016002</v>
-      </c>
-      <c r="P101">
-        <v>-21098.885196984</v>
-      </c>
-      <c r="Q101">
-        <v>-18739.885196984</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.766743431037202</v>
-      </c>
-      <c r="T101">
-        <v>85.93402843042038</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03559952444637006</v>
-      </c>
-      <c r="W101">
-        <v>0.227405632135546</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1379826528929071</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
